--- a/listings.xlsx
+++ b/listings.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H172"/>
+  <dimension ref="A1:H256"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
@@ -674,7 +674,7 @@
         <v>용인수지신정마을9단지</v>
       </c>
       <c r="B11" t="str">
-        <v>10억 6,000</v>
+        <v>10억 5,000</v>
       </c>
       <c r="C11">
         <v>72</v>
@@ -683,13 +683,13 @@
         <v>901동</v>
       </c>
       <c r="E11" t="str">
-        <v>10/18</v>
+        <v>18/18</v>
       </c>
       <c r="F11" t="str">
         <v>남동향</v>
       </c>
       <c r="G11" t="str">
-        <v>샷시포함올수리 거실확장 중문 수지구청역역세권</v>
+        <v>샷시포함올수리,트인전망,공원,탄천연결,초역세권,입주협의</v>
       </c>
       <c r="H11" t="str">
         <v>naver</v>
@@ -700,22 +700,22 @@
         <v>용인수지신정마을9단지</v>
       </c>
       <c r="B12" t="str">
-        <v>10억 3,000</v>
+        <v>11억 7,000</v>
       </c>
       <c r="C12">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="D12" t="str">
-        <v>905동</v>
+        <v>902동</v>
       </c>
       <c r="E12" t="str">
-        <v>8/18</v>
+        <v>7/20</v>
       </c>
       <c r="F12" t="str">
-        <v>남동향</v>
+        <v>남서향</v>
       </c>
       <c r="G12" t="str">
-        <v>올수리,탄천전망,주차여유,초역세권,공원,4월초부터입주협의</v>
+        <v>정상입주,샷시교체,올수리,방1확장,트인전망,초역세권,학군</v>
       </c>
       <c r="H12" t="str">
         <v>naver</v>
@@ -752,7 +752,7 @@
         <v>용인수지신정마을9단지</v>
       </c>
       <c r="B14" t="str">
-        <v>10억 5,000</v>
+        <v>10억 6,000</v>
       </c>
       <c r="C14">
         <v>72</v>
@@ -761,13 +761,13 @@
         <v>901동</v>
       </c>
       <c r="E14" t="str">
-        <v>18/18</v>
+        <v>10/18</v>
       </c>
       <c r="F14" t="str">
         <v>남동향</v>
       </c>
       <c r="G14" t="str">
-        <v>샷시포함올수리,트인전망,공원,탄천연결,초역세권,입주협의</v>
+        <v>샷시포함올수리 거실확장 중문 수지구청역역세권</v>
       </c>
       <c r="H14" t="str">
         <v>naver</v>
@@ -804,22 +804,22 @@
         <v>용인수지신정마을9단지</v>
       </c>
       <c r="B16" t="str">
-        <v>11억 7,000</v>
+        <v>10억 3,000</v>
       </c>
       <c r="C16">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D16" t="str">
-        <v>902동</v>
+        <v>905동</v>
       </c>
       <c r="E16" t="str">
-        <v>7/20</v>
+        <v>8/18</v>
       </c>
       <c r="F16" t="str">
-        <v>남서향</v>
+        <v>남동향</v>
       </c>
       <c r="G16" t="str">
-        <v>정상입주,샷시교체,올수리,방1확장,트인전망,초역세권,학군</v>
+        <v>올수리,탄천전망,주차여유,초역세권,공원,4월초부터입주협의</v>
       </c>
       <c r="H16" t="str">
         <v>naver</v>
@@ -856,22 +856,22 @@
         <v>용인수지신정마을9단지</v>
       </c>
       <c r="B18" t="str">
-        <v>10억 3,000</v>
+        <v>10억 4,000</v>
       </c>
       <c r="C18">
         <v>72</v>
       </c>
       <c r="D18" t="str">
-        <v>905동</v>
+        <v>908동</v>
       </c>
       <c r="E18" t="str">
-        <v>16/18</v>
+        <v>13/18</v>
       </c>
       <c r="F18" t="str">
         <v>남동향</v>
       </c>
       <c r="G18" t="str">
-        <v>정상,전체올수리,샷시,수지구청역세권,탄천전망,지하주차장 굿</v>
+        <v>정상입주,로얄동,올수리,깨끗</v>
       </c>
       <c r="H18" t="str">
         <v>naver</v>
@@ -882,22 +882,22 @@
         <v>용인수지신정마을9단지</v>
       </c>
       <c r="B19" t="str">
-        <v>10억 4,000</v>
+        <v>10억 3,000</v>
       </c>
       <c r="C19">
         <v>72</v>
       </c>
       <c r="D19" t="str">
-        <v>908동</v>
+        <v>905동</v>
       </c>
       <c r="E19" t="str">
-        <v>13/18</v>
+        <v>16/18</v>
       </c>
       <c r="F19" t="str">
         <v>남동향</v>
       </c>
       <c r="G19" t="str">
-        <v>정상입주,로얄동,올수리,깨끗</v>
+        <v>정상,전체올수리,샷시,수지구청역세권,탄천전망,지하주차장 굿</v>
       </c>
       <c r="H19" t="str">
         <v>naver</v>
@@ -1194,22 +1194,22 @@
         <v>신정7단지(상록)공무원</v>
       </c>
       <c r="B31" t="str">
-        <v>10억 4,000</v>
+        <v>13억 9,000</v>
       </c>
       <c r="C31">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="D31" t="str">
-        <v>705동</v>
+        <v>704동</v>
       </c>
       <c r="E31" t="str">
-        <v>2/20</v>
+        <v>19/20</v>
       </c>
       <c r="F31" t="str">
         <v>남동향</v>
       </c>
       <c r="G31" t="str">
-        <v>입주일협의가. 중도금이후인테리어가능.2년전 전체적으로 올수리</v>
+        <v>세안고27년9월말, 외부샷시교체,방1확장,내부일부수리,로얄동로얄층</v>
       </c>
       <c r="H31" t="str">
         <v>naver</v>
@@ -1220,22 +1220,22 @@
         <v>신정7단지(상록)공무원</v>
       </c>
       <c r="B32" t="str">
-        <v>13억 9,000</v>
+        <v>14억</v>
       </c>
       <c r="C32">
         <v>109</v>
       </c>
       <c r="D32" t="str">
-        <v>704동</v>
+        <v>701동</v>
       </c>
       <c r="E32" t="str">
-        <v>19/20</v>
+        <v>16/20</v>
       </c>
       <c r="F32" t="str">
         <v>남동향</v>
       </c>
       <c r="G32" t="str">
-        <v>세안고27년9월말, 외부샷시교체,방1확장,내부일부수리,로얄동로얄층</v>
+        <v>예전 올수리 방1 주방확장 초품아 학군최고 신분당선역세권</v>
       </c>
       <c r="H32" t="str">
         <v>naver</v>
@@ -1246,22 +1246,22 @@
         <v>신정7단지(상록)공무원</v>
       </c>
       <c r="B33" t="str">
-        <v>14억</v>
+        <v>10억 4,000</v>
       </c>
       <c r="C33">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="D33" t="str">
-        <v>701동</v>
+        <v>705동</v>
       </c>
       <c r="E33" t="str">
-        <v>16/20</v>
+        <v>2/20</v>
       </c>
       <c r="F33" t="str">
         <v>남동향</v>
       </c>
       <c r="G33" t="str">
-        <v>예전 올수리 방1 주방확장 초품아 학군최고 신분당선역세권</v>
+        <v>주인직접의뢰.로얄동,즉시입주가능.초급매</v>
       </c>
       <c r="H33" t="str">
         <v>naver</v>
@@ -1662,7 +1662,7 @@
         <v>한국</v>
       </c>
       <c r="B49" t="str">
-        <v>12억</v>
+        <v>11억 5,000</v>
       </c>
       <c r="C49">
         <v>105</v>
@@ -1671,13 +1671,13 @@
         <v>103동</v>
       </c>
       <c r="E49" t="str">
-        <v>고/16</v>
+        <v>저/16</v>
       </c>
       <c r="F49" t="str">
         <v>남동향</v>
       </c>
       <c r="G49" t="str">
-        <v>입주가,  샷시포함 올수리되고 깨끗함</v>
+        <v>로얄동 리모델링 추진단지 수지구청역초역세권 입주협의</v>
       </c>
       <c r="H49" t="str">
         <v>naver</v>
@@ -1688,7 +1688,7 @@
         <v>한국</v>
       </c>
       <c r="B50" t="str">
-        <v>11억 5,000</v>
+        <v>12억</v>
       </c>
       <c r="C50">
         <v>105</v>
@@ -1697,13 +1697,13 @@
         <v>103동</v>
       </c>
       <c r="E50" t="str">
-        <v>저/16</v>
+        <v>고/16</v>
       </c>
       <c r="F50" t="str">
         <v>남동향</v>
       </c>
       <c r="G50" t="str">
-        <v>로얄동 리모델링 추진단지 수지구청역초역세권 입주협의</v>
+        <v>입주가,  샷시포함 올수리되고 깨끗함</v>
       </c>
       <c r="H50" t="str">
         <v>naver</v>
@@ -1948,22 +1948,22 @@
         <v>현대</v>
       </c>
       <c r="B60" t="str">
-        <v>9억 9,000</v>
+        <v>9억 5,000</v>
       </c>
       <c r="C60">
         <v>74</v>
       </c>
       <c r="D60" t="str">
-        <v>101동</v>
+        <v>103동</v>
       </c>
       <c r="E60" t="str">
-        <v>9/15</v>
+        <v>5/15</v>
       </c>
       <c r="F60" t="str">
-        <v>남동향</v>
+        <v>남서향</v>
       </c>
       <c r="G60" t="str">
-        <v>로열동  로열층 내부수리 했었던 집 수지구청역 도보5분 초역세권</v>
+        <v>기본, 정상입주협의, 수지구청역 초역세권, 명문학군,편의시설다양</v>
       </c>
       <c r="H60" t="str">
         <v>naver</v>
@@ -2000,22 +2000,22 @@
         <v>현대</v>
       </c>
       <c r="B62" t="str">
-        <v>9억 5,000</v>
+        <v>9억 9,000</v>
       </c>
       <c r="C62">
         <v>74</v>
       </c>
       <c r="D62" t="str">
-        <v>103동</v>
+        <v>101동</v>
       </c>
       <c r="E62" t="str">
-        <v>5/15</v>
+        <v>9/15</v>
       </c>
       <c r="F62" t="str">
-        <v>남서향</v>
+        <v>남동향</v>
       </c>
       <c r="G62" t="str">
-        <v>기본, 정상입주협의, 수지구청역 초역세권, 명문학군,편의시설다양</v>
+        <v>로열동  로열층 내부수리 했었던 집 수지구청역 도보5분 초역세권</v>
       </c>
       <c r="H62" t="str">
         <v>naver</v>
@@ -2026,22 +2026,22 @@
         <v>현대</v>
       </c>
       <c r="B63" t="str">
-        <v>11억 8,000</v>
+        <v>12억</v>
       </c>
       <c r="C63">
         <v>104</v>
       </c>
       <c r="D63" t="str">
-        <v>102동</v>
+        <v>105동</v>
       </c>
       <c r="E63" t="str">
-        <v>6/15</v>
+        <v>9/15</v>
       </c>
       <c r="F63" t="str">
         <v>남동향</v>
       </c>
       <c r="G63" t="str">
-        <v>내부수리, 수지구청역 초역세권, 명문학군, 로얄층, 편의시설다양</v>
+        <v>로열동 내부수리 전망트여 시원해요  신분당선도보5분  생활인프라최고</v>
       </c>
       <c r="H63" t="str">
         <v>naver</v>
@@ -2052,22 +2052,22 @@
         <v>현대</v>
       </c>
       <c r="B64" t="str">
-        <v>11억 8,000</v>
+        <v>12억</v>
       </c>
       <c r="C64">
         <v>104</v>
       </c>
       <c r="D64" t="str">
-        <v>104동</v>
+        <v>111동</v>
       </c>
       <c r="E64" t="str">
-        <v>7/15</v>
+        <v>8/15</v>
       </c>
       <c r="F64" t="str">
-        <v>남서향</v>
+        <v>남동향</v>
       </c>
       <c r="G64" t="str">
-        <v>입주급매 앞 뒤 트여 바람 잘 통하고 밝은 집  살기 좋아요</v>
+        <v>입주협의, 부분수리된 집, 수지구청역 가까운 동, 로얄동</v>
       </c>
       <c r="H64" t="str">
         <v>naver</v>
@@ -2078,22 +2078,22 @@
         <v>현대</v>
       </c>
       <c r="B65" t="str">
-        <v>12억</v>
+        <v>11억 9,000</v>
       </c>
       <c r="C65">
         <v>104</v>
       </c>
       <c r="D65" t="str">
-        <v>111동</v>
+        <v>106동</v>
       </c>
       <c r="E65" t="str">
-        <v>8/15</v>
+        <v>12/15</v>
       </c>
       <c r="F65" t="str">
         <v>남동향</v>
       </c>
       <c r="G65" t="str">
-        <v>입주협의, 부분수리된 집, 수지구청역 가까운 동, 로얄동</v>
+        <v>수리깨끗, 수지구청역 초역세권, 명문학군,로얄동층, 편의시설다양</v>
       </c>
       <c r="H65" t="str">
         <v>naver</v>
@@ -2104,22 +2104,22 @@
         <v>현대</v>
       </c>
       <c r="B66" t="str">
-        <v>12억</v>
+        <v>11억 8,000</v>
       </c>
       <c r="C66">
         <v>104</v>
       </c>
       <c r="D66" t="str">
-        <v>105동</v>
+        <v>104동</v>
       </c>
       <c r="E66" t="str">
-        <v>9/15</v>
+        <v>7/15</v>
       </c>
       <c r="F66" t="str">
-        <v>남동향</v>
+        <v>남서향</v>
       </c>
       <c r="G66" t="str">
-        <v>로열동 내부수리 전망트여 시원해요  신분당선도보5분  생활인프라최고</v>
+        <v>입주급매 앞 뒤 트여 바람 잘 통하고 밝은 집  살기 좋아요</v>
       </c>
       <c r="H66" t="str">
         <v>naver</v>
@@ -2130,22 +2130,22 @@
         <v>현대</v>
       </c>
       <c r="B67" t="str">
-        <v>12억</v>
+        <v>11억 8,000</v>
       </c>
       <c r="C67">
         <v>104</v>
       </c>
       <c r="D67" t="str">
-        <v>109동</v>
+        <v>102동</v>
       </c>
       <c r="E67" t="str">
-        <v>2/15</v>
+        <v>6/15</v>
       </c>
       <c r="F67" t="str">
         <v>남동향</v>
       </c>
       <c r="G67" t="str">
-        <v>입주가능  중간샷시설치 중문설치 내부수리  로열동 저층 햇살 좋아요</v>
+        <v>내부수리, 수지구청역 초역세권, 명문학군, 로얄층, 편의시설다양</v>
       </c>
       <c r="H67" t="str">
         <v>naver</v>
@@ -2156,22 +2156,22 @@
         <v>현대</v>
       </c>
       <c r="B68" t="str">
-        <v>11억 9,000</v>
+        <v>12억</v>
       </c>
       <c r="C68">
         <v>104</v>
       </c>
       <c r="D68" t="str">
-        <v>106동</v>
+        <v>109동</v>
       </c>
       <c r="E68" t="str">
-        <v>12/15</v>
+        <v>2/15</v>
       </c>
       <c r="F68" t="str">
         <v>남동향</v>
       </c>
       <c r="G68" t="str">
-        <v>수리깨끗, 수지구청역 초역세권, 명문학군,로얄동층, 편의시설다양</v>
+        <v>입주가능  중간샷시설치 중문설치 내부수리  로열동 저층 햇살 좋아요</v>
       </c>
       <c r="H68" t="str">
         <v>naver</v>
@@ -2286,22 +2286,22 @@
         <v>현대</v>
       </c>
       <c r="B73" t="str">
-        <v>12억 5,000</v>
+        <v>11억</v>
       </c>
       <c r="C73">
         <v>104</v>
       </c>
       <c r="D73" t="str">
-        <v>106동</v>
+        <v>109동</v>
       </c>
       <c r="E73" t="str">
-        <v>2/15</v>
+        <v>1/15</v>
       </c>
       <c r="F73" t="str">
         <v>남동향</v>
       </c>
       <c r="G73" t="str">
-        <v>깨끗함, 기본상태, 8월말 입주가능</v>
+        <v>입주추천.샷시.화장실등 전체 올수리.역세권</v>
       </c>
       <c r="H73" t="str">
         <v>naver</v>
@@ -2312,22 +2312,22 @@
         <v>현대</v>
       </c>
       <c r="B74" t="str">
-        <v>9억 7,000</v>
+        <v>12억 5,000</v>
       </c>
       <c r="C74">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="D74" t="str">
-        <v>101동</v>
+        <v>106동</v>
       </c>
       <c r="E74" t="str">
-        <v>9/15</v>
+        <v>2/15</v>
       </c>
       <c r="F74" t="str">
         <v>남동향</v>
       </c>
       <c r="G74" t="str">
-        <v>예전수리된집, 10월말 입주가능</v>
+        <v>깨끗함, 기본상태, 8월말 입주가능</v>
       </c>
       <c r="H74" t="str">
         <v>naver</v>
@@ -2338,22 +2338,22 @@
         <v>현대</v>
       </c>
       <c r="B75" t="str">
-        <v>11억</v>
+        <v>9억 7,000</v>
       </c>
       <c r="C75">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="D75" t="str">
-        <v>109동</v>
+        <v>101동</v>
       </c>
       <c r="E75" t="str">
-        <v>1/15</v>
+        <v>9/15</v>
       </c>
       <c r="F75" t="str">
         <v>남동향</v>
       </c>
       <c r="G75" t="str">
-        <v>입주추천.샷시.화장실등 전체 올수리.역세권</v>
+        <v>예전수리된집, 10월말 입주가능</v>
       </c>
       <c r="H75" t="str">
         <v>naver</v>
@@ -2364,22 +2364,22 @@
         <v>현대</v>
       </c>
       <c r="B76" t="str">
-        <v>12억</v>
+        <v>11억</v>
       </c>
       <c r="C76">
         <v>104</v>
       </c>
       <c r="D76" t="str">
-        <v>112동</v>
+        <v>104동</v>
       </c>
       <c r="E76" t="str">
-        <v>3/15</v>
+        <v>1/15</v>
       </c>
       <c r="F76" t="str">
-        <v>남동향</v>
+        <v>남서향</v>
       </c>
       <c r="G76" t="str">
-        <v>정상입주 입주일협의 수지구청역 초역세권</v>
+        <v>세안고, 아이 키우기 좋아요. 동간 거리 넓고 조용한 동</v>
       </c>
       <c r="H76" t="str">
         <v>naver</v>
@@ -2390,22 +2390,22 @@
         <v>현대</v>
       </c>
       <c r="B77" t="str">
-        <v>11억</v>
+        <v>12억</v>
       </c>
       <c r="C77">
         <v>104</v>
       </c>
       <c r="D77" t="str">
-        <v>104동</v>
+        <v>112동</v>
       </c>
       <c r="E77" t="str">
-        <v>1/15</v>
+        <v>3/15</v>
       </c>
       <c r="F77" t="str">
-        <v>남서향</v>
+        <v>남동향</v>
       </c>
       <c r="G77" t="str">
-        <v>세안고, 아이 키우기 좋아요. 동간 거리 넓고 조용한 동</v>
+        <v>정상입주 입주일협의 수지구청역 초역세권</v>
       </c>
       <c r="H77" t="str">
         <v>naver</v>
@@ -2812,16 +2812,16 @@
         <v>78</v>
       </c>
       <c r="D93" t="str">
-        <v>103동</v>
+        <v>104동</v>
       </c>
       <c r="E93" t="str">
-        <v>5/17</v>
+        <v>12/17</v>
       </c>
       <c r="F93" t="str">
         <v>남동향</v>
       </c>
       <c r="G93" t="str">
-        <v>협의가능 투자가치굿, 도보역세권, 리모델링단지</v>
+        <v>R2, 주인거주, 올수리, 리모델링사업진행중</v>
       </c>
       <c r="H93" t="str">
         <v>naver</v>
@@ -2832,22 +2832,22 @@
         <v>동부</v>
       </c>
       <c r="B94" t="str">
-        <v>8억 2,000</v>
+        <v>8억 5,000</v>
       </c>
       <c r="C94">
         <v>78</v>
       </c>
       <c r="D94" t="str">
-        <v>102동</v>
+        <v>103동</v>
       </c>
       <c r="E94" t="str">
-        <v>8/17</v>
+        <v>5/17</v>
       </c>
       <c r="F94" t="str">
         <v>남동향</v>
       </c>
       <c r="G94" t="str">
-        <v>입주급매 신분당선도보8분 내부수리됨 아파트뒤 도서관 소아병동입점</v>
+        <v>협의가능 투자가치굿, 도보역세권, 리모델링단지</v>
       </c>
       <c r="H94" t="str">
         <v>naver</v>
@@ -2858,22 +2858,22 @@
         <v>동부</v>
       </c>
       <c r="B95" t="str">
-        <v>8억 5,000</v>
+        <v>8억 2,000</v>
       </c>
       <c r="C95">
         <v>78</v>
       </c>
       <c r="D95" t="str">
-        <v>101동</v>
+        <v>102동</v>
       </c>
       <c r="E95" t="str">
-        <v>2/17</v>
+        <v>8/17</v>
       </c>
       <c r="F95" t="str">
         <v>남동향</v>
       </c>
       <c r="G95" t="str">
-        <v>방3 특올수리 거실확장 리모델링 진행중</v>
+        <v>입주급매 신분당선도보8분 내부수리됨 아파트뒤 도서관 소아병동입점</v>
       </c>
       <c r="H95" t="str">
         <v>naver</v>
@@ -2884,7 +2884,7 @@
         <v>동부</v>
       </c>
       <c r="B96" t="str">
-        <v>9억 2,000</v>
+        <v>8억 5,000</v>
       </c>
       <c r="C96">
         <v>78</v>
@@ -2893,13 +2893,13 @@
         <v>105동</v>
       </c>
       <c r="E96" t="str">
-        <v>11/17</v>
+        <v>17/17</v>
       </c>
       <c r="F96" t="str">
         <v>남동향</v>
       </c>
       <c r="G96" t="str">
-        <v>R3, 주인거주,올수리,리모델링사업진행중</v>
+        <v xml:space="preserve">방3 리모델링 사업 진행중 입주일협의 </v>
       </c>
       <c r="H96" t="str">
         <v>naver</v>
@@ -2910,13 +2910,13 @@
         <v>동부</v>
       </c>
       <c r="B97" t="str">
-        <v>8억 8,000</v>
+        <v>9억 8,000</v>
       </c>
       <c r="C97">
         <v>78</v>
       </c>
       <c r="D97" t="str">
-        <v>103동</v>
+        <v>102동</v>
       </c>
       <c r="E97" t="str">
         <v>17/17</v>
@@ -2925,7 +2925,7 @@
         <v>남동향</v>
       </c>
       <c r="G97" t="str">
-        <v>최근 샷시포함 특올수리, 거실확장, 신혼부부 거주중</v>
+        <v>R2, 주인거주, 특올수리, 리모델링사업진행중</v>
       </c>
       <c r="H97" t="str">
         <v>naver</v>
@@ -2936,22 +2936,22 @@
         <v>동부</v>
       </c>
       <c r="B98" t="str">
-        <v>8억 5,000</v>
+        <v>8억 7,000</v>
       </c>
       <c r="C98">
         <v>78</v>
       </c>
       <c r="D98" t="str">
-        <v>104동</v>
+        <v>106동</v>
       </c>
       <c r="E98" t="str">
-        <v>12/17</v>
+        <v>2/17</v>
       </c>
       <c r="F98" t="str">
         <v>남동향</v>
       </c>
       <c r="G98" t="str">
-        <v>R2, 주인거주, 올수리, 리모델링사업진행중</v>
+        <v>방3, 거실확장 및 특올수리, 집상태 최고</v>
       </c>
       <c r="H98" t="str">
         <v>naver</v>
@@ -2962,22 +2962,22 @@
         <v>동부</v>
       </c>
       <c r="B99" t="str">
-        <v>8억 5,000</v>
+        <v>10억</v>
       </c>
       <c r="C99">
         <v>78</v>
       </c>
       <c r="D99" t="str">
-        <v>104동</v>
+        <v>106동</v>
       </c>
       <c r="E99" t="str">
-        <v>2/17</v>
+        <v>8/17</v>
       </c>
       <c r="F99" t="str">
         <v>남동향</v>
       </c>
       <c r="G99" t="str">
-        <v>R2, 주인거주, 올수리, 리모델링사업진행중</v>
+        <v>협의가능, 투자가치굿, 로얄동, 채광좋음</v>
       </c>
       <c r="H99" t="str">
         <v>naver</v>
@@ -2988,13 +2988,13 @@
         <v>동부</v>
       </c>
       <c r="B100" t="str">
-        <v>9억 8,000</v>
+        <v>8억 8,000</v>
       </c>
       <c r="C100">
         <v>78</v>
       </c>
       <c r="D100" t="str">
-        <v>102동</v>
+        <v>103동</v>
       </c>
       <c r="E100" t="str">
         <v>17/17</v>
@@ -3003,7 +3003,7 @@
         <v>남동향</v>
       </c>
       <c r="G100" t="str">
-        <v>R2, 주인거주, 특올수리, 리모델링사업진행중</v>
+        <v>최근 샷시포함 특올수리, 거실확장, 신혼부부 거주중</v>
       </c>
       <c r="H100" t="str">
         <v>naver</v>
@@ -3014,22 +3014,22 @@
         <v>동부</v>
       </c>
       <c r="B101" t="str">
-        <v>10억</v>
+        <v>9억</v>
       </c>
       <c r="C101">
         <v>78</v>
       </c>
       <c r="D101" t="str">
-        <v>106동</v>
+        <v>101동</v>
       </c>
       <c r="E101" t="str">
-        <v>8/17</v>
+        <v>6/17</v>
       </c>
       <c r="F101" t="str">
         <v>남동향</v>
       </c>
       <c r="G101" t="str">
-        <v>협의가능, 투자가치굿, 로얄동, 채광좋음</v>
+        <v>방3 리모델링 입주협의</v>
       </c>
       <c r="H101" t="str">
         <v>naver</v>
@@ -3040,13 +3040,13 @@
         <v>동부</v>
       </c>
       <c r="B102" t="str">
-        <v>8억 7,000</v>
+        <v>8억 5,000</v>
       </c>
       <c r="C102">
         <v>78</v>
       </c>
       <c r="D102" t="str">
-        <v>106동</v>
+        <v>101동</v>
       </c>
       <c r="E102" t="str">
         <v>2/17</v>
@@ -3055,7 +3055,7 @@
         <v>남동향</v>
       </c>
       <c r="G102" t="str">
-        <v>방3, 거실확장 및 특올수리, 집상태 최고</v>
+        <v>방3 특올수리 거실확장 리모델링 진행중</v>
       </c>
       <c r="H102" t="str">
         <v>naver</v>
@@ -3072,16 +3072,16 @@
         <v>78</v>
       </c>
       <c r="D103" t="str">
-        <v>105동</v>
+        <v>104동</v>
       </c>
       <c r="E103" t="str">
-        <v>17/17</v>
+        <v>2/17</v>
       </c>
       <c r="F103" t="str">
         <v>남동향</v>
       </c>
       <c r="G103" t="str">
-        <v xml:space="preserve">방3 리모델링 사업 진행중 입주일협의 </v>
+        <v>R2, 주인거주, 올수리, 리모델링사업진행중</v>
       </c>
       <c r="H103" t="str">
         <v>naver</v>
@@ -3092,22 +3092,22 @@
         <v>동부</v>
       </c>
       <c r="B104" t="str">
-        <v>9억</v>
+        <v>9억 2,000</v>
       </c>
       <c r="C104">
         <v>78</v>
       </c>
       <c r="D104" t="str">
-        <v>101동</v>
+        <v>105동</v>
       </c>
       <c r="E104" t="str">
-        <v>6/17</v>
+        <v>11/17</v>
       </c>
       <c r="F104" t="str">
         <v>남동향</v>
       </c>
       <c r="G104" t="str">
-        <v>방3 리모델링 입주협의</v>
+        <v>R3, 주인거주,올수리,리모델링사업진행중</v>
       </c>
       <c r="H104" t="str">
         <v>naver</v>
@@ -3118,22 +3118,22 @@
         <v>동부</v>
       </c>
       <c r="B105" t="str">
-        <v>8억 7,000</v>
+        <v>8억 5,000</v>
       </c>
       <c r="C105">
         <v>78</v>
       </c>
       <c r="D105" t="str">
-        <v>106동</v>
+        <v>103동</v>
       </c>
       <c r="E105" t="str">
-        <v>12/17</v>
+        <v>16/17</v>
       </c>
       <c r="F105" t="str">
         <v>남동향</v>
       </c>
       <c r="G105" t="str">
-        <v>방3화1, 계단식, 로얄동, 채광좋음</v>
+        <v>R2, 계단식,주인거주,로얄층,리모델링추진중</v>
       </c>
       <c r="H105" t="str">
         <v>naver</v>
@@ -3144,7 +3144,7 @@
         <v>동부</v>
       </c>
       <c r="B106" t="str">
-        <v>8억 7,000</v>
+        <v>8억 8,000</v>
       </c>
       <c r="C106">
         <v>78</v>
@@ -3153,13 +3153,13 @@
         <v>106동</v>
       </c>
       <c r="E106" t="str">
-        <v>11/17</v>
+        <v>9/17</v>
       </c>
       <c r="F106" t="str">
         <v>남동향</v>
       </c>
       <c r="G106" t="str">
-        <v>R3, 계단식,주인거주,올수리,리모델링추진중</v>
+        <v>R3, 계단식,주인거주,확장 특올수리,리모델링추진중</v>
       </c>
       <c r="H106" t="str">
         <v>naver</v>
@@ -3176,16 +3176,16 @@
         <v>78</v>
       </c>
       <c r="D107" t="str">
-        <v>101동</v>
+        <v>106동</v>
       </c>
       <c r="E107" t="str">
-        <v>5/17</v>
+        <v>8/17</v>
       </c>
       <c r="F107" t="str">
         <v>남동향</v>
       </c>
       <c r="G107" t="str">
-        <v>R3, 거실 방확장 올수리, 리모델링추진중</v>
+        <v>R3, 로얄층, 올수리,세안고,리모델링추진중</v>
       </c>
       <c r="H107" t="str">
         <v>naver</v>
@@ -3202,16 +3202,16 @@
         <v>78</v>
       </c>
       <c r="D108" t="str">
-        <v>106동</v>
+        <v>101동</v>
       </c>
       <c r="E108" t="str">
-        <v>8/17</v>
+        <v>5/17</v>
       </c>
       <c r="F108" t="str">
         <v>남동향</v>
       </c>
       <c r="G108" t="str">
-        <v>R3, 로얄층, 올수리,세안고,리모델링추진중</v>
+        <v>R3, 거실 방확장 올수리, 리모델링추진중</v>
       </c>
       <c r="H108" t="str">
         <v>naver</v>
@@ -3222,22 +3222,22 @@
         <v>동부</v>
       </c>
       <c r="B109" t="str">
-        <v>7억 5,000</v>
+        <v>8억 5,000</v>
       </c>
       <c r="C109">
         <v>78</v>
       </c>
       <c r="D109" t="str">
-        <v>104동</v>
+        <v>106동</v>
       </c>
       <c r="E109" t="str">
-        <v>1/17</v>
+        <v>15/17</v>
       </c>
       <c r="F109" t="str">
         <v>남동향</v>
       </c>
       <c r="G109" t="str">
-        <v>입주협의  부분수리  방2  리모추진중  초중고 도서관 역세권 메디칼센터</v>
+        <v>R3, 계단식,주인거주, 로얄층, 리모델링추진중</v>
       </c>
       <c r="H109" t="str">
         <v>naver</v>
@@ -3248,22 +3248,22 @@
         <v>동부</v>
       </c>
       <c r="B110" t="str">
-        <v>8억 5,000</v>
+        <v>8억 7,000</v>
       </c>
       <c r="C110">
         <v>78</v>
       </c>
       <c r="D110" t="str">
-        <v>103동</v>
+        <v>106동</v>
       </c>
       <c r="E110" t="str">
-        <v>16/17</v>
+        <v>12/17</v>
       </c>
       <c r="F110" t="str">
         <v>남동향</v>
       </c>
       <c r="G110" t="str">
-        <v>R2, 계단식,주인거주,로얄층,리모델링추진중</v>
+        <v>방3화1, 계단식, 로얄동, 채광좋음</v>
       </c>
       <c r="H110" t="str">
         <v>naver</v>
@@ -3274,22 +3274,22 @@
         <v>동부</v>
       </c>
       <c r="B111" t="str">
-        <v>8억 8,000</v>
+        <v>7억 5,000</v>
       </c>
       <c r="C111">
         <v>78</v>
       </c>
       <c r="D111" t="str">
-        <v>106동</v>
+        <v>104동</v>
       </c>
       <c r="E111" t="str">
-        <v>9/17</v>
+        <v>1/17</v>
       </c>
       <c r="F111" t="str">
         <v>남동향</v>
       </c>
       <c r="G111" t="str">
-        <v>R3, 계단식,주인거주,확장 특올수리,리모델링추진중</v>
+        <v>입주협의  부분수리  방2  리모추진중  초중고 도서관 역세권 메디칼센터</v>
       </c>
       <c r="H111" t="str">
         <v>naver</v>
@@ -3300,7 +3300,7 @@
         <v>동부</v>
       </c>
       <c r="B112" t="str">
-        <v>8억 5,000</v>
+        <v>8억 7,000</v>
       </c>
       <c r="C112">
         <v>78</v>
@@ -3309,13 +3309,13 @@
         <v>106동</v>
       </c>
       <c r="E112" t="str">
-        <v>15/17</v>
+        <v>11/17</v>
       </c>
       <c r="F112" t="str">
         <v>남동향</v>
       </c>
       <c r="G112" t="str">
-        <v>R3, 계단식,주인거주, 로얄층, 리모델링추진중</v>
+        <v>R3, 계단식,주인거주,올수리,리모델링추진중</v>
       </c>
       <c r="H112" t="str">
         <v>naver</v>
@@ -3326,22 +3326,22 @@
         <v>동부</v>
       </c>
       <c r="B113" t="str">
-        <v>9억</v>
+        <v>9억 2,000</v>
       </c>
       <c r="C113">
         <v>78</v>
       </c>
       <c r="D113" t="str">
-        <v>102동</v>
+        <v>101동</v>
       </c>
       <c r="E113" t="str">
-        <v>6/17</v>
+        <v>10/17</v>
       </c>
       <c r="F113" t="str">
         <v>남동향</v>
       </c>
       <c r="G113" t="str">
-        <v>방2화1,  도보역세권, 채광좋음, 수리됨</v>
+        <v>방3화1, 채광좋음, 도보역세권, 일정등협의가능</v>
       </c>
       <c r="H113" t="str">
         <v>naver</v>
@@ -3410,16 +3410,16 @@
         <v>78</v>
       </c>
       <c r="D116" t="str">
-        <v>105동</v>
+        <v>102동</v>
       </c>
       <c r="E116" t="str">
-        <v>7/17</v>
+        <v>6/17</v>
       </c>
       <c r="F116" t="str">
         <v>남동향</v>
       </c>
       <c r="G116" t="str">
-        <v>방3화1, 계단식, 방확장, 채광좋음, 도보역세권</v>
+        <v>방2화1,  도보역세권, 채광좋음, 수리됨</v>
       </c>
       <c r="H116" t="str">
         <v>naver</v>
@@ -3439,13 +3439,13 @@
         <v>101동</v>
       </c>
       <c r="E117" t="str">
-        <v>10/17</v>
+        <v>8/17</v>
       </c>
       <c r="F117" t="str">
         <v>남동향</v>
       </c>
       <c r="G117" t="str">
-        <v>방3화1, 채광좋음, 도보역세권, 일정등협의가능</v>
+        <v>방3, 계단식, 샷시포함올수리, 채광좋음</v>
       </c>
       <c r="H117" t="str">
         <v>naver</v>
@@ -3456,22 +3456,22 @@
         <v>동부</v>
       </c>
       <c r="B118" t="str">
-        <v>9억 2,000</v>
+        <v>9억</v>
       </c>
       <c r="C118">
         <v>78</v>
       </c>
       <c r="D118" t="str">
-        <v>101동</v>
+        <v>105동</v>
       </c>
       <c r="E118" t="str">
-        <v>8/17</v>
+        <v>7/17</v>
       </c>
       <c r="F118" t="str">
         <v>남동향</v>
       </c>
       <c r="G118" t="str">
-        <v>방3, 계단식, 샷시포함올수리, 채광좋음</v>
+        <v>방3화1, 계단식, 방확장, 채광좋음, 도보역세권</v>
       </c>
       <c r="H118" t="str">
         <v>naver</v>
@@ -3534,22 +3534,22 @@
         <v>동부</v>
       </c>
       <c r="B121" t="str">
-        <v>8억 3,000</v>
+        <v>9억 3,000</v>
       </c>
       <c r="C121">
         <v>78</v>
       </c>
       <c r="D121" t="str">
-        <v>105동</v>
+        <v>101동</v>
       </c>
       <c r="E121" t="str">
-        <v>중/17</v>
+        <v>13/17</v>
       </c>
       <c r="F121" t="str">
         <v>남동향</v>
       </c>
       <c r="G121" t="str">
-        <v>꼭팔아요 급매 입주협의 방3  특올수리  초중고 역세권 선호하는동 강추</v>
+        <v>협의가능 투자가치굿, 우수인프라, 도보역세권</v>
       </c>
       <c r="H121" t="str">
         <v>naver</v>
@@ -3560,22 +3560,22 @@
         <v>동부</v>
       </c>
       <c r="B122" t="str">
-        <v>9억 3,000</v>
+        <v>8억 3,000</v>
       </c>
       <c r="C122">
         <v>78</v>
       </c>
       <c r="D122" t="str">
-        <v>101동</v>
+        <v>105동</v>
       </c>
       <c r="E122" t="str">
-        <v>13/17</v>
+        <v>중/17</v>
       </c>
       <c r="F122" t="str">
         <v>남동향</v>
       </c>
       <c r="G122" t="str">
-        <v>협의가능 투자가치굿, 우수인프라, 도보역세권</v>
+        <v>꼭팔아요 급매 입주협의 방3  특올수리  초중고 역세권 선호하는동 강추</v>
       </c>
       <c r="H122" t="str">
         <v>naver</v>
@@ -3592,16 +3592,16 @@
         <v>78</v>
       </c>
       <c r="D123" t="str">
-        <v>105동</v>
+        <v>101동</v>
       </c>
       <c r="E123" t="str">
-        <v>고/17</v>
+        <v>중/17</v>
       </c>
       <c r="F123" t="str">
         <v>남동향</v>
       </c>
       <c r="G123" t="str">
-        <v>샷시 제외 특올수리이며 입주 가능하고 리모델링 추진 단지임</v>
+        <v>방3,주인거주,리모델링 이주확정</v>
       </c>
       <c r="H123" t="str">
         <v>naver</v>
@@ -3612,22 +3612,22 @@
         <v>동부</v>
       </c>
       <c r="B124" t="str">
-        <v>8억 5,000</v>
+        <v>8억 7,000</v>
       </c>
       <c r="C124">
         <v>78</v>
       </c>
       <c r="D124" t="str">
-        <v>105동</v>
+        <v>103동</v>
       </c>
       <c r="E124" t="str">
-        <v>중/17</v>
+        <v>고/17</v>
       </c>
       <c r="F124" t="str">
         <v>남동향</v>
       </c>
       <c r="G124" t="str">
-        <v>입주가능 화장실포함올수리 방3개 수지구청역도보권및도서관인접</v>
+        <v>방2화1, 계단식, 채광좋음, 도보역세권</v>
       </c>
       <c r="H124" t="str">
         <v>naver</v>
@@ -3638,22 +3638,22 @@
         <v>동부</v>
       </c>
       <c r="B125" t="str">
-        <v>8억 7,000</v>
+        <v>8억 5,000</v>
       </c>
       <c r="C125">
         <v>78</v>
       </c>
       <c r="D125" t="str">
-        <v>103동</v>
+        <v>105동</v>
       </c>
       <c r="E125" t="str">
-        <v>고/17</v>
+        <v>중/17</v>
       </c>
       <c r="F125" t="str">
         <v>남동향</v>
       </c>
       <c r="G125" t="str">
-        <v>방2화1, 계단식, 채광좋음, 도보역세권</v>
+        <v>입주가능 화장실포함올수리 방3개 수지구청역도보권및도서관인접</v>
       </c>
       <c r="H125" t="str">
         <v>naver</v>
@@ -3670,16 +3670,16 @@
         <v>78</v>
       </c>
       <c r="D126" t="str">
-        <v>101동</v>
+        <v>105동</v>
       </c>
       <c r="E126" t="str">
-        <v>중/17</v>
+        <v>고/17</v>
       </c>
       <c r="F126" t="str">
         <v>남동향</v>
       </c>
       <c r="G126" t="str">
-        <v>방3,주인거주,리모델링 이주확정</v>
+        <v>샷시 제외 특올수리이며 입주 가능하고 리모델링 추진 단지임</v>
       </c>
       <c r="H126" t="str">
         <v>naver</v>
@@ -3690,13 +3690,13 @@
         <v>동부</v>
       </c>
       <c r="B127" t="str">
-        <v>8억 6,000</v>
+        <v>9억</v>
       </c>
       <c r="C127">
         <v>78</v>
       </c>
       <c r="D127" t="str">
-        <v>103동</v>
+        <v>102동</v>
       </c>
       <c r="E127" t="str">
         <v>중/17</v>
@@ -3705,7 +3705,7 @@
         <v>남동향</v>
       </c>
       <c r="G127" t="str">
-        <v>방2화1, 로얄동로얄층, 올수리, 채광좋음</v>
+        <v>방2화1, 채광좋음, 올수리, 도보역세권</v>
       </c>
       <c r="H127" t="str">
         <v>naver</v>
@@ -3716,22 +3716,22 @@
         <v>동부</v>
       </c>
       <c r="B128" t="str">
-        <v>9억</v>
+        <v>8억 6,000</v>
       </c>
       <c r="C128">
         <v>78</v>
       </c>
       <c r="D128" t="str">
-        <v>104동</v>
+        <v>103동</v>
       </c>
       <c r="E128" t="str">
-        <v>고/17</v>
+        <v>중/17</v>
       </c>
       <c r="F128" t="str">
         <v>남동향</v>
       </c>
       <c r="G128" t="str">
-        <v>올수리, 도보역세권, 일정 등 협의가능</v>
+        <v>방2화1, 로얄동로얄층, 올수리, 채광좋음</v>
       </c>
       <c r="H128" t="str">
         <v>naver</v>
@@ -3748,16 +3748,16 @@
         <v>78</v>
       </c>
       <c r="D129" t="str">
-        <v>102동</v>
+        <v>104동</v>
       </c>
       <c r="E129" t="str">
-        <v>중/17</v>
+        <v>고/17</v>
       </c>
       <c r="F129" t="str">
         <v>남동향</v>
       </c>
       <c r="G129" t="str">
-        <v>방2화1, 채광좋음, 올수리, 도보역세권</v>
+        <v>올수리, 도보역세권, 일정 등 협의가능</v>
       </c>
       <c r="H129" t="str">
         <v>naver</v>
@@ -3794,16 +3794,16 @@
         <v>동부</v>
       </c>
       <c r="B131" t="str">
-        <v>8억 5,000</v>
+        <v>9억</v>
       </c>
       <c r="C131">
         <v>78</v>
       </c>
       <c r="D131" t="str">
-        <v>104동</v>
+        <v>102동</v>
       </c>
       <c r="E131" t="str">
-        <v>5/17</v>
+        <v>16/17</v>
       </c>
       <c r="F131" t="str">
         <v>남동향</v>
@@ -3820,16 +3820,16 @@
         <v>동부</v>
       </c>
       <c r="B132" t="str">
-        <v>9억</v>
+        <v>8억 5,000</v>
       </c>
       <c r="C132">
         <v>78</v>
       </c>
       <c r="D132" t="str">
-        <v>102동</v>
+        <v>104동</v>
       </c>
       <c r="E132" t="str">
-        <v>16/17</v>
+        <v>5/17</v>
       </c>
       <c r="F132" t="str">
         <v>남동향</v>
@@ -4034,16 +4034,16 @@
         <v>78</v>
       </c>
       <c r="D140" t="str">
-        <v>101동</v>
+        <v>102동</v>
       </c>
       <c r="E140" t="str">
-        <v>고/17</v>
+        <v>저/17</v>
       </c>
       <c r="F140" t="str">
         <v>남동향</v>
       </c>
       <c r="G140" t="str">
-        <v>방3 계단식,올수리,전망, 전철역세권</v>
+        <v>입주협의거실확장 샤시일부교체 리모추진중 역세권 초중고인접 도서관 메디컬외</v>
       </c>
       <c r="H140" t="str">
         <v>naver</v>
@@ -4054,22 +4054,22 @@
         <v>동부</v>
       </c>
       <c r="B141" t="str">
-        <v>9억</v>
+        <v>9억 3,000</v>
       </c>
       <c r="C141">
         <v>78</v>
       </c>
       <c r="D141" t="str">
-        <v>106동</v>
+        <v>105동</v>
       </c>
       <c r="E141" t="str">
-        <v>7/17</v>
+        <v>중/17</v>
       </c>
       <c r="F141" t="str">
         <v>남동향</v>
       </c>
       <c r="G141" t="str">
-        <v>방3 계단식,주인거주,로얄층,수리,전철역세권</v>
+        <v>입주협의 방3  최근올수리 초중고인접 도서관 메디칼센터 역세권 공원인접</v>
       </c>
       <c r="H141" t="str">
         <v>naver</v>
@@ -4086,16 +4086,16 @@
         <v>78</v>
       </c>
       <c r="D142" t="str">
-        <v>102동</v>
+        <v>101동</v>
       </c>
       <c r="E142" t="str">
-        <v>저/17</v>
+        <v>고/17</v>
       </c>
       <c r="F142" t="str">
         <v>남동향</v>
       </c>
       <c r="G142" t="str">
-        <v>입주협의거실확장 샤시일부교체 리모추진중 역세권 초중고인접 도서관 메디컬외</v>
+        <v>방3 계단식,올수리,전망, 전철역세권</v>
       </c>
       <c r="H142" t="str">
         <v>naver</v>
@@ -4106,22 +4106,22 @@
         <v>동부</v>
       </c>
       <c r="B143" t="str">
-        <v>9억 3,000</v>
+        <v>9억</v>
       </c>
       <c r="C143">
         <v>78</v>
       </c>
       <c r="D143" t="str">
-        <v>105동</v>
+        <v>106동</v>
       </c>
       <c r="E143" t="str">
-        <v>중/17</v>
+        <v>7/17</v>
       </c>
       <c r="F143" t="str">
         <v>남동향</v>
       </c>
       <c r="G143" t="str">
-        <v>입주협의 방3  최근올수리 초중고인접 도서관 메디칼센터 역세권 공원인접</v>
+        <v>방3 계단식,주인거주,로얄층,수리,전철역세권</v>
       </c>
       <c r="H143" t="str">
         <v>naver</v>
@@ -4132,22 +4132,22 @@
         <v>동부</v>
       </c>
       <c r="B144" t="str">
-        <v>8억 5,000</v>
+        <v>8억 2,000</v>
       </c>
       <c r="C144">
         <v>78</v>
       </c>
       <c r="D144" t="str">
-        <v>104동</v>
+        <v>103동</v>
       </c>
       <c r="E144" t="str">
-        <v>3/17</v>
+        <v>17/17</v>
       </c>
       <c r="F144" t="str">
         <v>남동향</v>
       </c>
       <c r="G144" t="str">
-        <v>깨끗함, 기본상태, 주인거주 정상입주</v>
+        <v>깨끗함, 주인거주</v>
       </c>
       <c r="H144" t="str">
         <v>naver</v>
@@ -4158,22 +4158,22 @@
         <v>동부</v>
       </c>
       <c r="B145" t="str">
-        <v>8억 2,000</v>
+        <v>8억 5,000</v>
       </c>
       <c r="C145">
         <v>78</v>
       </c>
       <c r="D145" t="str">
-        <v>103동</v>
+        <v>104동</v>
       </c>
       <c r="E145" t="str">
-        <v>17/17</v>
+        <v>3/17</v>
       </c>
       <c r="F145" t="str">
         <v>남동향</v>
       </c>
       <c r="G145" t="str">
-        <v>깨끗함, 주인거주</v>
+        <v>깨끗함, 기본상태, 주인거주 정상입주</v>
       </c>
       <c r="H145" t="str">
         <v>naver</v>
@@ -4883,9 +4883,2193 @@
         <v>naver</v>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>동천마을현대홈타운1차</v>
+      </c>
+      <c r="B173" t="str">
+        <v>10억 9,000</v>
+      </c>
+      <c r="C173">
+        <v>122</v>
+      </c>
+      <c r="D173" t="str">
+        <v>104동</v>
+      </c>
+      <c r="E173" t="str">
+        <v>23/25</v>
+      </c>
+      <c r="F173" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G173" t="str">
+        <v>역세권 단지 탁트인 전망의 엘베 연결 로얄동 입주 정상 협의</v>
+      </c>
+      <c r="H173" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>동천마을현대홈타운1차</v>
+      </c>
+      <c r="B174" t="str">
+        <v>10억 9,000</v>
+      </c>
+      <c r="C174">
+        <v>122</v>
+      </c>
+      <c r="D174" t="str">
+        <v>103동</v>
+      </c>
+      <c r="E174" t="str">
+        <v>5/16</v>
+      </c>
+      <c r="F174" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G174" t="str">
+        <v>종일 밝은 정남향 올확장 깨끗관리 컨디션최고 동천역5분</v>
+      </c>
+      <c r="H174" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>동천마을현대홈타운1차</v>
+      </c>
+      <c r="B175" t="str">
+        <v>10억 9,000</v>
+      </c>
+      <c r="C175">
+        <v>122</v>
+      </c>
+      <c r="D175" t="str">
+        <v>103동</v>
+      </c>
+      <c r="E175" t="str">
+        <v>중/16</v>
+      </c>
+      <c r="F175" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G175" t="str">
+        <v>동천역5분, 남향, 거실확장, 입주협의가능, 부분수리되어 깨끗함</v>
+      </c>
+      <c r="H175" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>동천마을현대홈타운1차</v>
+      </c>
+      <c r="B176" t="str">
+        <v>10억 7,000</v>
+      </c>
+      <c r="C176">
+        <v>122</v>
+      </c>
+      <c r="D176" t="str">
+        <v>106동</v>
+      </c>
+      <c r="E176" t="str">
+        <v>저/16</v>
+      </c>
+      <c r="F176" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G176" t="str">
+        <v>동천역5분, 남향, 세안고매매, 올확장, 1층아님, 주차연결동</v>
+      </c>
+      <c r="H176" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>동천마을현대홈타운1차</v>
+      </c>
+      <c r="B177" t="str">
+        <v>12억</v>
+      </c>
+      <c r="C177">
+        <v>122</v>
+      </c>
+      <c r="D177" t="str">
+        <v>101동</v>
+      </c>
+      <c r="E177" t="str">
+        <v>8/25</v>
+      </c>
+      <c r="F177" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G177" t="str">
+        <v>37. 신분당선동천역 화이트톤올수리 확트인뷰 해 잘드는집 정남향 입주협</v>
+      </c>
+      <c r="H177" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>동천마을현대홈타운1차</v>
+      </c>
+      <c r="B178" t="str">
+        <v>11억</v>
+      </c>
+      <c r="C178">
+        <v>122</v>
+      </c>
+      <c r="D178" t="str">
+        <v>104동</v>
+      </c>
+      <c r="E178" t="str">
+        <v>6/25</v>
+      </c>
+      <c r="F178" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G178" t="str">
+        <v>동천역5분, 남향, 주방,욕실,도배,장판,탄성 등 수리됨, 가격조정가</v>
+      </c>
+      <c r="H178" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>동천마을현대홈타운1차</v>
+      </c>
+      <c r="B179" t="str">
+        <v>11억</v>
+      </c>
+      <c r="C179">
+        <v>122</v>
+      </c>
+      <c r="D179" t="str">
+        <v>106동</v>
+      </c>
+      <c r="E179" t="str">
+        <v>고/16</v>
+      </c>
+      <c r="F179" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G179" t="str">
+        <v>동천역5분, 남향, 로열동, 주차연결, 입주협의가능, 수리기간드림</v>
+      </c>
+      <c r="H179" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>동천마을현대홈타운1차</v>
+      </c>
+      <c r="B180" t="str">
+        <v>11억</v>
+      </c>
+      <c r="C180">
+        <v>122</v>
+      </c>
+      <c r="D180" t="str">
+        <v>104동</v>
+      </c>
+      <c r="E180" t="str">
+        <v>고/25</v>
+      </c>
+      <c r="F180" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G180" t="str">
+        <v>동천역5분, 남향, 화이트수리, 비확장, 입주협의가능</v>
+      </c>
+      <c r="H180" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>동천마을현대홈타운1차</v>
+      </c>
+      <c r="B181" t="str">
+        <v>11억 9,000</v>
+      </c>
+      <c r="C181">
+        <v>122</v>
+      </c>
+      <c r="D181" t="str">
+        <v>101동</v>
+      </c>
+      <c r="E181" t="str">
+        <v>저/25</v>
+      </c>
+      <c r="F181" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G181" t="str">
+        <v>H. 햇살가득 따뜻한 남향 올확장 화이트수리 관리최상 동천역</v>
+      </c>
+      <c r="H181" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>동천마을현대홈타운1차</v>
+      </c>
+      <c r="B182" t="str">
+        <v>11억 5,000</v>
+      </c>
+      <c r="C182">
+        <v>122</v>
+      </c>
+      <c r="D182" t="str">
+        <v>105동</v>
+      </c>
+      <c r="E182" t="str">
+        <v>중/16</v>
+      </c>
+      <c r="F182" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G182" t="str">
+        <v>동천역5분, 남향, 전망굿, 로열동, 7월이후입주 협의가능</v>
+      </c>
+      <c r="H182" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>동천마을현대홈타운1차</v>
+      </c>
+      <c r="B183" t="str">
+        <v>11억 7,000</v>
+      </c>
+      <c r="C183">
+        <v>122</v>
+      </c>
+      <c r="D183" t="str">
+        <v>107동</v>
+      </c>
+      <c r="E183" t="str">
+        <v>고/23</v>
+      </c>
+      <c r="F183" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G183" t="str">
+        <v>올수리. 2027.8월 임대안고, 전망좋은집, 동천역 도보3분</v>
+      </c>
+      <c r="H183" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>동천마을현대홈타운1차</v>
+      </c>
+      <c r="B184" t="str">
+        <v>11억 7,000</v>
+      </c>
+      <c r="C184">
+        <v>122</v>
+      </c>
+      <c r="D184" t="str">
+        <v>107동</v>
+      </c>
+      <c r="E184" t="str">
+        <v>18/23</v>
+      </c>
+      <c r="F184" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G184" t="str">
+        <v>2027년 8월 월세안고, 전망이 좋은집, 동천역 도보5분거리,수리된집</v>
+      </c>
+      <c r="H184" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>동천마을현대홈타운1차</v>
+      </c>
+      <c r="B185" t="str">
+        <v>10억 9,000</v>
+      </c>
+      <c r="C185" t="str">
+        <v>122</v>
+      </c>
+      <c r="D185" t="str">
+        <v>104동</v>
+      </c>
+      <c r="E185" t="str">
+        <v>고층</v>
+      </c>
+      <c r="F185" t="str">
+        <v/>
+      </c>
+      <c r="G185" t="str">
+        <v>햇살가득남향 특전망 로얄동 올수리 컨디션최고 엘베연결</v>
+      </c>
+      <c r="H185" t="str">
+        <v>asil</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>동천마을현대홈타운1차</v>
+      </c>
+      <c r="B186" t="str">
+        <v>10억 7,000</v>
+      </c>
+      <c r="C186" t="str">
+        <v>122</v>
+      </c>
+      <c r="D186" t="str">
+        <v>106동</v>
+      </c>
+      <c r="E186" t="str">
+        <v>고층</v>
+      </c>
+      <c r="F186" t="str">
+        <v/>
+      </c>
+      <c r="G186" t="str">
+        <v>동천역5분, 남향, 로열동, 주차연결, 입주협의가능, 수리기간드림</v>
+      </c>
+      <c r="H186" t="str">
+        <v>asil</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>동천마을현대홈타운1차</v>
+      </c>
+      <c r="B187" t="str">
+        <v>11억</v>
+      </c>
+      <c r="C187" t="str">
+        <v>122</v>
+      </c>
+      <c r="D187" t="str">
+        <v>104동</v>
+      </c>
+      <c r="E187" t="str">
+        <v>23층</v>
+      </c>
+      <c r="F187" t="str">
+        <v/>
+      </c>
+      <c r="G187" t="str">
+        <v>동천역5분, 남향, 전망굿, 부분수리, 주차연결동, 입주협의가능</v>
+      </c>
+      <c r="H187" t="str">
+        <v>asil</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>동천마을현대홈타운2차</v>
+      </c>
+      <c r="B188" t="str">
+        <v>11억</v>
+      </c>
+      <c r="C188">
+        <v>122</v>
+      </c>
+      <c r="D188" t="str">
+        <v>204동</v>
+      </c>
+      <c r="E188" t="str">
+        <v>20/25</v>
+      </c>
+      <c r="F188" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G188" t="str">
+        <v>남향 조용한단지전망 햇볕짱 부분수리 싱크대,도기교체 세안고</v>
+      </c>
+      <c r="H188" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>동천마을현대홈타운2차</v>
+      </c>
+      <c r="B189" t="str">
+        <v>10억</v>
+      </c>
+      <c r="C189">
+        <v>81</v>
+      </c>
+      <c r="D189" t="str">
+        <v>201동</v>
+      </c>
+      <c r="E189" t="str">
+        <v>5/25</v>
+      </c>
+      <c r="F189" t="str">
+        <v>동향</v>
+      </c>
+      <c r="G189" t="str">
+        <v>o.최근화이트특올수리.샤시교체. 트인전망시원함. 조용한입구동,신혼추천</v>
+      </c>
+      <c r="H189" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>동천마을현대홈타운2차</v>
+      </c>
+      <c r="B190" t="str">
+        <v>10억 5,000</v>
+      </c>
+      <c r="C190">
+        <v>122</v>
+      </c>
+      <c r="D190" t="str">
+        <v>204동</v>
+      </c>
+      <c r="E190" t="str">
+        <v>6/25</v>
+      </c>
+      <c r="F190" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G190" t="str">
+        <v>따스한남향 조용한단지전망 동천역인접동 동천역세권 세안고</v>
+      </c>
+      <c r="H190" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>동천마을현대홈타운2차</v>
+      </c>
+      <c r="B191" t="str">
+        <v>10억 3,000</v>
+      </c>
+      <c r="C191">
+        <v>122</v>
+      </c>
+      <c r="D191" t="str">
+        <v>204동</v>
+      </c>
+      <c r="E191" t="str">
+        <v>1/25</v>
+      </c>
+      <c r="F191" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G191" t="str">
+        <v>남향, 확장, 부분수리, 깨끗, 동천역가까운동, 입지좋은대단지</v>
+      </c>
+      <c r="H191" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>동천마을현대홈타운2차</v>
+      </c>
+      <c r="B192" t="str">
+        <v>9억</v>
+      </c>
+      <c r="C192">
+        <v>81</v>
+      </c>
+      <c r="D192" t="str">
+        <v>201동</v>
+      </c>
+      <c r="E192" t="str">
+        <v>2/25</v>
+      </c>
+      <c r="F192" t="str">
+        <v>동향</v>
+      </c>
+      <c r="G192" t="str">
+        <v>대단지아파트 동천역근접동  기본형 9월초이후 교통편리</v>
+      </c>
+      <c r="H192" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>동천마을현대홈타운2차</v>
+      </c>
+      <c r="B193" t="str">
+        <v>11억</v>
+      </c>
+      <c r="C193">
+        <v>122</v>
+      </c>
+      <c r="D193" t="str">
+        <v>206동</v>
+      </c>
+      <c r="E193" t="str">
+        <v>중/25</v>
+      </c>
+      <c r="F193" t="str">
+        <v>동향</v>
+      </c>
+      <c r="G193" t="str">
+        <v>탁트인전망 채광굿 잘관리된집 동천역세권 입주협의</v>
+      </c>
+      <c r="H193" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>동천마을현대홈타운2차</v>
+      </c>
+      <c r="B194" t="str">
+        <v>11억</v>
+      </c>
+      <c r="C194">
+        <v>122</v>
+      </c>
+      <c r="D194" t="str">
+        <v>208동</v>
+      </c>
+      <c r="E194" t="str">
+        <v>고/25</v>
+      </c>
+      <c r="F194" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G194" t="str">
+        <v>남향 정상입주 로얄동 환상전망 채광굿 기본형</v>
+      </c>
+      <c r="H194" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>동천마을현대홈타운2차</v>
+      </c>
+      <c r="B195" t="str">
+        <v>10억 6,000</v>
+      </c>
+      <c r="C195">
+        <v>122</v>
+      </c>
+      <c r="D195" t="str">
+        <v>206동</v>
+      </c>
+      <c r="E195" t="str">
+        <v>중/25</v>
+      </c>
+      <c r="F195" t="str">
+        <v>동향</v>
+      </c>
+      <c r="G195" t="str">
+        <v>올확장 시원한전망 관리가 잘된집  동천역세권 입주협의</v>
+      </c>
+      <c r="H195" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>동천마을현대홈타운2차</v>
+      </c>
+      <c r="B196" t="str">
+        <v>11억 1,000</v>
+      </c>
+      <c r="C196">
+        <v>122</v>
+      </c>
+      <c r="D196" t="str">
+        <v>209동</v>
+      </c>
+      <c r="E196" t="str">
+        <v>고/25</v>
+      </c>
+      <c r="F196" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G196" t="str">
+        <v>따스한남향 로얄동 관리가잘된집 싱크대교체 채광굿 입주협의</v>
+      </c>
+      <c r="H196" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>동천마을현대홈타운2차</v>
+      </c>
+      <c r="B197" t="str">
+        <v>9억 9,000</v>
+      </c>
+      <c r="C197">
+        <v>122</v>
+      </c>
+      <c r="D197" t="str">
+        <v>202동</v>
+      </c>
+      <c r="E197" t="str">
+        <v>저/24</v>
+      </c>
+      <c r="F197" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G197" t="str">
+        <v>H.햇살가득 따뜻한 남향 거실확장 부분수리 깔끔해요 동천역 세안고</v>
+      </c>
+      <c r="H197" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>동천마을현대홈타운2차</v>
+      </c>
+      <c r="B198" t="str">
+        <v>10억 8,000</v>
+      </c>
+      <c r="C198">
+        <v>122</v>
+      </c>
+      <c r="D198" t="str">
+        <v>202동</v>
+      </c>
+      <c r="E198" t="str">
+        <v>고/24</v>
+      </c>
+      <c r="F198" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G198" t="str">
+        <v>H. 좋은집 밝고환한남향 관리최상 채광굿 주차편리 학세권 동천역</v>
+      </c>
+      <c r="H198" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>동천마을현대홈타운2차</v>
+      </c>
+      <c r="B199" t="str">
+        <v>11억 5,000</v>
+      </c>
+      <c r="C199">
+        <v>122</v>
+      </c>
+      <c r="D199" t="str">
+        <v>207동</v>
+      </c>
+      <c r="E199" t="str">
+        <v>고/23</v>
+      </c>
+      <c r="F199" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G199" t="str">
+        <v>따스한남향 로얄동 관리가잘된집 화이트수리 채광굿 입주협의</v>
+      </c>
+      <c r="H199" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>동천마을현대홈타운2차</v>
+      </c>
+      <c r="B200" t="str">
+        <v>11억 3,000</v>
+      </c>
+      <c r="C200">
+        <v>122</v>
+      </c>
+      <c r="D200" t="str">
+        <v>207동</v>
+      </c>
+      <c r="E200" t="str">
+        <v>6/23</v>
+      </c>
+      <c r="F200" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G200" t="str">
+        <v>로얄동 부분수리 채광굿 깔끔관리 정상입주</v>
+      </c>
+      <c r="H200" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>동천마을현대홈타운2차</v>
+      </c>
+      <c r="B201" t="str">
+        <v>10억 5,000</v>
+      </c>
+      <c r="C201">
+        <v>122</v>
+      </c>
+      <c r="D201" t="str">
+        <v>204동</v>
+      </c>
+      <c r="E201" t="str">
+        <v>2/25</v>
+      </c>
+      <c r="F201" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G201" t="str">
+        <v>남향 확장형 화이트올수리 싱크대욕실ok   세안고</v>
+      </c>
+      <c r="H201" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>동천마을현대홈타운2차</v>
+      </c>
+      <c r="B202" t="str">
+        <v>11억 5,000</v>
+      </c>
+      <c r="C202">
+        <v>122</v>
+      </c>
+      <c r="D202" t="str">
+        <v>208동</v>
+      </c>
+      <c r="E202" t="str">
+        <v>고/25</v>
+      </c>
+      <c r="F202" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G202" t="str">
+        <v>로얄동층 굿라인 화이트올수리 환상전망 샷시교체 입주협의</v>
+      </c>
+      <c r="H202" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B203" t="str">
+        <v>11억 5,000</v>
+      </c>
+      <c r="C203">
+        <v>108</v>
+      </c>
+      <c r="D203" t="str">
+        <v>511동</v>
+      </c>
+      <c r="E203" t="str">
+        <v>22/24</v>
+      </c>
+      <c r="F203" t="str">
+        <v>남동향</v>
+      </c>
+      <c r="G203" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="H203" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B204" t="str">
+        <v>13억</v>
+      </c>
+      <c r="C204">
+        <v>108</v>
+      </c>
+      <c r="D204" t="str">
+        <v>514동</v>
+      </c>
+      <c r="E204" t="str">
+        <v>12/25</v>
+      </c>
+      <c r="F204" t="str">
+        <v>남동향</v>
+      </c>
+      <c r="G204" t="str">
+        <v>로얄동,프리미엄확장,트인전망,깔끔</v>
+      </c>
+      <c r="H204" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B205" t="str">
+        <v>12억 3,000</v>
+      </c>
+      <c r="C205">
+        <v>108</v>
+      </c>
+      <c r="D205" t="str">
+        <v>509동</v>
+      </c>
+      <c r="E205" t="str">
+        <v>20/25</v>
+      </c>
+      <c r="F205" t="str">
+        <v>남서향</v>
+      </c>
+      <c r="G205" t="str">
+        <v>입구동. 확장형.부분수리  컨디션 아주 좋음. 햇빛가득한 집.</v>
+      </c>
+      <c r="H205" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B206" t="str">
+        <v>12억 5,000</v>
+      </c>
+      <c r="C206">
+        <v>108</v>
+      </c>
+      <c r="D206" t="str">
+        <v>502동</v>
+      </c>
+      <c r="E206" t="str">
+        <v>10/21</v>
+      </c>
+      <c r="F206" t="str">
+        <v>남동향</v>
+      </c>
+      <c r="G206" t="str">
+        <v>앞트인 시원뷰.프리미엄확장.상태최상.입구동산책로근접,동천역도보권.생활편리</v>
+      </c>
+      <c r="H206" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B207" t="str">
+        <v>12억 2,000</v>
+      </c>
+      <c r="C207">
+        <v>108</v>
+      </c>
+      <c r="D207" t="str">
+        <v>514동</v>
+      </c>
+      <c r="E207" t="str">
+        <v>고/25</v>
+      </c>
+      <c r="F207" t="str">
+        <v>남동향</v>
+      </c>
+      <c r="G207" t="str">
+        <v>트인뷰,프리미엄확장형, 선호동,선호층,채광,환기좋음. 세안고</v>
+      </c>
+      <c r="H207" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B208" t="str">
+        <v>12억 5,000</v>
+      </c>
+      <c r="C208">
+        <v>108</v>
+      </c>
+      <c r="D208" t="str">
+        <v>509동</v>
+      </c>
+      <c r="E208" t="str">
+        <v>22/25</v>
+      </c>
+      <c r="F208" t="str">
+        <v>남서향</v>
+      </c>
+      <c r="G208" t="str">
+        <v>강추 눈부시게예쁜집 3년전특올수리올확장 시스템에어컨4대 동간거리넓은광장뷰</v>
+      </c>
+      <c r="H208" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B209" t="str">
+        <v>12억</v>
+      </c>
+      <c r="C209">
+        <v>108</v>
+      </c>
+      <c r="D209" t="str">
+        <v>514동</v>
+      </c>
+      <c r="E209" t="str">
+        <v>6/25</v>
+      </c>
+      <c r="F209" t="str">
+        <v>남동향</v>
+      </c>
+      <c r="G209" t="str">
+        <v>0318966776 수리됨입주협의전망짱</v>
+      </c>
+      <c r="H209" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B210" t="str">
+        <v>13억</v>
+      </c>
+      <c r="C210">
+        <v>108</v>
+      </c>
+      <c r="D210" t="str">
+        <v>512동</v>
+      </c>
+      <c r="E210" t="str">
+        <v>중/23</v>
+      </c>
+      <c r="F210" t="str">
+        <v>남동향</v>
+      </c>
+      <c r="G210" t="str">
+        <v>o.최근특올수리,올확장,화이트톤,탁트인전망,최로얄동층,상태최상,정상입주</v>
+      </c>
+      <c r="H210" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B211" t="str">
+        <v>12억 4,000</v>
+      </c>
+      <c r="C211">
+        <v>108</v>
+      </c>
+      <c r="D211" t="str">
+        <v>506동</v>
+      </c>
+      <c r="E211" t="str">
+        <v>22/25</v>
+      </c>
+      <c r="F211" t="str">
+        <v>남동향</v>
+      </c>
+      <c r="G211" t="str">
+        <v>프리미엄확장형, 빠른입주가능, 동천역세권</v>
+      </c>
+      <c r="H211" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B212" t="str">
+        <v>13억</v>
+      </c>
+      <c r="C212">
+        <v>108</v>
+      </c>
+      <c r="D212" t="str">
+        <v>514동</v>
+      </c>
+      <c r="E212" t="str">
+        <v>10/25</v>
+      </c>
+      <c r="F212" t="str">
+        <v>남동향</v>
+      </c>
+      <c r="G212" t="str">
+        <v>0318966776 최근확장올수리됨입주협의가능.</v>
+      </c>
+      <c r="H212" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B213" t="str">
+        <v>13억</v>
+      </c>
+      <c r="C213">
+        <v>108</v>
+      </c>
+      <c r="D213" t="str">
+        <v>512동</v>
+      </c>
+      <c r="E213" t="str">
+        <v>저/23</v>
+      </c>
+      <c r="F213" t="str">
+        <v>남서향</v>
+      </c>
+      <c r="G213" t="str">
+        <v>로얄동,로얄층,특올수리,특전망</v>
+      </c>
+      <c r="H213" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B214" t="str">
+        <v>12억 2,000</v>
+      </c>
+      <c r="C214">
+        <v>108</v>
+      </c>
+      <c r="D214" t="str">
+        <v>512동</v>
+      </c>
+      <c r="E214" t="str">
+        <v>중/23</v>
+      </c>
+      <c r="F214" t="str">
+        <v>남서향</v>
+      </c>
+      <c r="G214" t="str">
+        <v>로얄동 확장 깨끗  세안고</v>
+      </c>
+      <c r="H214" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B215" t="str">
+        <v>11억 7,000</v>
+      </c>
+      <c r="C215">
+        <v>108</v>
+      </c>
+      <c r="D215" t="str">
+        <v>510동</v>
+      </c>
+      <c r="E215" t="str">
+        <v>저/24</v>
+      </c>
+      <c r="F215" t="str">
+        <v>남동향</v>
+      </c>
+      <c r="G215" t="str">
+        <v>프리미엄확장.정상입주.동천역 도보 9분. 전자계약 가능</v>
+      </c>
+      <c r="H215" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B216" t="str">
+        <v>12억 3,000</v>
+      </c>
+      <c r="C216">
+        <v>108</v>
+      </c>
+      <c r="D216" t="str">
+        <v>515동</v>
+      </c>
+      <c r="E216" t="str">
+        <v>저/23</v>
+      </c>
+      <c r="F216" t="str">
+        <v>북서향</v>
+      </c>
+      <c r="G216" t="str">
+        <v>전체 확장 화이트올수리 입주가 탁트인정원전망 라인굿</v>
+      </c>
+      <c r="H216" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B217" t="str">
+        <v>12억 7,000</v>
+      </c>
+      <c r="C217">
+        <v>108</v>
+      </c>
+      <c r="D217" t="str">
+        <v>503동</v>
+      </c>
+      <c r="E217" t="str">
+        <v>25/25</v>
+      </c>
+      <c r="F217" t="str">
+        <v>남동향</v>
+      </c>
+      <c r="G217" t="str">
+        <v>o성실o프리미엄확장.전망굿탑층.실입주.로얄동.주인관리깨끗.동천역도보</v>
+      </c>
+      <c r="H217" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B218" t="str">
+        <v>12억</v>
+      </c>
+      <c r="C218">
+        <v>108</v>
+      </c>
+      <c r="D218" t="str">
+        <v>504동</v>
+      </c>
+      <c r="E218" t="str">
+        <v>2/25</v>
+      </c>
+      <c r="F218" t="str">
+        <v>남서향</v>
+      </c>
+      <c r="G218" t="str">
+        <v>0318966776 전망아주좋음확장수리잘됨</v>
+      </c>
+      <c r="H218" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B219" t="str">
+        <v>12억 2,000</v>
+      </c>
+      <c r="C219">
+        <v>108</v>
+      </c>
+      <c r="D219" t="str">
+        <v>515동</v>
+      </c>
+      <c r="E219" t="str">
+        <v>중/23</v>
+      </c>
+      <c r="F219" t="str">
+        <v>남서향</v>
+      </c>
+      <c r="G219" t="str">
+        <v>로얄동층 트인전망예뻐요 확장형 동천역과상가인접이라서 편해요</v>
+      </c>
+      <c r="H219" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B220" t="str">
+        <v>11억 1,000</v>
+      </c>
+      <c r="C220">
+        <v>108</v>
+      </c>
+      <c r="D220" t="str">
+        <v>501동</v>
+      </c>
+      <c r="E220" t="str">
+        <v>저/25</v>
+      </c>
+      <c r="F220" t="str">
+        <v>남동향</v>
+      </c>
+      <c r="G220" t="str">
+        <v>로얄동 출입동 입주협의가 깨끗 생활편리 동천역도보편리</v>
+      </c>
+      <c r="H220" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B221" t="str">
+        <v>12억 9,000</v>
+      </c>
+      <c r="C221">
+        <v>108</v>
+      </c>
+      <c r="D221" t="str">
+        <v>509동</v>
+      </c>
+      <c r="E221" t="str">
+        <v>고/25</v>
+      </c>
+      <c r="F221" t="str">
+        <v>남서향</v>
+      </c>
+      <c r="G221" t="str">
+        <v>특올수리 채광좋은고층 생활편리 로얄동 입주협의 소유주직접의뢰</v>
+      </c>
+      <c r="H221" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B222" t="str">
+        <v>12억 3,000</v>
+      </c>
+      <c r="C222">
+        <v>108</v>
+      </c>
+      <c r="D222" t="str">
+        <v>505동</v>
+      </c>
+      <c r="E222" t="str">
+        <v>고/25</v>
+      </c>
+      <c r="F222" t="str">
+        <v>남동향</v>
+      </c>
+      <c r="G222" t="str">
+        <v>확장형 채광좋은 관리잘된집 조율가 동천역도보10분</v>
+      </c>
+      <c r="H222" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B223" t="str">
+        <v>12억</v>
+      </c>
+      <c r="C223">
+        <v>108</v>
+      </c>
+      <c r="D223" t="str">
+        <v>504동</v>
+      </c>
+      <c r="E223" t="str">
+        <v>중/25</v>
+      </c>
+      <c r="F223" t="str">
+        <v>남서향</v>
+      </c>
+      <c r="G223" t="str">
+        <v>전망 좋은 로얄동,올확장,입주일 협의 가</v>
+      </c>
+      <c r="H223" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B224" t="str">
+        <v>12억 2,000</v>
+      </c>
+      <c r="C224">
+        <v>108</v>
+      </c>
+      <c r="D224" t="str">
+        <v>502동</v>
+      </c>
+      <c r="E224" t="str">
+        <v>중/21</v>
+      </c>
+      <c r="F224" t="str">
+        <v>남동향</v>
+      </c>
+      <c r="G224" t="str">
+        <v>올수리 프리미엄확장 로얄동층 트인불곡산전망 출입동생활편리</v>
+      </c>
+      <c r="H224" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B225" t="str">
+        <v>12억</v>
+      </c>
+      <c r="C225">
+        <v>108</v>
+      </c>
+      <c r="D225" t="str">
+        <v>509동</v>
+      </c>
+      <c r="E225" t="str">
+        <v>7/25</v>
+      </c>
+      <c r="F225" t="str">
+        <v>남서향</v>
+      </c>
+      <c r="G225" t="str">
+        <v>세안고, 파크뷰, 동천초, 산책로굿, 조용</v>
+      </c>
+      <c r="H225" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B226" t="str">
+        <v>12억 5,000</v>
+      </c>
+      <c r="C226">
+        <v>108</v>
+      </c>
+      <c r="D226" t="str">
+        <v>503동</v>
+      </c>
+      <c r="E226" t="str">
+        <v>중/25</v>
+      </c>
+      <c r="F226" t="str">
+        <v>남동향</v>
+      </c>
+      <c r="G226" t="str">
+        <v>로얄동층 트인불곡산전망 확장 화이트수리 관리최상 동천역도보편리</v>
+      </c>
+      <c r="H226" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B227" t="str">
+        <v>12억 3,000</v>
+      </c>
+      <c r="C227">
+        <v>108</v>
+      </c>
+      <c r="D227" t="str">
+        <v>515동</v>
+      </c>
+      <c r="E227" t="str">
+        <v>중/23</v>
+      </c>
+      <c r="F227" t="str">
+        <v>남서향</v>
+      </c>
+      <c r="G227" t="str">
+        <v>올확장  입주가능 탁트인뷰 채광굿</v>
+      </c>
+      <c r="H227" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B228" t="str">
+        <v>12억</v>
+      </c>
+      <c r="C228">
+        <v>108</v>
+      </c>
+      <c r="D228" t="str">
+        <v>505동</v>
+      </c>
+      <c r="E228" t="str">
+        <v>고/25</v>
+      </c>
+      <c r="F228" t="str">
+        <v>남동향</v>
+      </c>
+      <c r="G228" t="str">
+        <v>프리미엄확장,밝고 깔끔,학교까까운 동</v>
+      </c>
+      <c r="H228" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B229" t="str">
+        <v>13억</v>
+      </c>
+      <c r="C229">
+        <v>108</v>
+      </c>
+      <c r="D229" t="str">
+        <v>514동</v>
+      </c>
+      <c r="E229" t="str">
+        <v>중/25</v>
+      </c>
+      <c r="F229" t="str">
+        <v/>
+      </c>
+      <c r="G229" t="str">
+        <v>로얄동,트인뷰,프리미엄확장,깔끔관리</v>
+      </c>
+      <c r="H229" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B230" t="str">
+        <v>12억 4,000</v>
+      </c>
+      <c r="C230" t="str">
+        <v>108</v>
+      </c>
+      <c r="D230" t="str">
+        <v>506동</v>
+      </c>
+      <c r="E230" t="str">
+        <v>고층</v>
+      </c>
+      <c r="F230" t="str">
+        <v/>
+      </c>
+      <c r="G230" t="str">
+        <v>o성실o전체확장형.해잘들어밝아요.LED교체.깨끗해요.빠른입주가능</v>
+      </c>
+      <c r="H230" t="str">
+        <v>asil</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B231" t="str">
+        <v>11억 2,000</v>
+      </c>
+      <c r="C231" t="str">
+        <v>108</v>
+      </c>
+      <c r="D231" t="str">
+        <v>506동</v>
+      </c>
+      <c r="E231" t="str">
+        <v>7층</v>
+      </c>
+      <c r="F231" t="str">
+        <v/>
+      </c>
+      <c r="G231" t="str">
+        <v>급매, 확장형, 공원전망 , 입주일자 협의가능</v>
+      </c>
+      <c r="H231" t="str">
+        <v>asil</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B232" t="str">
+        <v>11억 5,000</v>
+      </c>
+      <c r="C232" t="str">
+        <v>108</v>
+      </c>
+      <c r="D232" t="str">
+        <v>511동</v>
+      </c>
+      <c r="E232" t="str">
+        <v>고층</v>
+      </c>
+      <c r="F232" t="str">
+        <v/>
+      </c>
+      <c r="G232" t="str">
+        <v>o.세안고27.3.27입주,탁트인전망,올확장,최근올수리,관리최상</v>
+      </c>
+      <c r="H232" t="str">
+        <v>asil</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B233" t="str">
+        <v>12억 5,000</v>
+      </c>
+      <c r="C233" t="str">
+        <v>108</v>
+      </c>
+      <c r="D233" t="str">
+        <v>503동</v>
+      </c>
+      <c r="E233" t="str">
+        <v>25층</v>
+      </c>
+      <c r="F233" t="str">
+        <v/>
+      </c>
+      <c r="G233" t="str">
+        <v>탁트인로얄동 환상전망 프리미엄확장 상권교통편리한입구동 대단지</v>
+      </c>
+      <c r="H233" t="str">
+        <v>asil</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>동천디이스트</v>
+      </c>
+      <c r="B234" t="str">
+        <v>12억 5,000</v>
+      </c>
+      <c r="C234" t="str">
+        <v>108</v>
+      </c>
+      <c r="D234" t="str">
+        <v>502동</v>
+      </c>
+      <c r="E234" t="str">
+        <v>중층</v>
+      </c>
+      <c r="F234" t="str">
+        <v/>
+      </c>
+      <c r="G234" t="str">
+        <v>로얄동층 완전트인뷰 프리미엄확장 입주협의가 출입동 동천역도보편리</v>
+      </c>
+      <c r="H234" t="str">
+        <v>asil</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>써니벨리</v>
+      </c>
+      <c r="B235" t="str">
+        <v>9억 3,000</v>
+      </c>
+      <c r="C235">
+        <v>92</v>
+      </c>
+      <c r="D235" t="str">
+        <v>106동</v>
+      </c>
+      <c r="E235" t="str">
+        <v>1/19</v>
+      </c>
+      <c r="F235" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G235" t="str">
+        <v>정상,깨끗하고 일부수리에 전망굿 단지내초등학교 신분당선 동천역10분</v>
+      </c>
+      <c r="H235" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>써니벨리</v>
+      </c>
+      <c r="B236" t="str">
+        <v>11억 2,000</v>
+      </c>
+      <c r="C236">
+        <v>109</v>
+      </c>
+      <c r="D236" t="str">
+        <v>107동</v>
+      </c>
+      <c r="E236" t="str">
+        <v>7/18</v>
+      </c>
+      <c r="F236" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G236" t="str">
+        <v>추천매물 로얄동 앞트인전망 결로 곰팡이없이 관리최상</v>
+      </c>
+      <c r="H236" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>써니벨리</v>
+      </c>
+      <c r="B237" t="str">
+        <v>10억</v>
+      </c>
+      <c r="C237">
+        <v>92</v>
+      </c>
+      <c r="D237" t="str">
+        <v>101동</v>
+      </c>
+      <c r="E237" t="str">
+        <v>13/15</v>
+      </c>
+      <c r="F237" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G237" t="str">
+        <v>28. 동천역 손곡초중 남향 방3화2 현재 세입자거주중 월세안고매매</v>
+      </c>
+      <c r="H237" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>써니벨리</v>
+      </c>
+      <c r="B238" t="str">
+        <v>10억 3,000</v>
+      </c>
+      <c r="C238">
+        <v>109</v>
+      </c>
+      <c r="D238" t="str">
+        <v>103동</v>
+      </c>
+      <c r="E238" t="str">
+        <v>1/19</v>
+      </c>
+      <c r="F238" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G238" t="str">
+        <v>초품아,방2확장 화이트수리,주인거주,강남판교 출퇴근 용이</v>
+      </c>
+      <c r="H238" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>써니벨리</v>
+      </c>
+      <c r="B239" t="str">
+        <v>11억</v>
+      </c>
+      <c r="C239">
+        <v>109</v>
+      </c>
+      <c r="D239" t="str">
+        <v>104동</v>
+      </c>
+      <c r="E239" t="str">
+        <v>7/19</v>
+      </c>
+      <c r="F239" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G239" t="str">
+        <v>로얄동 급매 짧은세안고</v>
+      </c>
+      <c r="H239" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>써니벨리</v>
+      </c>
+      <c r="B240" t="str">
+        <v>10억</v>
+      </c>
+      <c r="C240">
+        <v>92</v>
+      </c>
+      <c r="D240" t="str">
+        <v>106동</v>
+      </c>
+      <c r="E240" t="str">
+        <v>18/19</v>
+      </c>
+      <c r="F240" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G240" t="str">
+        <v>귀한매물 올확장 수리 전망트임</v>
+      </c>
+      <c r="H240" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>써니벨리</v>
+      </c>
+      <c r="B241" t="str">
+        <v>10억 3,000</v>
+      </c>
+      <c r="C241">
+        <v>109</v>
+      </c>
+      <c r="D241" t="str">
+        <v>105동</v>
+      </c>
+      <c r="E241" t="str">
+        <v>2/19</v>
+      </c>
+      <c r="F241" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G241" t="str">
+        <v>로얄동 5.1억 전세안고 매매 초품아 잔금일협의</v>
+      </c>
+      <c r="H241" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>써니벨리</v>
+      </c>
+      <c r="B242" t="str">
+        <v>10억</v>
+      </c>
+      <c r="C242">
+        <v>92</v>
+      </c>
+      <c r="D242" t="str">
+        <v>106동</v>
+      </c>
+      <c r="E242" t="str">
+        <v>고/19</v>
+      </c>
+      <c r="F242" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G242" t="str">
+        <v>정상,깨끗하고 전망굿 단지내초등학교 신분당선 동천역10분</v>
+      </c>
+      <c r="H242" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>써니벨리</v>
+      </c>
+      <c r="B243" t="str">
+        <v>11억 5,000</v>
+      </c>
+      <c r="C243">
+        <v>109</v>
+      </c>
+      <c r="D243" t="str">
+        <v>107동</v>
+      </c>
+      <c r="E243" t="str">
+        <v>17/18</v>
+      </c>
+      <c r="F243" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G243" t="str">
+        <v>로얄동 전망최고 수리됨</v>
+      </c>
+      <c r="H243" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>써니벨리</v>
+      </c>
+      <c r="B244" t="str">
+        <v>10억</v>
+      </c>
+      <c r="C244">
+        <v>109</v>
+      </c>
+      <c r="D244" t="str">
+        <v>105동</v>
+      </c>
+      <c r="E244" t="str">
+        <v>1/19</v>
+      </c>
+      <c r="F244" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G244" t="str">
+        <v>따스한남향 방확장 주인거주 채광굿 깔끔관리</v>
+      </c>
+      <c r="H244" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>써니벨리</v>
+      </c>
+      <c r="B245" t="str">
+        <v>10억 2,000</v>
+      </c>
+      <c r="C245">
+        <v>109</v>
+      </c>
+      <c r="D245" t="str">
+        <v>102동</v>
+      </c>
+      <c r="E245" t="str">
+        <v>3/14</v>
+      </c>
+      <c r="F245" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G245" t="str">
+        <v>남향 확장 세안고</v>
+      </c>
+      <c r="H245" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>성동마을강남</v>
+      </c>
+      <c r="B246" t="str">
+        <v>13억</v>
+      </c>
+      <c r="C246">
+        <v>163</v>
+      </c>
+      <c r="D246" t="str">
+        <v>107동</v>
+      </c>
+      <c r="E246" t="str">
+        <v>15/18</v>
+      </c>
+      <c r="F246" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G246" t="str">
+        <v>강추,49형,로얄동,화이트올수리,깨끗한집.초역세권,세안고다주택자</v>
+      </c>
+      <c r="H246" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>성동마을강남</v>
+      </c>
+      <c r="B247" t="str">
+        <v>14억 5,000</v>
+      </c>
+      <c r="C247">
+        <v>163</v>
+      </c>
+      <c r="D247" t="str">
+        <v>107동</v>
+      </c>
+      <c r="E247" t="str">
+        <v>6/18</v>
+      </c>
+      <c r="F247" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G247" t="str">
+        <v>로얄동 트인전망  초역세권 생활권좋음 세안고</v>
+      </c>
+      <c r="H247" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>성동마을강남</v>
+      </c>
+      <c r="B248" t="str">
+        <v>14억 3,000</v>
+      </c>
+      <c r="C248">
+        <v>195</v>
+      </c>
+      <c r="D248" t="str">
+        <v>101동</v>
+      </c>
+      <c r="E248" t="str">
+        <v>18/18</v>
+      </c>
+      <c r="F248" t="str">
+        <v>남서향</v>
+      </c>
+      <c r="G248" t="str">
+        <v>입구동 전망굿 초역세권 화장실2수리</v>
+      </c>
+      <c r="H248" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>성동마을강남</v>
+      </c>
+      <c r="B249" t="str">
+        <v>14억 5,000</v>
+      </c>
+      <c r="C249">
+        <v>163</v>
+      </c>
+      <c r="D249" t="str">
+        <v>105동</v>
+      </c>
+      <c r="E249" t="str">
+        <v>중/18</v>
+      </c>
+      <c r="F249" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G249" t="str">
+        <v>샷시포함특올수리 성복역세권 생활편리 학군최고</v>
+      </c>
+      <c r="H249" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>성동마을강남</v>
+      </c>
+      <c r="B250" t="str">
+        <v>12억</v>
+      </c>
+      <c r="C250">
+        <v>109</v>
+      </c>
+      <c r="D250" t="str">
+        <v>103동</v>
+      </c>
+      <c r="E250" t="str">
+        <v>중/18</v>
+      </c>
+      <c r="F250" t="str">
+        <v>남동향</v>
+      </c>
+      <c r="G250" t="str">
+        <v>정상입주,방확장,주방씽크대외수리함.성복역초역세권</v>
+      </c>
+      <c r="H250" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>성동마을강남</v>
+      </c>
+      <c r="B251" t="str">
+        <v>11억 5,000</v>
+      </c>
+      <c r="C251">
+        <v>109</v>
+      </c>
+      <c r="D251" t="str">
+        <v>103동</v>
+      </c>
+      <c r="E251" t="str">
+        <v>11/18</v>
+      </c>
+      <c r="F251" t="str">
+        <v>남동향</v>
+      </c>
+      <c r="G251" t="str">
+        <v>올수리 폴딩도어 정상입주 성복역 도보2분 생활권좋음</v>
+      </c>
+      <c r="H251" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>성동마을강남</v>
+      </c>
+      <c r="B252" t="str">
+        <v>13억 5,000</v>
+      </c>
+      <c r="C252">
+        <v>163</v>
+      </c>
+      <c r="D252" t="str">
+        <v>105동</v>
+      </c>
+      <c r="E252" t="str">
+        <v>7/18</v>
+      </c>
+      <c r="F252" t="str">
+        <v>남향</v>
+      </c>
+      <c r="G252" t="str">
+        <v>세안고 남향 성복역 도보2분 상권인접 기본</v>
+      </c>
+      <c r="H252" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>성동마을강남</v>
+      </c>
+      <c r="B253" t="str">
+        <v>13억 5,000</v>
+      </c>
+      <c r="C253">
+        <v>163</v>
+      </c>
+      <c r="D253" t="str">
+        <v>106동</v>
+      </c>
+      <c r="E253" t="str">
+        <v>12/18</v>
+      </c>
+      <c r="F253" t="str">
+        <v>남동향</v>
+      </c>
+      <c r="G253" t="str">
+        <v>채광굿 초역세권 도보2분 생활권 좋음  기본</v>
+      </c>
+      <c r="H253" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>성동마을강남</v>
+      </c>
+      <c r="B254" t="str">
+        <v>11억 2,000</v>
+      </c>
+      <c r="C254">
+        <v>109</v>
+      </c>
+      <c r="D254" t="str">
+        <v>104동</v>
+      </c>
+      <c r="E254" t="str">
+        <v>10/18</v>
+      </c>
+      <c r="F254" t="str">
+        <v>남동향</v>
+      </c>
+      <c r="G254" t="str">
+        <v>거실확장 방1확장 올수리 초역세권 도보3분 상권인접</v>
+      </c>
+      <c r="H254" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>성동마을강남</v>
+      </c>
+      <c r="B255" t="str">
+        <v>15억</v>
+      </c>
+      <c r="C255">
+        <v>195</v>
+      </c>
+      <c r="D255" t="str">
+        <v>101동</v>
+      </c>
+      <c r="E255" t="str">
+        <v>고/18</v>
+      </c>
+      <c r="F255" t="str">
+        <v>남서향</v>
+      </c>
+      <c r="G255" t="str">
+        <v>깨끗하고 해잘드는 이쁜집</v>
+      </c>
+      <c r="H255" t="str">
+        <v>naver</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>성동마을강남</v>
+      </c>
+      <c r="B256" t="str">
+        <v>12억 9,000</v>
+      </c>
+      <c r="C256" t="str">
+        <v>163</v>
+      </c>
+      <c r="D256" t="str">
+        <v>107동</v>
+      </c>
+      <c r="E256" t="str">
+        <v>15층</v>
+      </c>
+      <c r="F256" t="str">
+        <v/>
+      </c>
+      <c r="G256" t="str">
+        <v>무주택자, 세안고, 남향, 화이트 올수리, 트인 조망, 성복역 도보5분</v>
+      </c>
+      <c r="H256" t="str">
+        <v>asil</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H172"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H256"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/listings.xlsx
+++ b/listings.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H256"/>
+  <dimension ref="A1:H236"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
@@ -544,22 +544,22 @@
         <v>신정마을주공1</v>
       </c>
       <c r="B6" t="str">
-        <v>12억</v>
+        <v>12억 8,000</v>
       </c>
       <c r="C6">
         <v>83</v>
       </c>
       <c r="D6" t="str">
-        <v>104동</v>
+        <v>111동</v>
       </c>
       <c r="E6" t="str">
-        <v>중/20</v>
+        <v>6/20</v>
       </c>
       <c r="F6" t="str">
         <v>남동향</v>
       </c>
       <c r="G6" t="str">
-        <v>세안고 거실방확장 화장실씽크대수리 로얄동 수지구청초역세권 생활편리</v>
+        <v>입주일협의,샷시,확장,최근특올수리,시스템에어컨</v>
       </c>
       <c r="H6" t="str">
         <v>naver</v>
@@ -570,22 +570,22 @@
         <v>신정마을주공1</v>
       </c>
       <c r="B7" t="str">
-        <v>12억 8,000</v>
+        <v>12억</v>
       </c>
       <c r="C7">
         <v>83</v>
       </c>
       <c r="D7" t="str">
-        <v>111동</v>
+        <v>104동</v>
       </c>
       <c r="E7" t="str">
-        <v>6/20</v>
+        <v>중/20</v>
       </c>
       <c r="F7" t="str">
         <v>남동향</v>
       </c>
       <c r="G7" t="str">
-        <v>입주일협의,샷시,확장,최근특올수리,시스템에어컨</v>
+        <v>세안고 거실방확장 화장실씽크대수리 로얄동 수지구청초역세권 생활편리</v>
       </c>
       <c r="H7" t="str">
         <v>naver</v>
@@ -674,22 +674,22 @@
         <v>용인수지신정마을9단지</v>
       </c>
       <c r="B11" t="str">
-        <v>10억 5,000</v>
+        <v>10억 3,000</v>
       </c>
       <c r="C11">
         <v>72</v>
       </c>
       <c r="D11" t="str">
-        <v>901동</v>
+        <v>905동</v>
       </c>
       <c r="E11" t="str">
-        <v>18/18</v>
+        <v>8/18</v>
       </c>
       <c r="F11" t="str">
         <v>남동향</v>
       </c>
       <c r="G11" t="str">
-        <v>샷시포함올수리,트인전망,공원,탄천연결,초역세권,입주협의</v>
+        <v>올수리,탄천전망,주차여유,초역세권,공원,4월초부터입주협의</v>
       </c>
       <c r="H11" t="str">
         <v>naver</v>
@@ -700,22 +700,22 @@
         <v>용인수지신정마을9단지</v>
       </c>
       <c r="B12" t="str">
-        <v>11억 7,000</v>
+        <v>9억</v>
       </c>
       <c r="C12">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D12" t="str">
-        <v>902동</v>
+        <v>901동</v>
       </c>
       <c r="E12" t="str">
-        <v>7/20</v>
+        <v>2/18</v>
       </c>
       <c r="F12" t="str">
-        <v>남서향</v>
+        <v>남동향</v>
       </c>
       <c r="G12" t="str">
-        <v>정상입주,샷시교체,올수리,방1확장,트인전망,초역세권,학군</v>
+        <v>월세안고, 기본, 신분당선초역세권, 공원탄천도서관인접</v>
       </c>
       <c r="H12" t="str">
         <v>naver</v>
@@ -726,22 +726,22 @@
         <v>용인수지신정마을9단지</v>
       </c>
       <c r="B13" t="str">
-        <v>11억 9,000</v>
+        <v>10억 6,000</v>
       </c>
       <c r="C13">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D13" t="str">
-        <v>909동</v>
+        <v>901동</v>
       </c>
       <c r="E13" t="str">
-        <v>15/18</v>
+        <v>10/18</v>
       </c>
       <c r="F13" t="str">
         <v>남동향</v>
       </c>
       <c r="G13" t="str">
-        <v>올수리, 거실확장, 신분당선초역세권, 공원탄천도서관인접, 주차천국</v>
+        <v>샷시포함올수리 거실확장 중문 수지구청역역세권</v>
       </c>
       <c r="H13" t="str">
         <v>naver</v>
@@ -752,22 +752,22 @@
         <v>용인수지신정마을9단지</v>
       </c>
       <c r="B14" t="str">
-        <v>10억 6,000</v>
+        <v>10억</v>
       </c>
       <c r="C14">
         <v>72</v>
       </c>
       <c r="D14" t="str">
-        <v>901동</v>
+        <v>908동</v>
       </c>
       <c r="E14" t="str">
-        <v>10/18</v>
+        <v>15/18</v>
       </c>
       <c r="F14" t="str">
         <v>남동향</v>
       </c>
       <c r="G14" t="str">
-        <v>샷시포함올수리 거실확장 중문 수지구청역역세권</v>
+        <v>정상입주, 로얄동층, 신분당선초역세권, 공원탄천도서관인접, 초품아</v>
       </c>
       <c r="H14" t="str">
         <v>naver</v>
@@ -778,7 +778,7 @@
         <v>용인수지신정마을9단지</v>
       </c>
       <c r="B15" t="str">
-        <v>9억</v>
+        <v>10억 5,000</v>
       </c>
       <c r="C15">
         <v>72</v>
@@ -787,13 +787,13 @@
         <v>901동</v>
       </c>
       <c r="E15" t="str">
-        <v>2/18</v>
+        <v>18/18</v>
       </c>
       <c r="F15" t="str">
         <v>남동향</v>
       </c>
       <c r="G15" t="str">
-        <v>월세안고, 기본, 신분당선초역세권, 공원탄천도서관인접</v>
+        <v>샷시포함올수리,트인전망,공원,탄천연결,초역세권,입주협의</v>
       </c>
       <c r="H15" t="str">
         <v>naver</v>
@@ -804,22 +804,22 @@
         <v>용인수지신정마을9단지</v>
       </c>
       <c r="B16" t="str">
-        <v>10억 3,000</v>
+        <v>11억 7,000</v>
       </c>
       <c r="C16">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="D16" t="str">
-        <v>905동</v>
+        <v>902동</v>
       </c>
       <c r="E16" t="str">
-        <v>8/18</v>
+        <v>7/20</v>
       </c>
       <c r="F16" t="str">
-        <v>남동향</v>
+        <v>남서향</v>
       </c>
       <c r="G16" t="str">
-        <v>올수리,탄천전망,주차여유,초역세권,공원,4월초부터입주협의</v>
+        <v>정상입주,샷시교체,올수리,방1확장,트인전망,초역세권,학군</v>
       </c>
       <c r="H16" t="str">
         <v>naver</v>
@@ -830,13 +830,13 @@
         <v>용인수지신정마을9단지</v>
       </c>
       <c r="B17" t="str">
-        <v>10억</v>
+        <v>11억 9,000</v>
       </c>
       <c r="C17">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="D17" t="str">
-        <v>908동</v>
+        <v>909동</v>
       </c>
       <c r="E17" t="str">
         <v>15/18</v>
@@ -845,7 +845,7 @@
         <v>남동향</v>
       </c>
       <c r="G17" t="str">
-        <v>정상입주, 로얄동층, 신분당선초역세권, 공원탄천도서관인접, 초품아</v>
+        <v>올수리, 거실확장, 신분당선초역세권, 공원탄천도서관인접, 주차천국</v>
       </c>
       <c r="H17" t="str">
         <v>naver</v>
@@ -856,22 +856,22 @@
         <v>용인수지신정마을9단지</v>
       </c>
       <c r="B18" t="str">
-        <v>10억 4,000</v>
+        <v>10억 3,000</v>
       </c>
       <c r="C18">
         <v>72</v>
       </c>
       <c r="D18" t="str">
-        <v>908동</v>
+        <v>905동</v>
       </c>
       <c r="E18" t="str">
-        <v>13/18</v>
+        <v>16/18</v>
       </c>
       <c r="F18" t="str">
         <v>남동향</v>
       </c>
       <c r="G18" t="str">
-        <v>정상입주,로얄동,올수리,깨끗</v>
+        <v>정상,전체올수리,샷시,수지구청역세권,탄천전망,지하주차장 굿</v>
       </c>
       <c r="H18" t="str">
         <v>naver</v>
@@ -882,22 +882,22 @@
         <v>용인수지신정마을9단지</v>
       </c>
       <c r="B19" t="str">
-        <v>10억 3,000</v>
+        <v>10억 4,000</v>
       </c>
       <c r="C19">
         <v>72</v>
       </c>
       <c r="D19" t="str">
-        <v>905동</v>
+        <v>908동</v>
       </c>
       <c r="E19" t="str">
-        <v>16/18</v>
+        <v>13/18</v>
       </c>
       <c r="F19" t="str">
         <v>남동향</v>
       </c>
       <c r="G19" t="str">
-        <v>정상,전체올수리,샷시,수지구청역세권,탄천전망,지하주차장 굿</v>
+        <v>정상입주,로얄동,올수리,깨끗</v>
       </c>
       <c r="H19" t="str">
         <v>naver</v>
@@ -1191,25 +1191,25 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>신정7단지(상록)공무원</v>
+        <v>한국</v>
       </c>
       <c r="B31" t="str">
-        <v>13억 9,000</v>
+        <v>9억 5,000</v>
       </c>
       <c r="C31">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="D31" t="str">
-        <v>704동</v>
+        <v>102동</v>
       </c>
       <c r="E31" t="str">
-        <v>19/20</v>
+        <v>1/16</v>
       </c>
       <c r="F31" t="str">
-        <v>남동향</v>
+        <v>동향</v>
       </c>
       <c r="G31" t="str">
-        <v>세안고27년9월말, 외부샷시교체,방1확장,내부일부수리,로얄동로얄층</v>
+        <v>내부샷시까지 올수리,  초역세권</v>
       </c>
       <c r="H31" t="str">
         <v>naver</v>
@@ -1217,25 +1217,25 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>신정7단지(상록)공무원</v>
+        <v>한국</v>
       </c>
       <c r="B32" t="str">
-        <v>14억</v>
+        <v>10억</v>
       </c>
       <c r="C32">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D32" t="str">
-        <v>701동</v>
+        <v>104동</v>
       </c>
       <c r="E32" t="str">
-        <v>16/20</v>
+        <v>1/16</v>
       </c>
       <c r="F32" t="str">
         <v>남동향</v>
       </c>
       <c r="G32" t="str">
-        <v>예전 올수리 방1 주방확장 초품아 학군최고 신분당선역세권</v>
+        <v>내부 올수리, 전세안고투자, 수지구청역 초역세권, 명문학군, 편의시설</v>
       </c>
       <c r="H32" t="str">
         <v>naver</v>
@@ -1243,25 +1243,25 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>신정7단지(상록)공무원</v>
+        <v>한국</v>
       </c>
       <c r="B33" t="str">
-        <v>10억 4,000</v>
+        <v>11억 5,000</v>
       </c>
       <c r="C33">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="D33" t="str">
-        <v>705동</v>
+        <v>105동</v>
       </c>
       <c r="E33" t="str">
-        <v>2/20</v>
+        <v>중/16</v>
       </c>
       <c r="F33" t="str">
         <v>남동향</v>
       </c>
       <c r="G33" t="str">
-        <v>주인직접의뢰.로얄동,즉시입주가능.초급매</v>
+        <v>입주가,  내부샷시포함 올수리, 깨끗</v>
       </c>
       <c r="H33" t="str">
         <v>naver</v>
@@ -1269,25 +1269,25 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>신정7단지(상록)공무원</v>
+        <v>한국</v>
       </c>
       <c r="B34" t="str">
-        <v>11억 2,000</v>
+        <v>11억 5,000</v>
       </c>
       <c r="C34">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="D34" t="str">
-        <v>706동</v>
+        <v>104동</v>
       </c>
       <c r="E34" t="str">
-        <v>5/20</v>
+        <v>고/16</v>
       </c>
       <c r="F34" t="str">
         <v>남동향</v>
       </c>
       <c r="G34" t="str">
-        <v>11월입주가능, 수리되어 깔끔해요. 정평초학군, 신분당선초역세권</v>
+        <v>로얄동 로얄층 확트인뷰 수지구청역 초역세권</v>
       </c>
       <c r="H34" t="str">
         <v>naver</v>
@@ -1295,25 +1295,25 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>신정7단지(상록)공무원</v>
+        <v>한국</v>
       </c>
       <c r="B35" t="str">
-        <v>13억 7,000</v>
+        <v>11억 3,000</v>
       </c>
       <c r="C35">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D35" t="str">
-        <v>702동</v>
+        <v>104동</v>
       </c>
       <c r="E35" t="str">
-        <v>13/20</v>
+        <v>6/16</v>
       </c>
       <c r="F35" t="str">
         <v>남동향</v>
       </c>
       <c r="G35" t="str">
-        <v>27년1월초기본,화장실수리.신발장교체,결로 곰팡이 없음.</v>
+        <v>급매 도배장판 씽크대 부분수리 수지구청역 초역세권</v>
       </c>
       <c r="H35" t="str">
         <v>naver</v>
@@ -1321,25 +1321,25 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>신정7단지(상록)공무원</v>
+        <v>한국</v>
       </c>
       <c r="B36" t="str">
-        <v>13억 5,000</v>
+        <v>11억 5,000</v>
       </c>
       <c r="C36">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D36" t="str">
-        <v>702동</v>
+        <v>103동</v>
       </c>
       <c r="E36" t="str">
-        <v>2/20</v>
+        <v>저/16</v>
       </c>
       <c r="F36" t="str">
         <v>남동향</v>
       </c>
       <c r="G36" t="str">
-        <v>33P, 기본, 정평초, 수지구청역세권</v>
+        <v>로얄동 리모델링 추진단지 수지구청역초역세권 입주협의</v>
       </c>
       <c r="H36" t="str">
         <v>naver</v>
@@ -1347,25 +1347,25 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>신정7단지(상록)공무원</v>
+        <v>한국</v>
       </c>
       <c r="B37" t="str">
-        <v>14억 2,000</v>
+        <v>12억</v>
       </c>
       <c r="C37">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D37" t="str">
-        <v>704동</v>
+        <v>103동</v>
       </c>
       <c r="E37" t="str">
-        <v>9/20</v>
+        <v>고/16</v>
       </c>
       <c r="F37" t="str">
         <v>남동향</v>
       </c>
       <c r="G37" t="str">
-        <v>입주협의가 샷시포함 특올수리 거실방1주방 확장 로얄동로얄층</v>
+        <v>입주가,  샷시포함 올수리되고 깨끗함</v>
       </c>
       <c r="H37" t="str">
         <v>naver</v>
@@ -1373,25 +1373,25 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>신정7단지(상록)공무원</v>
+        <v>한국</v>
       </c>
       <c r="B38" t="str">
-        <v>14억</v>
+        <v>11억 3,000</v>
       </c>
       <c r="C38">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D38" t="str">
-        <v>704동</v>
+        <v>104동</v>
       </c>
       <c r="E38" t="str">
-        <v>4/20</v>
+        <v>3/16</v>
       </c>
       <c r="F38" t="str">
         <v>남동향</v>
       </c>
       <c r="G38" t="str">
-        <v>세안고2026년7월,로얄동,일부수리</v>
+        <v>방확장.리모델링추진단지.수지구청역 도보 1분</v>
       </c>
       <c r="H38" t="str">
         <v>naver</v>
@@ -1399,25 +1399,25 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>신정7단지(상록)공무원</v>
+        <v>한국</v>
       </c>
       <c r="B39" t="str">
-        <v>11억 3,000</v>
+        <v>12억</v>
       </c>
       <c r="C39">
         <v>81</v>
       </c>
       <c r="D39" t="str">
-        <v>705동</v>
+        <v>101동</v>
       </c>
       <c r="E39" t="str">
-        <v>8/20</v>
+        <v>13/16</v>
       </c>
       <c r="F39" t="str">
         <v>남동향</v>
       </c>
       <c r="G39" t="str">
-        <v>세안고2027년7월, 로얄동 전망굿, 깨끗합니다.</v>
+        <v>초역세권리모델링추진단지로,전체 수리한집입니다.</v>
       </c>
       <c r="H39" t="str">
         <v>naver</v>
@@ -1425,25 +1425,25 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>신정7단지(상록)공무원</v>
+        <v>한국</v>
       </c>
       <c r="B40" t="str">
-        <v>13억 8,000</v>
+        <v>11억 4,000</v>
       </c>
       <c r="C40">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D40" t="str">
-        <v>701동</v>
+        <v>105동</v>
       </c>
       <c r="E40" t="str">
-        <v>17/20</v>
+        <v>저/16</v>
       </c>
       <c r="F40" t="str">
         <v>남동향</v>
       </c>
       <c r="G40" t="str">
-        <v>정상,전망굿,기본,초중고인접,수지구청역세권</v>
+        <v>초역세권, 올수리, 리모델링추진단지.</v>
       </c>
       <c r="H40" t="str">
         <v>naver</v>
@@ -1451,25 +1451,25 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>신정7단지(상록)공무원</v>
+        <v>한국</v>
       </c>
       <c r="B41" t="str">
-        <v>10억 3,000</v>
+        <v>11억 8,000</v>
       </c>
       <c r="C41">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="D41" t="str">
-        <v>706동</v>
+        <v>104동</v>
       </c>
       <c r="E41" t="str">
-        <v>1/20</v>
+        <v>중/16</v>
       </c>
       <c r="F41" t="str">
         <v>남동향</v>
       </c>
       <c r="G41" t="str">
-        <v>올수리 최근 지인샷시 중문 교체 학군우수 수지구청역 도보5분 세안고</v>
+        <v>깨끗함,  입주협의,  초역세권</v>
       </c>
       <c r="H41" t="str">
         <v>naver</v>
@@ -1477,25 +1477,25 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>신정7단지(상록)공무원</v>
+        <v>한국</v>
       </c>
       <c r="B42" t="str">
-        <v>14억</v>
+        <v>10억 5,000</v>
       </c>
       <c r="C42">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="D42" t="str">
-        <v>701동</v>
+        <v>101동</v>
       </c>
       <c r="E42" t="str">
-        <v>6/20</v>
+        <v>고/16</v>
       </c>
       <c r="F42" t="str">
         <v>남동향</v>
       </c>
       <c r="G42" t="str">
-        <v>신정7단지상록</v>
+        <v>수지구청초역세권 확트인 전망채광굿 로얄동,층</v>
       </c>
       <c r="H42" t="str">
         <v>naver</v>
@@ -1503,25 +1503,25 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>신정7단지(상록)공무원</v>
+        <v>한국</v>
       </c>
       <c r="B43" t="str">
-        <v>11억 9,000</v>
+        <v>11억 4,000</v>
       </c>
       <c r="C43">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="D43" t="str">
-        <v>705동</v>
+        <v>105동</v>
       </c>
       <c r="E43" t="str">
-        <v>19/20</v>
+        <v>고/16</v>
       </c>
       <c r="F43" t="str">
         <v>남동향</v>
       </c>
       <c r="G43" t="str">
-        <v>6월이 2년 됨,샷시외 확장 올수리됨,</v>
+        <v>초역세권.탁트인 조망.수지구청역 도보2분.전자계약</v>
       </c>
       <c r="H43" t="str">
         <v>naver</v>
@@ -1529,25 +1529,25 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>한국</v>
+        <v>현대</v>
       </c>
       <c r="B44" t="str">
-        <v>9억 5,000</v>
+        <v>12억 5,000</v>
       </c>
       <c r="C44">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="D44" t="str">
-        <v>102동</v>
+        <v>108동</v>
       </c>
       <c r="E44" t="str">
-        <v>1/16</v>
+        <v>12/15</v>
       </c>
       <c r="F44" t="str">
-        <v>동향</v>
+        <v>남동향</v>
       </c>
       <c r="G44" t="str">
-        <v>내부샷시까지 올수리,  초역세권</v>
+        <v>내부샷시포함 올수리 로얄동 로얄층 관리잘된집28년2월입주</v>
       </c>
       <c r="H44" t="str">
         <v>naver</v>
@@ -1555,25 +1555,25 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>한국</v>
+        <v>현대</v>
       </c>
       <c r="B45" t="str">
-        <v>10억</v>
+        <v>12억 5,000</v>
       </c>
       <c r="C45">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D45" t="str">
-        <v>104동</v>
+        <v>112동</v>
       </c>
       <c r="E45" t="str">
-        <v>1/16</v>
+        <v>6/15</v>
       </c>
       <c r="F45" t="str">
         <v>남동향</v>
       </c>
       <c r="G45" t="str">
-        <v>내부 올수리, 전세안고투자, 수지구청역 초역세권, 명문학군, 편의시설</v>
+        <v>현대 로얄동, 입주협의가능, 주인거주 컨디션 좋은집</v>
       </c>
       <c r="H45" t="str">
         <v>naver</v>
@@ -1581,25 +1581,25 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>한국</v>
+        <v>현대</v>
       </c>
       <c r="B46" t="str">
         <v>11억 5,000</v>
       </c>
       <c r="C46">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D46" t="str">
-        <v>105동</v>
+        <v>102동</v>
       </c>
       <c r="E46" t="str">
-        <v>중/16</v>
+        <v>9/15</v>
       </c>
       <c r="F46" t="str">
         <v>남동향</v>
       </c>
       <c r="G46" t="str">
-        <v>입주가,  내부샷시포함 올수리, 깨끗</v>
+        <v>내부 수리,정상 입주협의, 수지구청역 초역세권, 명문학군</v>
       </c>
       <c r="H46" t="str">
         <v>naver</v>
@@ -1607,25 +1607,25 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>한국</v>
+        <v>현대</v>
       </c>
       <c r="B47" t="str">
-        <v>11억 5,000</v>
+        <v>9억 9,000</v>
       </c>
       <c r="C47">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="D47" t="str">
-        <v>104동</v>
+        <v>101동</v>
       </c>
       <c r="E47" t="str">
-        <v>고/16</v>
+        <v>9/15</v>
       </c>
       <c r="F47" t="str">
         <v>남동향</v>
       </c>
       <c r="G47" t="str">
-        <v>로얄동 로얄층 확트인뷰 수지구청역 초역세권</v>
+        <v>로열동  로열층 내부수리 했었던 집 수지구청역 도보5분 초역세권</v>
       </c>
       <c r="H47" t="str">
         <v>naver</v>
@@ -1633,25 +1633,25 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>한국</v>
+        <v>현대</v>
       </c>
       <c r="B48" t="str">
-        <v>11억 3,000</v>
+        <v>9억 5,000</v>
       </c>
       <c r="C48">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="D48" t="str">
-        <v>104동</v>
+        <v>103동</v>
       </c>
       <c r="E48" t="str">
-        <v>6/16</v>
+        <v>9/15</v>
       </c>
       <c r="F48" t="str">
-        <v>남동향</v>
+        <v>남서향</v>
       </c>
       <c r="G48" t="str">
-        <v>급매 도배장판 씽크대 부분수리 수지구청역 초역세권</v>
+        <v>현대</v>
       </c>
       <c r="H48" t="str">
         <v>naver</v>
@@ -1659,25 +1659,25 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>한국</v>
+        <v>현대</v>
       </c>
       <c r="B49" t="str">
-        <v>11억 5,000</v>
+        <v>11억 8,000</v>
       </c>
       <c r="C49">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D49" t="str">
-        <v>103동</v>
+        <v>104동</v>
       </c>
       <c r="E49" t="str">
-        <v>저/16</v>
+        <v>7/15</v>
       </c>
       <c r="F49" t="str">
-        <v>남동향</v>
+        <v>남서향</v>
       </c>
       <c r="G49" t="str">
-        <v>로얄동 리모델링 추진단지 수지구청역초역세권 입주협의</v>
+        <v>입주급매 앞 뒤 트여 바람 잘 통하고 밝은 집  살기 좋아요</v>
       </c>
       <c r="H49" t="str">
         <v>naver</v>
@@ -1685,25 +1685,25 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>한국</v>
+        <v>현대</v>
       </c>
       <c r="B50" t="str">
-        <v>12억</v>
+        <v>11억 9,000</v>
       </c>
       <c r="C50">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D50" t="str">
-        <v>103동</v>
+        <v>106동</v>
       </c>
       <c r="E50" t="str">
-        <v>고/16</v>
+        <v>12/15</v>
       </c>
       <c r="F50" t="str">
         <v>남동향</v>
       </c>
       <c r="G50" t="str">
-        <v>입주가,  샷시포함 올수리되고 깨끗함</v>
+        <v>수리깨끗, 수지구청역 초역세권, 명문학군,로얄동층, 편의시설다양</v>
       </c>
       <c r="H50" t="str">
         <v>naver</v>
@@ -1711,25 +1711,25 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>한국</v>
+        <v>현대</v>
       </c>
       <c r="B51" t="str">
-        <v>11억 3,000</v>
+        <v>12억</v>
       </c>
       <c r="C51">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D51" t="str">
-        <v>104동</v>
+        <v>109동</v>
       </c>
       <c r="E51" t="str">
-        <v>3/16</v>
+        <v>2/15</v>
       </c>
       <c r="F51" t="str">
         <v>남동향</v>
       </c>
       <c r="G51" t="str">
-        <v>방확장.리모델링추진단지.수지구청역 도보 1분</v>
+        <v>입주가능  중간샷시설치 중문설치 내부수리  로열동 저층 햇살 좋아요</v>
       </c>
       <c r="H51" t="str">
         <v>naver</v>
@@ -1737,25 +1737,25 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>한국</v>
+        <v>현대</v>
       </c>
       <c r="B52" t="str">
         <v>12억</v>
       </c>
       <c r="C52">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="D52" t="str">
-        <v>101동</v>
+        <v>105동</v>
       </c>
       <c r="E52" t="str">
-        <v>13/16</v>
+        <v>9/15</v>
       </c>
       <c r="F52" t="str">
         <v>남동향</v>
       </c>
       <c r="G52" t="str">
-        <v>초역세권리모델링추진단지로,전체 수리한집입니다.</v>
+        <v>로열동 내부수리 전망트여 시원해요  신분당선도보5분  생활인프라최고</v>
       </c>
       <c r="H52" t="str">
         <v>naver</v>
@@ -1763,25 +1763,25 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>한국</v>
+        <v>현대</v>
       </c>
       <c r="B53" t="str">
-        <v>11억 4,000</v>
+        <v>11억 8,000</v>
       </c>
       <c r="C53">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D53" t="str">
-        <v>105동</v>
+        <v>102동</v>
       </c>
       <c r="E53" t="str">
-        <v>저/16</v>
+        <v>6/15</v>
       </c>
       <c r="F53" t="str">
         <v>남동향</v>
       </c>
       <c r="G53" t="str">
-        <v>초역세권, 올수리, 리모델링추진단지.</v>
+        <v>내부수리, 수지구청역 초역세권, 명문학군, 로얄층, 편의시설다양</v>
       </c>
       <c r="H53" t="str">
         <v>naver</v>
@@ -1789,25 +1789,25 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>한국</v>
+        <v>현대</v>
       </c>
       <c r="B54" t="str">
-        <v>11억 8,000</v>
+        <v>12억</v>
       </c>
       <c r="C54">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D54" t="str">
-        <v>104동</v>
+        <v>111동</v>
       </c>
       <c r="E54" t="str">
-        <v>중/16</v>
+        <v>8/15</v>
       </c>
       <c r="F54" t="str">
         <v>남동향</v>
       </c>
       <c r="G54" t="str">
-        <v>깨끗함,  입주협의,  초역세권</v>
+        <v>입주협의, 부분수리된 집, 수지구청역 가까운 동, 로얄동</v>
       </c>
       <c r="H54" t="str">
         <v>naver</v>
@@ -1815,25 +1815,25 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>한국</v>
+        <v>현대</v>
       </c>
       <c r="B55" t="str">
-        <v>10억 5,000</v>
+        <v>9억 7,000</v>
       </c>
       <c r="C55">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D55" t="str">
-        <v>101동</v>
+        <v>103동</v>
       </c>
       <c r="E55" t="str">
-        <v>고/16</v>
+        <v>2/15</v>
       </c>
       <c r="F55" t="str">
-        <v>남동향</v>
+        <v>남서향</v>
       </c>
       <c r="G55" t="str">
-        <v>수지구청초역세권 확트인 전망채광굿 로얄동,층</v>
+        <v>샷시포함특올수리, 즉시입주가능, 신혼부부추천,명문학군,편의시설다양</v>
       </c>
       <c r="H55" t="str">
         <v>naver</v>
@@ -1841,25 +1841,25 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>한국</v>
+        <v>현대</v>
       </c>
       <c r="B56" t="str">
-        <v>11억 4,000</v>
+        <v>11억 5,000</v>
       </c>
       <c r="C56">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D56" t="str">
-        <v>105동</v>
+        <v>112동</v>
       </c>
       <c r="E56" t="str">
-        <v>고/16</v>
+        <v>1/15</v>
       </c>
       <c r="F56" t="str">
         <v>남동향</v>
       </c>
       <c r="G56" t="str">
-        <v>초역세권.탁트인 조망.수지구청역 도보2분.전자계약</v>
+        <v>내부샷시 교체, 방1확장, 중문, 입주협의, 깨끗하게 관리 잘 된 집</v>
       </c>
       <c r="H56" t="str">
         <v>naver</v>
@@ -1870,22 +1870,22 @@
         <v>현대</v>
       </c>
       <c r="B57" t="str">
-        <v>12억 5,000</v>
+        <v>11억 5,000</v>
       </c>
       <c r="C57">
         <v>104</v>
       </c>
       <c r="D57" t="str">
-        <v>108동</v>
+        <v>104동</v>
       </c>
       <c r="E57" t="str">
-        <v>12/15</v>
+        <v>13/15</v>
       </c>
       <c r="F57" t="str">
-        <v>남동향</v>
+        <v>남서향</v>
       </c>
       <c r="G57" t="str">
-        <v>내부샷시포함 올수리 로얄동 로얄층 관리잘된집28년2월입주</v>
+        <v>내부수리, 빠른입주 가능, 수지구청역 초역세권, 명문학군, 로얄층</v>
       </c>
       <c r="H57" t="str">
         <v>naver</v>
@@ -1896,22 +1896,22 @@
         <v>현대</v>
       </c>
       <c r="B58" t="str">
-        <v>12억 5,000</v>
+        <v>11억 5,000</v>
       </c>
       <c r="C58">
         <v>104</v>
       </c>
       <c r="D58" t="str">
-        <v>112동</v>
+        <v>108동</v>
       </c>
       <c r="E58" t="str">
-        <v>6/15</v>
+        <v>저/15</v>
       </c>
       <c r="F58" t="str">
         <v>남동향</v>
       </c>
       <c r="G58" t="str">
-        <v>현대 로얄동, 입주협의가능, 주인거주 컨디션 좋은집</v>
+        <v>수지구청역 도보 5분 초역세권, 8월입주협의, 올리모델링, 살기좋은동네</v>
       </c>
       <c r="H58" t="str">
         <v>naver</v>
@@ -1922,13 +1922,13 @@
         <v>현대</v>
       </c>
       <c r="B59" t="str">
-        <v>11억 5,000</v>
+        <v>9억 7,000</v>
       </c>
       <c r="C59">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="D59" t="str">
-        <v>102동</v>
+        <v>101동</v>
       </c>
       <c r="E59" t="str">
         <v>9/15</v>
@@ -1937,7 +1937,7 @@
         <v>남동향</v>
       </c>
       <c r="G59" t="str">
-        <v>내부 수리,정상 입주협의, 수지구청역 초역세권, 명문학군</v>
+        <v>예전수리된집, 10월말 입주가능</v>
       </c>
       <c r="H59" t="str">
         <v>naver</v>
@@ -1948,22 +1948,22 @@
         <v>현대</v>
       </c>
       <c r="B60" t="str">
-        <v>9억 5,000</v>
+        <v>11억</v>
       </c>
       <c r="C60">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="D60" t="str">
-        <v>103동</v>
+        <v>109동</v>
       </c>
       <c r="E60" t="str">
-        <v>5/15</v>
+        <v>1/15</v>
       </c>
       <c r="F60" t="str">
-        <v>남서향</v>
+        <v>남동향</v>
       </c>
       <c r="G60" t="str">
-        <v>기본, 정상입주협의, 수지구청역 초역세권, 명문학군,편의시설다양</v>
+        <v>입주추천.샷시.화장실등 전체 올수리.역세권</v>
       </c>
       <c r="H60" t="str">
         <v>naver</v>
@@ -1974,22 +1974,22 @@
         <v>현대</v>
       </c>
       <c r="B61" t="str">
-        <v>9억 5,000</v>
+        <v>12억 5,000</v>
       </c>
       <c r="C61">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="D61" t="str">
-        <v>103동</v>
+        <v>106동</v>
       </c>
       <c r="E61" t="str">
-        <v>9/15</v>
+        <v>2/15</v>
       </c>
       <c r="F61" t="str">
-        <v>남서향</v>
+        <v>남동향</v>
       </c>
       <c r="G61" t="str">
-        <v>현대</v>
+        <v>깨끗함, 기본상태, 8월말 입주가능</v>
       </c>
       <c r="H61" t="str">
         <v>naver</v>
@@ -2000,22 +2000,22 @@
         <v>현대</v>
       </c>
       <c r="B62" t="str">
-        <v>9억 9,000</v>
+        <v>12억</v>
       </c>
       <c r="C62">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="D62" t="str">
-        <v>101동</v>
+        <v>112동</v>
       </c>
       <c r="E62" t="str">
-        <v>9/15</v>
+        <v>3/15</v>
       </c>
       <c r="F62" t="str">
         <v>남동향</v>
       </c>
       <c r="G62" t="str">
-        <v>로열동  로열층 내부수리 했었던 집 수지구청역 도보5분 초역세권</v>
+        <v>정상입주 입주일협의 수지구청역 초역세권</v>
       </c>
       <c r="H62" t="str">
         <v>naver</v>
@@ -2026,22 +2026,22 @@
         <v>현대</v>
       </c>
       <c r="B63" t="str">
-        <v>12억</v>
+        <v>11억</v>
       </c>
       <c r="C63">
         <v>104</v>
       </c>
       <c r="D63" t="str">
-        <v>105동</v>
+        <v>104동</v>
       </c>
       <c r="E63" t="str">
-        <v>9/15</v>
+        <v>1/15</v>
       </c>
       <c r="F63" t="str">
-        <v>남동향</v>
+        <v>남서향</v>
       </c>
       <c r="G63" t="str">
-        <v>로열동 내부수리 전망트여 시원해요  신분당선도보5분  생활인프라최고</v>
+        <v>세안고, 아이 키우기 좋아요. 동간 거리 넓고 조용한 동</v>
       </c>
       <c r="H63" t="str">
         <v>naver</v>
@@ -2058,16 +2058,16 @@
         <v>104</v>
       </c>
       <c r="D64" t="str">
-        <v>111동</v>
+        <v>105동</v>
       </c>
       <c r="E64" t="str">
-        <v>8/15</v>
+        <v>고/15</v>
       </c>
       <c r="F64" t="str">
         <v>남동향</v>
       </c>
       <c r="G64" t="str">
-        <v>입주협의, 부분수리된 집, 수지구청역 가까운 동, 로얄동</v>
+        <v>입주협의, 내부샷시 교체, 방1확장, 로얄동, 로얄라인</v>
       </c>
       <c r="H64" t="str">
         <v>naver</v>
@@ -2078,7 +2078,7 @@
         <v>현대</v>
       </c>
       <c r="B65" t="str">
-        <v>11억 9,000</v>
+        <v>12억</v>
       </c>
       <c r="C65">
         <v>104</v>
@@ -2087,13 +2087,13 @@
         <v>106동</v>
       </c>
       <c r="E65" t="str">
-        <v>12/15</v>
+        <v>1/15</v>
       </c>
       <c r="F65" t="str">
         <v>남동향</v>
       </c>
       <c r="G65" t="str">
-        <v>수리깨끗, 수지구청역 초역세권, 명문학군,로얄동층, 편의시설다양</v>
+        <v>내부올수리,정상입주가능, 수지구청역 초역세권, 명문학군</v>
       </c>
       <c r="H65" t="str">
         <v>naver</v>
@@ -2104,22 +2104,22 @@
         <v>현대</v>
       </c>
       <c r="B66" t="str">
-        <v>11억 8,000</v>
+        <v>11억</v>
       </c>
       <c r="C66">
         <v>104</v>
       </c>
       <c r="D66" t="str">
-        <v>104동</v>
+        <v>106동</v>
       </c>
       <c r="E66" t="str">
-        <v>7/15</v>
+        <v>1/15</v>
       </c>
       <c r="F66" t="str">
-        <v>남서향</v>
+        <v>남향</v>
       </c>
       <c r="G66" t="str">
-        <v>입주급매 앞 뒤 트여 바람 잘 통하고 밝은 집  살기 좋아요</v>
+        <v>샷쉬교체 및 화장실 씽크대등 내부 올 리모델링</v>
       </c>
       <c r="H66" t="str">
         <v>naver</v>
@@ -2130,22 +2130,22 @@
         <v>현대</v>
       </c>
       <c r="B67" t="str">
-        <v>11억 8,000</v>
+        <v>10억 2,000</v>
       </c>
       <c r="C67">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="D67" t="str">
-        <v>102동</v>
+        <v>101동</v>
       </c>
       <c r="E67" t="str">
-        <v>6/15</v>
+        <v>15/15</v>
       </c>
       <c r="F67" t="str">
         <v>남동향</v>
       </c>
       <c r="G67" t="str">
-        <v>내부수리, 수지구청역 초역세권, 명문학군, 로얄층, 편의시설다양</v>
+        <v>깨끗, 정상입주협의, 수지구청역 초역세권, 명문학군,편의시설다양</v>
       </c>
       <c r="H67" t="str">
         <v>naver</v>
@@ -2156,22 +2156,22 @@
         <v>현대</v>
       </c>
       <c r="B68" t="str">
-        <v>12억</v>
+        <v>10억</v>
       </c>
       <c r="C68">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="D68" t="str">
-        <v>109동</v>
+        <v>101동</v>
       </c>
       <c r="E68" t="str">
-        <v>2/15</v>
+        <v>14/15</v>
       </c>
       <c r="F68" t="str">
         <v>남동향</v>
       </c>
       <c r="G68" t="str">
-        <v>입주가능  중간샷시설치 중문설치 내부수리  로열동 저층 햇살 좋아요</v>
+        <v>기본, 긴 잔금, 수지구청 도보8분, 최고 입지의 대단지아파트</v>
       </c>
       <c r="H68" t="str">
         <v>naver</v>
@@ -2182,22 +2182,22 @@
         <v>현대</v>
       </c>
       <c r="B69" t="str">
-        <v>9억 7,000</v>
+        <v>11억 5,000</v>
       </c>
       <c r="C69">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="D69" t="str">
-        <v>103동</v>
+        <v>109동</v>
       </c>
       <c r="E69" t="str">
-        <v>2/15</v>
+        <v>1/15</v>
       </c>
       <c r="F69" t="str">
-        <v>남서향</v>
+        <v>남동향</v>
       </c>
       <c r="G69" t="str">
-        <v>샷시포함특올수리, 즉시입주가능, 신혼부부추천,명문학군,편의시설다양</v>
+        <v>빠른입주협의, 방1확장, 도배,데코우드마루, 화장실문교체 및 줄눈시공</v>
       </c>
       <c r="H69" t="str">
         <v>naver</v>
@@ -2208,22 +2208,22 @@
         <v>현대</v>
       </c>
       <c r="B70" t="str">
-        <v>11억 5,000</v>
+        <v>9억 5,000</v>
       </c>
       <c r="C70">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="D70" t="str">
-        <v>112동</v>
+        <v>103동</v>
       </c>
       <c r="E70" t="str">
-        <v>1/15</v>
+        <v>저/15</v>
       </c>
       <c r="F70" t="str">
-        <v>남동향</v>
+        <v>남서향</v>
       </c>
       <c r="G70" t="str">
-        <v>내부샷시 교체, 방1확장, 중문, 입주협의, 깨끗하게 관리 잘 된 집</v>
+        <v>22p,남서향,기본,상권학원가 이용편리해요.</v>
       </c>
       <c r="H70" t="str">
         <v>naver</v>
@@ -2234,22 +2234,22 @@
         <v>현대</v>
       </c>
       <c r="B71" t="str">
-        <v>11억 5,000</v>
+        <v>13억</v>
       </c>
       <c r="C71">
         <v>104</v>
       </c>
       <c r="D71" t="str">
-        <v>104동</v>
+        <v>107동</v>
       </c>
       <c r="E71" t="str">
-        <v>13/15</v>
+        <v>중/15</v>
       </c>
       <c r="F71" t="str">
-        <v>남서향</v>
+        <v>남동향</v>
       </c>
       <c r="G71" t="str">
-        <v>내부수리, 빠른입주 가능, 수지구청역 초역세권, 명문학군, 로얄층</v>
+        <v>입주협의, 깨끗, 샷시 제외, 예전수리, 로얄동</v>
       </c>
       <c r="H71" t="str">
         <v>naver</v>
@@ -2260,22 +2260,22 @@
         <v>현대</v>
       </c>
       <c r="B72" t="str">
-        <v>11억 5,000</v>
+        <v>12억</v>
       </c>
       <c r="C72">
         <v>104</v>
       </c>
       <c r="D72" t="str">
-        <v>108동</v>
+        <v>102동</v>
       </c>
       <c r="E72" t="str">
-        <v>저/15</v>
+        <v>5/15</v>
       </c>
       <c r="F72" t="str">
         <v>남동향</v>
       </c>
       <c r="G72" t="str">
-        <v>수지구청역 도보 5분 초역세권, 8월입주협의, 올리모델링, 살기좋은동네</v>
+        <v>깨끗, 정상입주협의 수지구청역 초역세권, 명문학군, 편의시설 다양</v>
       </c>
       <c r="H72" t="str">
         <v>naver</v>
@@ -2286,22 +2286,22 @@
         <v>현대</v>
       </c>
       <c r="B73" t="str">
-        <v>11억</v>
+        <v>11억 5,000</v>
       </c>
       <c r="C73">
         <v>104</v>
       </c>
       <c r="D73" t="str">
-        <v>109동</v>
+        <v>108동</v>
       </c>
       <c r="E73" t="str">
-        <v>1/15</v>
+        <v>3/15</v>
       </c>
       <c r="F73" t="str">
         <v>남동향</v>
       </c>
       <c r="G73" t="str">
-        <v>입주추천.샷시.화장실등 전체 올수리.역세권</v>
+        <v>깨끗, 수지구청역 초역세권, 명문학군, 로얄동, 편의시설다양</v>
       </c>
       <c r="H73" t="str">
         <v>naver</v>
@@ -2312,22 +2312,22 @@
         <v>현대</v>
       </c>
       <c r="B74" t="str">
-        <v>12억 5,000</v>
+        <v>13억</v>
       </c>
       <c r="C74">
         <v>104</v>
       </c>
       <c r="D74" t="str">
-        <v>106동</v>
+        <v>107동</v>
       </c>
       <c r="E74" t="str">
-        <v>2/15</v>
+        <v>10/15</v>
       </c>
       <c r="F74" t="str">
-        <v>남동향</v>
+        <v/>
       </c>
       <c r="G74" t="str">
-        <v>깨끗함, 기본상태, 8월말 입주가능</v>
+        <v>부분수리, 깨끗, 수지구청역 초역세권, 편의시설 인접</v>
       </c>
       <c r="H74" t="str">
         <v>naver</v>
@@ -2338,13 +2338,13 @@
         <v>현대</v>
       </c>
       <c r="B75" t="str">
-        <v>9억 7,000</v>
+        <v>11억 8,000</v>
       </c>
       <c r="C75">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="D75" t="str">
-        <v>101동</v>
+        <v>105동</v>
       </c>
       <c r="E75" t="str">
         <v>9/15</v>
@@ -2353,7 +2353,7 @@
         <v>남동향</v>
       </c>
       <c r="G75" t="str">
-        <v>예전수리된집, 10월말 입주가능</v>
+        <v xml:space="preserve"> 입주 로열동 좋은 집 수지구청역5분 생활인프라 최고 </v>
       </c>
       <c r="H75" t="str">
         <v>naver</v>
@@ -2364,48 +2364,48 @@
         <v>현대</v>
       </c>
       <c r="B76" t="str">
-        <v>11억</v>
-      </c>
-      <c r="C76">
+        <v>11억 6,000</v>
+      </c>
+      <c r="C76" t="str">
         <v>104</v>
       </c>
       <c r="D76" t="str">
-        <v>104동</v>
+        <v>108동</v>
       </c>
       <c r="E76" t="str">
-        <v>1/15</v>
+        <v>저층</v>
       </c>
       <c r="F76" t="str">
-        <v>남서향</v>
+        <v/>
       </c>
       <c r="G76" t="str">
-        <v>세안고, 아이 키우기 좋아요. 동간 거리 넓고 조용한 동</v>
+        <v>수지구청역 도보 5분 초역세권, 올리모델링, 살기좋은동네</v>
       </c>
       <c r="H76" t="str">
-        <v>naver</v>
+        <v>asil</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>현대</v>
+        <v>동부</v>
       </c>
       <c r="B77" t="str">
-        <v>12억</v>
+        <v>8억 5,000</v>
       </c>
       <c r="C77">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D77" t="str">
-        <v>112동</v>
+        <v>105동</v>
       </c>
       <c r="E77" t="str">
-        <v>3/15</v>
+        <v>17/17</v>
       </c>
       <c r="F77" t="str">
         <v>남동향</v>
       </c>
       <c r="G77" t="str">
-        <v>정상입주 입주일협의 수지구청역 초역세권</v>
+        <v xml:space="preserve">방3 리모델링 사업 진행중 입주일협의 </v>
       </c>
       <c r="H77" t="str">
         <v>naver</v>
@@ -2413,25 +2413,25 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>현대</v>
+        <v>동부</v>
       </c>
       <c r="B78" t="str">
-        <v>12억</v>
+        <v>10억</v>
       </c>
       <c r="C78">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D78" t="str">
-        <v>105동</v>
+        <v>106동</v>
       </c>
       <c r="E78" t="str">
-        <v>고/15</v>
+        <v>8/17</v>
       </c>
       <c r="F78" t="str">
         <v>남동향</v>
       </c>
       <c r="G78" t="str">
-        <v>입주협의, 내부샷시 교체, 방1확장, 로얄동, 로얄라인</v>
+        <v>협의가능, 투자가치굿, 로얄동, 채광좋음</v>
       </c>
       <c r="H78" t="str">
         <v>naver</v>
@@ -2439,25 +2439,25 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>현대</v>
+        <v>동부</v>
       </c>
       <c r="B79" t="str">
-        <v>12억</v>
+        <v>8억 7,000</v>
       </c>
       <c r="C79">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D79" t="str">
         <v>106동</v>
       </c>
       <c r="E79" t="str">
-        <v>1/15</v>
+        <v>2/17</v>
       </c>
       <c r="F79" t="str">
         <v>남동향</v>
       </c>
       <c r="G79" t="str">
-        <v>내부올수리,정상입주가능, 수지구청역 초역세권, 명문학군</v>
+        <v>방3, 거실확장 및 특올수리, 집상태 최고</v>
       </c>
       <c r="H79" t="str">
         <v>naver</v>
@@ -2465,25 +2465,25 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>현대</v>
+        <v>동부</v>
       </c>
       <c r="B80" t="str">
-        <v>11억</v>
+        <v>8억 8,000</v>
       </c>
       <c r="C80">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D80" t="str">
-        <v>106동</v>
+        <v>103동</v>
       </c>
       <c r="E80" t="str">
-        <v>1/15</v>
+        <v>17/17</v>
       </c>
       <c r="F80" t="str">
-        <v>남향</v>
+        <v>남동향</v>
       </c>
       <c r="G80" t="str">
-        <v>샷쉬교체 및 화장실 씽크대등 내부 올 리모델링</v>
+        <v>최근 샷시포함 특올수리, 거실확장, 신혼부부 거주중</v>
       </c>
       <c r="H80" t="str">
         <v>naver</v>
@@ -2491,25 +2491,25 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>현대</v>
+        <v>동부</v>
       </c>
       <c r="B81" t="str">
-        <v>10억 2,000</v>
+        <v>9억 8,000</v>
       </c>
       <c r="C81">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D81" t="str">
-        <v>101동</v>
+        <v>102동</v>
       </c>
       <c r="E81" t="str">
-        <v>15/15</v>
+        <v>17/17</v>
       </c>
       <c r="F81" t="str">
         <v>남동향</v>
       </c>
       <c r="G81" t="str">
-        <v>깨끗, 정상입주협의, 수지구청역 초역세권, 명문학군,편의시설다양</v>
+        <v>R2, 주인거주, 특올수리, 리모델링 단지</v>
       </c>
       <c r="H81" t="str">
         <v>naver</v>
@@ -2517,25 +2517,25 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>현대</v>
+        <v>동부</v>
       </c>
       <c r="B82" t="str">
-        <v>10억</v>
+        <v>8억 5,000</v>
       </c>
       <c r="C82">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D82" t="str">
-        <v>101동</v>
+        <v>104동</v>
       </c>
       <c r="E82" t="str">
-        <v>14/15</v>
+        <v>2/17</v>
       </c>
       <c r="F82" t="str">
         <v>남동향</v>
       </c>
       <c r="G82" t="str">
-        <v>기본, 긴 잔금, 수지구청 도보8분, 최고 입지의 대단지아파트</v>
+        <v>R2, 주인거주, 올수리, 리모델링 단지</v>
       </c>
       <c r="H82" t="str">
         <v>naver</v>
@@ -2543,25 +2543,25 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>현대</v>
+        <v>동부</v>
       </c>
       <c r="B83" t="str">
-        <v>11억 5,000</v>
+        <v>8억 5,000</v>
       </c>
       <c r="C83">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D83" t="str">
-        <v>109동</v>
+        <v>104동</v>
       </c>
       <c r="E83" t="str">
-        <v>1/15</v>
+        <v>12/17</v>
       </c>
       <c r="F83" t="str">
         <v>남동향</v>
       </c>
       <c r="G83" t="str">
-        <v>빠른입주협의, 방1확장, 도배,데코우드마루, 화장실문교체 및 줄눈시공</v>
+        <v>R2, 주인거주, 올수리, 리모델링 단지</v>
       </c>
       <c r="H83" t="str">
         <v>naver</v>
@@ -2569,25 +2569,25 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>현대</v>
+        <v>동부</v>
       </c>
       <c r="B84" t="str">
-        <v>13억</v>
+        <v>8억 2,000</v>
       </c>
       <c r="C84">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D84" t="str">
-        <v>107동</v>
+        <v>102동</v>
       </c>
       <c r="E84" t="str">
-        <v>중/15</v>
+        <v>8/17</v>
       </c>
       <c r="F84" t="str">
         <v>남동향</v>
       </c>
       <c r="G84" t="str">
-        <v>입주협의, 깨끗, 샷시 제외, 예전수리, 로얄동</v>
+        <v>입주급매 신분당선도보8분 내부수리됨 아파트뒤 도서관 소아병동입점</v>
       </c>
       <c r="H84" t="str">
         <v>naver</v>
@@ -2595,25 +2595,25 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>현대</v>
+        <v>동부</v>
       </c>
       <c r="B85" t="str">
-        <v>12억</v>
+        <v>9억</v>
       </c>
       <c r="C85">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D85" t="str">
-        <v>102동</v>
+        <v>101동</v>
       </c>
       <c r="E85" t="str">
-        <v>5/15</v>
+        <v>6/17</v>
       </c>
       <c r="F85" t="str">
         <v>남동향</v>
       </c>
       <c r="G85" t="str">
-        <v>깨끗, 정상입주협의 수지구청역 초역세권, 명문학군, 편의시설 다양</v>
+        <v>방3 리모델링 입주협의</v>
       </c>
       <c r="H85" t="str">
         <v>naver</v>
@@ -2621,25 +2621,25 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>현대</v>
+        <v>동부</v>
       </c>
       <c r="B86" t="str">
-        <v>11억 5,000</v>
+        <v>9억 2,000</v>
       </c>
       <c r="C86">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D86" t="str">
-        <v>108동</v>
+        <v>105동</v>
       </c>
       <c r="E86" t="str">
-        <v>3/15</v>
+        <v>11/17</v>
       </c>
       <c r="F86" t="str">
         <v>남동향</v>
       </c>
       <c r="G86" t="str">
-        <v>깨끗, 수지구청역 초역세권, 명문학군, 로얄동, 편의시설다양</v>
+        <v>R3, 주인거주, 올수리, 리모델링 단지</v>
       </c>
       <c r="H86" t="str">
         <v>naver</v>
@@ -2647,25 +2647,25 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>현대</v>
+        <v>동부</v>
       </c>
       <c r="B87" t="str">
-        <v>13억</v>
+        <v>8억 5,000</v>
       </c>
       <c r="C87">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D87" t="str">
-        <v>107동</v>
+        <v>101동</v>
       </c>
       <c r="E87" t="str">
-        <v>10/15</v>
+        <v>2/17</v>
       </c>
       <c r="F87" t="str">
-        <v/>
+        <v>남동향</v>
       </c>
       <c r="G87" t="str">
-        <v>부분수리, 깨끗, 수지구청역 초역세권, 편의시설 인접</v>
+        <v>방3 특올수리 거실확장 리모델링 진행중</v>
       </c>
       <c r="H87" t="str">
         <v>naver</v>
@@ -2673,25 +2673,25 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>현대</v>
+        <v>동부</v>
       </c>
       <c r="B88" t="str">
-        <v>11억 8,000</v>
+        <v>8억 5,000</v>
       </c>
       <c r="C88">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D88" t="str">
-        <v>105동</v>
+        <v>103동</v>
       </c>
       <c r="E88" t="str">
-        <v>9/15</v>
+        <v>5/17</v>
       </c>
       <c r="F88" t="str">
         <v>남동향</v>
       </c>
       <c r="G88" t="str">
-        <v xml:space="preserve"> 입주 로열동 좋은 집 수지구청역5분 생활인프라 최고 </v>
+        <v>협의가능 투자가치굿, 도보역세권, 리모델링단지</v>
       </c>
       <c r="H88" t="str">
         <v>naver</v>
@@ -2699,106 +2699,106 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>현대</v>
+        <v>동부</v>
       </c>
       <c r="B89" t="str">
-        <v>11억 6,000</v>
-      </c>
-      <c r="C89" t="str">
-        <v>104</v>
+        <v>8억 7,000</v>
+      </c>
+      <c r="C89">
+        <v>78</v>
       </c>
       <c r="D89" t="str">
-        <v>108동</v>
+        <v>106동</v>
       </c>
       <c r="E89" t="str">
-        <v>저층</v>
+        <v>12/17</v>
       </c>
       <c r="F89" t="str">
-        <v/>
+        <v>남동향</v>
       </c>
       <c r="G89" t="str">
-        <v>수지구청역 도보 5분 초역세권, 올리모델링, 살기좋은동네</v>
+        <v>방3화1, 계단식, 로얄동, 채광좋음</v>
       </c>
       <c r="H89" t="str">
-        <v>asil</v>
+        <v>naver</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>한성</v>
+        <v>동부</v>
       </c>
       <c r="B90" t="str">
-        <v>11억 8,000</v>
-      </c>
-      <c r="C90" t="str">
-        <v>77</v>
+        <v>8억 5,000</v>
+      </c>
+      <c r="C90">
+        <v>78</v>
       </c>
       <c r="D90" t="str">
-        <v>104동</v>
+        <v>106동</v>
       </c>
       <c r="E90" t="str">
-        <v>고층</v>
+        <v>15/17</v>
       </c>
       <c r="F90" t="str">
-        <v/>
+        <v>남동향</v>
       </c>
       <c r="G90" t="str">
-        <v>입주권 승계매물 수지구청역 역세권 신축 선점하세요</v>
+        <v>R3, 주인거주, 로얄층, 리모델링 단지</v>
       </c>
       <c r="H90" t="str">
-        <v>asil</v>
+        <v>naver</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>한성</v>
+        <v>동부</v>
       </c>
       <c r="B91" t="str">
-        <v>13억</v>
-      </c>
-      <c r="C91" t="str">
-        <v>77</v>
+        <v>8억 8,000</v>
+      </c>
+      <c r="C91">
+        <v>78</v>
       </c>
       <c r="D91" t="str">
-        <v>104동</v>
+        <v>106동</v>
       </c>
       <c r="E91" t="str">
-        <v>9층</v>
+        <v>9/17</v>
       </c>
       <c r="F91" t="str">
-        <v/>
+        <v>남동향</v>
       </c>
       <c r="G91" t="str">
-        <v>올수리 정상입주 6월19일입주</v>
+        <v>R3,주인거주,확장 특올수리,리모델링 단지</v>
       </c>
       <c r="H91" t="str">
-        <v>asil</v>
+        <v>naver</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>한성</v>
+        <v>동부</v>
       </c>
       <c r="B92" t="str">
-        <v>12억 5,000</v>
-      </c>
-      <c r="C92" t="str">
-        <v>77</v>
+        <v>8억 7,000</v>
+      </c>
+      <c r="C92">
+        <v>78</v>
       </c>
       <c r="D92" t="str">
         <v>101동</v>
       </c>
       <c r="E92" t="str">
-        <v>중층</v>
+        <v>5/17</v>
       </c>
       <c r="F92" t="str">
-        <v/>
+        <v>남동향</v>
       </c>
       <c r="G92" t="str">
-        <v>역세권 재건축 신축 입주권 선점하세요 조합원 승계 귀한 입주매매</v>
+        <v>R3, 거실 방확장 올수리, 리모델링 단지</v>
       </c>
       <c r="H92" t="str">
-        <v>asil</v>
+        <v>naver</v>
       </c>
     </row>
     <row r="93">
@@ -2812,16 +2812,16 @@
         <v>78</v>
       </c>
       <c r="D93" t="str">
-        <v>104동</v>
+        <v>103동</v>
       </c>
       <c r="E93" t="str">
-        <v>12/17</v>
+        <v>16/17</v>
       </c>
       <c r="F93" t="str">
         <v>남동향</v>
       </c>
       <c r="G93" t="str">
-        <v>R2, 주인거주, 올수리, 리모델링사업진행중</v>
+        <v>R2, 주인거주, 로얄층, 리모델링 단지</v>
       </c>
       <c r="H93" t="str">
         <v>naver</v>
@@ -2832,22 +2832,22 @@
         <v>동부</v>
       </c>
       <c r="B94" t="str">
-        <v>8억 5,000</v>
+        <v>7억 5,000</v>
       </c>
       <c r="C94">
         <v>78</v>
       </c>
       <c r="D94" t="str">
-        <v>103동</v>
+        <v>104동</v>
       </c>
       <c r="E94" t="str">
-        <v>5/17</v>
+        <v>1/17</v>
       </c>
       <c r="F94" t="str">
         <v>남동향</v>
       </c>
       <c r="G94" t="str">
-        <v>협의가능 투자가치굿, 도보역세권, 리모델링단지</v>
+        <v>입주협의  부분수리  방2  리모추진중  초중고 도서관 역세권 메디칼센터</v>
       </c>
       <c r="H94" t="str">
         <v>naver</v>
@@ -2858,13 +2858,13 @@
         <v>동부</v>
       </c>
       <c r="B95" t="str">
-        <v>8억 2,000</v>
+        <v>8억 7,000</v>
       </c>
       <c r="C95">
         <v>78</v>
       </c>
       <c r="D95" t="str">
-        <v>102동</v>
+        <v>106동</v>
       </c>
       <c r="E95" t="str">
         <v>8/17</v>
@@ -2873,7 +2873,7 @@
         <v>남동향</v>
       </c>
       <c r="G95" t="str">
-        <v>입주급매 신분당선도보8분 내부수리됨 아파트뒤 도서관 소아병동입점</v>
+        <v>R3, 로얄층, 올수리,세안고,리모델링 단지</v>
       </c>
       <c r="H95" t="str">
         <v>naver</v>
@@ -2884,22 +2884,22 @@
         <v>동부</v>
       </c>
       <c r="B96" t="str">
-        <v>8억 5,000</v>
+        <v>8억 7,000</v>
       </c>
       <c r="C96">
         <v>78</v>
       </c>
       <c r="D96" t="str">
-        <v>105동</v>
+        <v>106동</v>
       </c>
       <c r="E96" t="str">
-        <v>17/17</v>
+        <v>11/17</v>
       </c>
       <c r="F96" t="str">
         <v>남동향</v>
       </c>
       <c r="G96" t="str">
-        <v xml:space="preserve">방3 리모델링 사업 진행중 입주일협의 </v>
+        <v>R3, 주인거주, 올수리, 리모델링 단지</v>
       </c>
       <c r="H96" t="str">
         <v>naver</v>
@@ -2910,22 +2910,22 @@
         <v>동부</v>
       </c>
       <c r="B97" t="str">
-        <v>9억 8,000</v>
+        <v>9억 2,000</v>
       </c>
       <c r="C97">
         <v>78</v>
       </c>
       <c r="D97" t="str">
-        <v>102동</v>
+        <v>101동</v>
       </c>
       <c r="E97" t="str">
-        <v>17/17</v>
+        <v>8/17</v>
       </c>
       <c r="F97" t="str">
         <v>남동향</v>
       </c>
       <c r="G97" t="str">
-        <v>R2, 주인거주, 특올수리, 리모델링사업진행중</v>
+        <v>방3, 계단식, 샷시포함올수리, 채광좋음</v>
       </c>
       <c r="H97" t="str">
         <v>naver</v>
@@ -2936,22 +2936,22 @@
         <v>동부</v>
       </c>
       <c r="B98" t="str">
-        <v>8억 7,000</v>
+        <v>8억 9,000</v>
       </c>
       <c r="C98">
         <v>78</v>
       </c>
       <c r="D98" t="str">
-        <v>106동</v>
+        <v>105동</v>
       </c>
       <c r="E98" t="str">
-        <v>2/17</v>
+        <v>6/17</v>
       </c>
       <c r="F98" t="str">
         <v>남동향</v>
       </c>
       <c r="G98" t="str">
-        <v>방3, 거실확장 및 특올수리, 집상태 최고</v>
+        <v>방3화1, 특올수리, 채광굿, 도보역세권</v>
       </c>
       <c r="H98" t="str">
         <v>naver</v>
@@ -2962,7 +2962,7 @@
         <v>동부</v>
       </c>
       <c r="B99" t="str">
-        <v>10억</v>
+        <v>8억 5,000</v>
       </c>
       <c r="C99">
         <v>78</v>
@@ -2971,13 +2971,13 @@
         <v>106동</v>
       </c>
       <c r="E99" t="str">
-        <v>8/17</v>
+        <v>6/17</v>
       </c>
       <c r="F99" t="str">
         <v>남동향</v>
       </c>
       <c r="G99" t="str">
-        <v>협의가능, 투자가치굿, 로얄동, 채광좋음</v>
+        <v>방3화1, 올수리, 계단식, 채광좋음</v>
       </c>
       <c r="H99" t="str">
         <v>naver</v>
@@ -2988,22 +2988,22 @@
         <v>동부</v>
       </c>
       <c r="B100" t="str">
-        <v>8억 8,000</v>
+        <v>9억 2,000</v>
       </c>
       <c r="C100">
         <v>78</v>
       </c>
       <c r="D100" t="str">
-        <v>103동</v>
+        <v>101동</v>
       </c>
       <c r="E100" t="str">
-        <v>17/17</v>
+        <v>10/17</v>
       </c>
       <c r="F100" t="str">
         <v>남동향</v>
       </c>
       <c r="G100" t="str">
-        <v>최근 샷시포함 특올수리, 거실확장, 신혼부부 거주중</v>
+        <v>방3화1, 채광좋음, 도보역세권, 일정등협의가능</v>
       </c>
       <c r="H100" t="str">
         <v>naver</v>
@@ -3020,7 +3020,7 @@
         <v>78</v>
       </c>
       <c r="D101" t="str">
-        <v>101동</v>
+        <v>102동</v>
       </c>
       <c r="E101" t="str">
         <v>6/17</v>
@@ -3029,7 +3029,7 @@
         <v>남동향</v>
       </c>
       <c r="G101" t="str">
-        <v>방3 리모델링 입주협의</v>
+        <v>방2화1,  도보역세권, 채광좋음, 수리됨</v>
       </c>
       <c r="H101" t="str">
         <v>naver</v>
@@ -3040,22 +3040,22 @@
         <v>동부</v>
       </c>
       <c r="B102" t="str">
-        <v>8억 5,000</v>
+        <v>9억</v>
       </c>
       <c r="C102">
         <v>78</v>
       </c>
       <c r="D102" t="str">
-        <v>101동</v>
+        <v>105동</v>
       </c>
       <c r="E102" t="str">
-        <v>2/17</v>
+        <v>7/17</v>
       </c>
       <c r="F102" t="str">
         <v>남동향</v>
       </c>
       <c r="G102" t="str">
-        <v>방3 특올수리 거실확장 리모델링 진행중</v>
+        <v>방3화1, 계단식, 방확장, 채광좋음, 도보역세권</v>
       </c>
       <c r="H102" t="str">
         <v>naver</v>
@@ -3066,22 +3066,22 @@
         <v>동부</v>
       </c>
       <c r="B103" t="str">
-        <v>8억 5,000</v>
+        <v>8억 7,000</v>
       </c>
       <c r="C103">
         <v>78</v>
       </c>
       <c r="D103" t="str">
-        <v>104동</v>
+        <v>105동</v>
       </c>
       <c r="E103" t="str">
-        <v>2/17</v>
+        <v>14/17</v>
       </c>
       <c r="F103" t="str">
         <v>남동향</v>
       </c>
       <c r="G103" t="str">
-        <v>R2, 주인거주, 올수리, 리모델링사업진행중</v>
+        <v>방3 계단식,주인거주,로얄층,수리,전철역세권</v>
       </c>
       <c r="H103" t="str">
         <v>naver</v>
@@ -3092,22 +3092,22 @@
         <v>동부</v>
       </c>
       <c r="B104" t="str">
-        <v>9억 2,000</v>
+        <v>9억</v>
       </c>
       <c r="C104">
         <v>78</v>
       </c>
       <c r="D104" t="str">
-        <v>105동</v>
+        <v>101동</v>
       </c>
       <c r="E104" t="str">
-        <v>11/17</v>
+        <v>중/17</v>
       </c>
       <c r="F104" t="str">
         <v>남동향</v>
       </c>
       <c r="G104" t="str">
-        <v>R3, 주인거주,올수리,리모델링사업진행중</v>
+        <v>방3,주인거주,리모델링 이주확정</v>
       </c>
       <c r="H104" t="str">
         <v>naver</v>
@@ -3118,22 +3118,22 @@
         <v>동부</v>
       </c>
       <c r="B105" t="str">
-        <v>8억 5,000</v>
+        <v>8억 3,000</v>
       </c>
       <c r="C105">
         <v>78</v>
       </c>
       <c r="D105" t="str">
-        <v>103동</v>
+        <v>105동</v>
       </c>
       <c r="E105" t="str">
-        <v>16/17</v>
+        <v>중/17</v>
       </c>
       <c r="F105" t="str">
         <v>남동향</v>
       </c>
       <c r="G105" t="str">
-        <v>R2, 계단식,주인거주,로얄층,리모델링추진중</v>
+        <v>꼭팔아요 급매 입주협의 방3  특올수리  초중고 역세권 선호하는동 강추</v>
       </c>
       <c r="H105" t="str">
         <v>naver</v>
@@ -3144,22 +3144,22 @@
         <v>동부</v>
       </c>
       <c r="B106" t="str">
-        <v>8억 8,000</v>
+        <v>8억 7,000</v>
       </c>
       <c r="C106">
         <v>78</v>
       </c>
       <c r="D106" t="str">
-        <v>106동</v>
+        <v>103동</v>
       </c>
       <c r="E106" t="str">
-        <v>9/17</v>
+        <v>고/17</v>
       </c>
       <c r="F106" t="str">
         <v>남동향</v>
       </c>
       <c r="G106" t="str">
-        <v>R3, 계단식,주인거주,확장 특올수리,리모델링추진중</v>
+        <v>방2화1, 계단식, 채광좋음, 도보역세권</v>
       </c>
       <c r="H106" t="str">
         <v>naver</v>
@@ -3170,22 +3170,22 @@
         <v>동부</v>
       </c>
       <c r="B107" t="str">
-        <v>8억 7,000</v>
+        <v>9억</v>
       </c>
       <c r="C107">
         <v>78</v>
       </c>
       <c r="D107" t="str">
-        <v>106동</v>
+        <v>105동</v>
       </c>
       <c r="E107" t="str">
-        <v>8/17</v>
+        <v>고/17</v>
       </c>
       <c r="F107" t="str">
         <v>남동향</v>
       </c>
       <c r="G107" t="str">
-        <v>R3, 로얄층, 올수리,세안고,리모델링추진중</v>
+        <v>샷시 제외 특올수리이며 입주 가능하고 리모델링 추진 단지임</v>
       </c>
       <c r="H107" t="str">
         <v>naver</v>
@@ -3196,22 +3196,22 @@
         <v>동부</v>
       </c>
       <c r="B108" t="str">
-        <v>8억 7,000</v>
+        <v>8억 5,000</v>
       </c>
       <c r="C108">
         <v>78</v>
       </c>
       <c r="D108" t="str">
-        <v>101동</v>
+        <v>105동</v>
       </c>
       <c r="E108" t="str">
-        <v>5/17</v>
+        <v>중/17</v>
       </c>
       <c r="F108" t="str">
         <v>남동향</v>
       </c>
       <c r="G108" t="str">
-        <v>R3, 거실 방확장 올수리, 리모델링추진중</v>
+        <v>입주가능 화장실포함올수리 방3개 수지구청역도보권및도서관인접</v>
       </c>
       <c r="H108" t="str">
         <v>naver</v>
@@ -3222,22 +3222,22 @@
         <v>동부</v>
       </c>
       <c r="B109" t="str">
-        <v>8억 5,000</v>
+        <v>9억 3,000</v>
       </c>
       <c r="C109">
         <v>78</v>
       </c>
       <c r="D109" t="str">
-        <v>106동</v>
+        <v>101동</v>
       </c>
       <c r="E109" t="str">
-        <v>15/17</v>
+        <v>13/17</v>
       </c>
       <c r="F109" t="str">
         <v>남동향</v>
       </c>
       <c r="G109" t="str">
-        <v>R3, 계단식,주인거주, 로얄층, 리모델링추진중</v>
+        <v>협의가능 투자가치굿, 우수인프라, 도보역세권</v>
       </c>
       <c r="H109" t="str">
         <v>naver</v>
@@ -3248,22 +3248,22 @@
         <v>동부</v>
       </c>
       <c r="B110" t="str">
-        <v>8억 7,000</v>
+        <v>9억</v>
       </c>
       <c r="C110">
         <v>78</v>
       </c>
       <c r="D110" t="str">
-        <v>106동</v>
+        <v>102동</v>
       </c>
       <c r="E110" t="str">
-        <v>12/17</v>
+        <v>중/17</v>
       </c>
       <c r="F110" t="str">
         <v>남동향</v>
       </c>
       <c r="G110" t="str">
-        <v>방3화1, 계단식, 로얄동, 채광좋음</v>
+        <v>방2화1, 채광좋음, 올수리, 도보역세권</v>
       </c>
       <c r="H110" t="str">
         <v>naver</v>
@@ -3274,22 +3274,22 @@
         <v>동부</v>
       </c>
       <c r="B111" t="str">
-        <v>7억 5,000</v>
+        <v>8억 6,000</v>
       </c>
       <c r="C111">
         <v>78</v>
       </c>
       <c r="D111" t="str">
-        <v>104동</v>
+        <v>103동</v>
       </c>
       <c r="E111" t="str">
-        <v>1/17</v>
+        <v>중/17</v>
       </c>
       <c r="F111" t="str">
         <v>남동향</v>
       </c>
       <c r="G111" t="str">
-        <v>입주협의  부분수리  방2  리모추진중  초중고 도서관 역세권 메디칼센터</v>
+        <v>방2화1, 로얄동로얄층, 올수리, 채광좋음</v>
       </c>
       <c r="H111" t="str">
         <v>naver</v>
@@ -3300,22 +3300,22 @@
         <v>동부</v>
       </c>
       <c r="B112" t="str">
-        <v>8억 7,000</v>
+        <v>9억</v>
       </c>
       <c r="C112">
         <v>78</v>
       </c>
       <c r="D112" t="str">
-        <v>106동</v>
+        <v>104동</v>
       </c>
       <c r="E112" t="str">
-        <v>11/17</v>
+        <v>고/17</v>
       </c>
       <c r="F112" t="str">
         <v>남동향</v>
       </c>
       <c r="G112" t="str">
-        <v>R3, 계단식,주인거주,올수리,리모델링추진중</v>
+        <v>올수리, 도보역세권, 일정 등 협의가능</v>
       </c>
       <c r="H112" t="str">
         <v>naver</v>
@@ -3326,22 +3326,22 @@
         <v>동부</v>
       </c>
       <c r="B113" t="str">
-        <v>9억 2,000</v>
+        <v>8억 5,000</v>
       </c>
       <c r="C113">
         <v>78</v>
       </c>
       <c r="D113" t="str">
-        <v>101동</v>
+        <v>103동</v>
       </c>
       <c r="E113" t="str">
-        <v>10/17</v>
+        <v>7/17</v>
       </c>
       <c r="F113" t="str">
         <v>남동향</v>
       </c>
       <c r="G113" t="str">
-        <v>방3화1, 채광좋음, 도보역세권, 일정등협의가능</v>
+        <v>깨끗함, 주인거주</v>
       </c>
       <c r="H113" t="str">
         <v>naver</v>
@@ -3352,22 +3352,22 @@
         <v>동부</v>
       </c>
       <c r="B114" t="str">
-        <v>8억 9,000</v>
+        <v>8억 5,000</v>
       </c>
       <c r="C114">
         <v>78</v>
       </c>
       <c r="D114" t="str">
-        <v>105동</v>
+        <v>104동</v>
       </c>
       <c r="E114" t="str">
-        <v>6/17</v>
+        <v>5/17</v>
       </c>
       <c r="F114" t="str">
         <v>남동향</v>
       </c>
       <c r="G114" t="str">
-        <v>방3화1, 특올수리, 채광굿, 도보역세권</v>
+        <v>방2 계단식,주인거주,올수리,전철역 초중고10분내</v>
       </c>
       <c r="H114" t="str">
         <v>naver</v>
@@ -3378,22 +3378,22 @@
         <v>동부</v>
       </c>
       <c r="B115" t="str">
-        <v>8억 5,000</v>
+        <v>9억</v>
       </c>
       <c r="C115">
         <v>78</v>
       </c>
       <c r="D115" t="str">
-        <v>106동</v>
+        <v>102동</v>
       </c>
       <c r="E115" t="str">
-        <v>6/17</v>
+        <v>16/17</v>
       </c>
       <c r="F115" t="str">
         <v>남동향</v>
       </c>
       <c r="G115" t="str">
-        <v>방3화1, 올수리, 계단식, 채광좋음</v>
+        <v>방2 계단식,주인거주,올수리,전철역 초중고10분내</v>
       </c>
       <c r="H115" t="str">
         <v>naver</v>
@@ -3404,22 +3404,22 @@
         <v>동부</v>
       </c>
       <c r="B116" t="str">
-        <v>9억</v>
+        <v>8억 3,000</v>
       </c>
       <c r="C116">
         <v>78</v>
       </c>
       <c r="D116" t="str">
-        <v>102동</v>
+        <v>104동</v>
       </c>
       <c r="E116" t="str">
-        <v>6/17</v>
+        <v>5/17</v>
       </c>
       <c r="F116" t="str">
         <v>남동향</v>
       </c>
       <c r="G116" t="str">
-        <v>방2화1,  도보역세권, 채광좋음, 수리됨</v>
+        <v>입주협의 내부샤시교체 올수리 리모델링추진중 수지구청역 명문초중고</v>
       </c>
       <c r="H116" t="str">
         <v>naver</v>
@@ -3430,13 +3430,13 @@
         <v>동부</v>
       </c>
       <c r="B117" t="str">
-        <v>9억 2,000</v>
+        <v>8억 7,000</v>
       </c>
       <c r="C117">
         <v>78</v>
       </c>
       <c r="D117" t="str">
-        <v>101동</v>
+        <v>104동</v>
       </c>
       <c r="E117" t="str">
         <v>8/17</v>
@@ -3445,7 +3445,7 @@
         <v>남동향</v>
       </c>
       <c r="G117" t="str">
-        <v>방3, 계단식, 샷시포함올수리, 채광좋음</v>
+        <v>즉시 입주 가능 올수리 깔끔한 매매입니다</v>
       </c>
       <c r="H117" t="str">
         <v>naver</v>
@@ -3456,22 +3456,22 @@
         <v>동부</v>
       </c>
       <c r="B118" t="str">
-        <v>9억</v>
+        <v>9억 5,000</v>
       </c>
       <c r="C118">
         <v>78</v>
       </c>
       <c r="D118" t="str">
-        <v>105동</v>
+        <v>106동</v>
       </c>
       <c r="E118" t="str">
-        <v>7/17</v>
+        <v>중/17</v>
       </c>
       <c r="F118" t="str">
         <v>남동향</v>
       </c>
       <c r="G118" t="str">
-        <v>방3화1, 계단식, 방확장, 채광좋음, 도보역세권</v>
+        <v>조합승계 입주협의 방3 특올수리 초중고 메디컬센터 도서관 역세권등</v>
       </c>
       <c r="H118" t="str">
         <v>naver</v>
@@ -3482,22 +3482,22 @@
         <v>동부</v>
       </c>
       <c r="B119" t="str">
-        <v>8억 3,000</v>
+        <v>8억 2,000</v>
       </c>
       <c r="C119">
         <v>78</v>
       </c>
       <c r="D119" t="str">
-        <v>102동</v>
+        <v>103동</v>
       </c>
       <c r="E119" t="str">
-        <v>2/17</v>
+        <v>1/17</v>
       </c>
       <c r="F119" t="str">
         <v>남동향</v>
       </c>
       <c r="G119" t="str">
-        <v>방2 계단식,주인거주,올수리,역세권</v>
+        <v>세안고,  샷시포함 올수리</v>
       </c>
       <c r="H119" t="str">
         <v>naver</v>
@@ -3508,22 +3508,22 @@
         <v>동부</v>
       </c>
       <c r="B120" t="str">
-        <v>8억 7,000</v>
+        <v>9억 5,000</v>
       </c>
       <c r="C120">
         <v>78</v>
       </c>
       <c r="D120" t="str">
-        <v>105동</v>
+        <v>106동</v>
       </c>
       <c r="E120" t="str">
-        <v>14/17</v>
+        <v>9/17</v>
       </c>
       <c r="F120" t="str">
         <v>남동향</v>
       </c>
       <c r="G120" t="str">
-        <v>방3 계단식,주인거주,로얄층,수리,전철역세권</v>
+        <v>입주 협의 리모델링 추진단지 방3개 올수리 깨끗</v>
       </c>
       <c r="H120" t="str">
         <v>naver</v>
@@ -3534,22 +3534,22 @@
         <v>동부</v>
       </c>
       <c r="B121" t="str">
-        <v>9억 3,000</v>
+        <v>8억 3,000</v>
       </c>
       <c r="C121">
         <v>78</v>
       </c>
       <c r="D121" t="str">
-        <v>101동</v>
+        <v>106동</v>
       </c>
       <c r="E121" t="str">
-        <v>13/17</v>
+        <v>고/17</v>
       </c>
       <c r="F121" t="str">
         <v>남동향</v>
       </c>
       <c r="G121" t="str">
-        <v>협의가능 투자가치굿, 우수인프라, 도보역세권</v>
+        <v xml:space="preserve">조합세대 세안고 급매매 로얄동 </v>
       </c>
       <c r="H121" t="str">
         <v>naver</v>
@@ -3560,22 +3560,22 @@
         <v>동부</v>
       </c>
       <c r="B122" t="str">
-        <v>8억 3,000</v>
+        <v>9억</v>
       </c>
       <c r="C122">
         <v>78</v>
       </c>
       <c r="D122" t="str">
-        <v>105동</v>
+        <v>103동</v>
       </c>
       <c r="E122" t="str">
-        <v>중/17</v>
+        <v>7/17</v>
       </c>
       <c r="F122" t="str">
         <v>남동향</v>
       </c>
       <c r="G122" t="str">
-        <v>꼭팔아요 급매 입주협의 방3  특올수리  초중고 역세권 선호하는동 강추</v>
+        <v>방2, 수리깨끗, 정상입주가능, 수지구청역 역세권, 로얄층, 명문학군</v>
       </c>
       <c r="H122" t="str">
         <v>naver</v>
@@ -3592,16 +3592,16 @@
         <v>78</v>
       </c>
       <c r="D123" t="str">
-        <v>101동</v>
+        <v>106동</v>
       </c>
       <c r="E123" t="str">
-        <v>중/17</v>
+        <v>7/17</v>
       </c>
       <c r="F123" t="str">
         <v>남동향</v>
       </c>
       <c r="G123" t="str">
-        <v>방3,주인거주,리모델링 이주확정</v>
+        <v>방3 계단식,주인거주,로얄층,수리,전철역세권</v>
       </c>
       <c r="H123" t="str">
         <v>naver</v>
@@ -3612,13 +3612,13 @@
         <v>동부</v>
       </c>
       <c r="B124" t="str">
-        <v>8억 7,000</v>
+        <v>8억 5,000</v>
       </c>
       <c r="C124">
         <v>78</v>
       </c>
       <c r="D124" t="str">
-        <v>103동</v>
+        <v>101동</v>
       </c>
       <c r="E124" t="str">
         <v>고/17</v>
@@ -3627,7 +3627,7 @@
         <v>남동향</v>
       </c>
       <c r="G124" t="str">
-        <v>방2화1, 계단식, 채광좋음, 도보역세권</v>
+        <v>방3 계단식,올수리,전망, 전철역세권</v>
       </c>
       <c r="H124" t="str">
         <v>naver</v>
@@ -3644,16 +3644,16 @@
         <v>78</v>
       </c>
       <c r="D125" t="str">
-        <v>105동</v>
+        <v>102동</v>
       </c>
       <c r="E125" t="str">
-        <v>중/17</v>
+        <v>저/17</v>
       </c>
       <c r="F125" t="str">
         <v>남동향</v>
       </c>
       <c r="G125" t="str">
-        <v>입주가능 화장실포함올수리 방3개 수지구청역도보권및도서관인접</v>
+        <v>입주협의거실확장 샤시일부교체 리모추진중 역세권 초중고인접 도서관 메디컬외</v>
       </c>
       <c r="H125" t="str">
         <v>naver</v>
@@ -3664,7 +3664,7 @@
         <v>동부</v>
       </c>
       <c r="B126" t="str">
-        <v>9억</v>
+        <v>9억 3,000</v>
       </c>
       <c r="C126">
         <v>78</v>
@@ -3673,13 +3673,13 @@
         <v>105동</v>
       </c>
       <c r="E126" t="str">
-        <v>고/17</v>
+        <v>중/17</v>
       </c>
       <c r="F126" t="str">
         <v>남동향</v>
       </c>
       <c r="G126" t="str">
-        <v>샷시 제외 특올수리이며 입주 가능하고 리모델링 추진 단지임</v>
+        <v>입주협의 방3  최근올수리 초중고인접 도서관 메디칼센터 역세권 공원인접</v>
       </c>
       <c r="H126" t="str">
         <v>naver</v>
@@ -3690,22 +3690,22 @@
         <v>동부</v>
       </c>
       <c r="B127" t="str">
-        <v>9억</v>
+        <v>8억 2,000</v>
       </c>
       <c r="C127">
         <v>78</v>
       </c>
       <c r="D127" t="str">
-        <v>102동</v>
+        <v>103동</v>
       </c>
       <c r="E127" t="str">
-        <v>중/17</v>
+        <v>17/17</v>
       </c>
       <c r="F127" t="str">
         <v>남동향</v>
       </c>
       <c r="G127" t="str">
-        <v>방2화1, 채광좋음, 올수리, 도보역세권</v>
+        <v>깨끗함, 주인거주</v>
       </c>
       <c r="H127" t="str">
         <v>naver</v>
@@ -3716,22 +3716,22 @@
         <v>동부</v>
       </c>
       <c r="B128" t="str">
-        <v>8억 6,000</v>
+        <v>8억 5,000</v>
       </c>
       <c r="C128">
         <v>78</v>
       </c>
       <c r="D128" t="str">
-        <v>103동</v>
+        <v>104동</v>
       </c>
       <c r="E128" t="str">
-        <v>중/17</v>
+        <v>3/17</v>
       </c>
       <c r="F128" t="str">
         <v>남동향</v>
       </c>
       <c r="G128" t="str">
-        <v>방2화1, 로얄동로얄층, 올수리, 채광좋음</v>
+        <v>깨끗함, 기본상태, 주인거주 정상입주</v>
       </c>
       <c r="H128" t="str">
         <v>naver</v>
@@ -3751,13 +3751,13 @@
         <v>104동</v>
       </c>
       <c r="E129" t="str">
-        <v>고/17</v>
+        <v>중/17</v>
       </c>
       <c r="F129" t="str">
         <v>남동향</v>
       </c>
       <c r="G129" t="str">
-        <v>올수리, 도보역세권, 일정 등 협의가능</v>
+        <v>방2 계단식,주인거주,올수리,로얄층,역세권</v>
       </c>
       <c r="H129" t="str">
         <v>naver</v>
@@ -3768,22 +3768,22 @@
         <v>동부</v>
       </c>
       <c r="B130" t="str">
-        <v>8억 5,000</v>
+        <v>9억 3,000</v>
       </c>
       <c r="C130">
         <v>78</v>
       </c>
       <c r="D130" t="str">
-        <v>103동</v>
+        <v>104동</v>
       </c>
       <c r="E130" t="str">
-        <v>7/17</v>
+        <v>중/17</v>
       </c>
       <c r="F130" t="str">
         <v>남동향</v>
       </c>
       <c r="G130" t="str">
-        <v>깨끗함, 주인거주</v>
+        <v>입주협의, 방2개, 관리잘된집, 리모델링추진중, 수지구청역 도보10분</v>
       </c>
       <c r="H130" t="str">
         <v>naver</v>
@@ -3794,7 +3794,7 @@
         <v>동부</v>
       </c>
       <c r="B131" t="str">
-        <v>9억</v>
+        <v>8억 9,000</v>
       </c>
       <c r="C131">
         <v>78</v>
@@ -3803,13 +3803,13 @@
         <v>102동</v>
       </c>
       <c r="E131" t="str">
-        <v>16/17</v>
+        <v>중/17</v>
       </c>
       <c r="F131" t="str">
         <v>남동향</v>
       </c>
       <c r="G131" t="str">
-        <v>방2 계단식,주인거주,올수리,전철역 초중고10분내</v>
+        <v xml:space="preserve">세안고 로얄동로얄층 화이트올수리 리모델링추진단지 </v>
       </c>
       <c r="H131" t="str">
         <v>naver</v>
@@ -3820,7 +3820,7 @@
         <v>동부</v>
       </c>
       <c r="B132" t="str">
-        <v>8억 5,000</v>
+        <v>8억 9,000</v>
       </c>
       <c r="C132">
         <v>78</v>
@@ -3829,13 +3829,13 @@
         <v>104동</v>
       </c>
       <c r="E132" t="str">
-        <v>5/17</v>
+        <v>7/17</v>
       </c>
       <c r="F132" t="str">
         <v>남동향</v>
       </c>
       <c r="G132" t="str">
-        <v>방2 계단식,주인거주,올수리,전철역 초중고10분내</v>
+        <v>내부수리 도배깨끗 즉시입주 입주일자유선택가능 앞뒤전망트임</v>
       </c>
       <c r="H132" t="str">
         <v>naver</v>
@@ -3846,22 +3846,22 @@
         <v>동부</v>
       </c>
       <c r="B133" t="str">
-        <v>8억 3,000</v>
+        <v>9억 5,000</v>
       </c>
       <c r="C133">
         <v>78</v>
       </c>
       <c r="D133" t="str">
-        <v>104동</v>
+        <v>102동</v>
       </c>
       <c r="E133" t="str">
-        <v>5/17</v>
+        <v>12/17</v>
       </c>
       <c r="F133" t="str">
         <v>남동향</v>
       </c>
       <c r="G133" t="str">
-        <v>입주협의 내부샤시교체 올수리 리모델링추진중 수지구청역 명문초중고</v>
+        <v>기본상태, 주인거주</v>
       </c>
       <c r="H133" t="str">
         <v>naver</v>
@@ -3872,22 +3872,22 @@
         <v>동부</v>
       </c>
       <c r="B134" t="str">
-        <v>8억 7,000</v>
+        <v>9억 2,000</v>
       </c>
       <c r="C134">
         <v>78</v>
       </c>
       <c r="D134" t="str">
-        <v>104동</v>
+        <v>101동</v>
       </c>
       <c r="E134" t="str">
-        <v>8/17</v>
+        <v>고/17</v>
       </c>
       <c r="F134" t="str">
         <v>남동향</v>
       </c>
       <c r="G134" t="str">
-        <v>즉시 입주 가능 올수리 깔끔한 매매입니다</v>
+        <v>강추 로얄동로얄층  최근특급올수리 방3 화1 전망최고 채광 일조량최고</v>
       </c>
       <c r="H134" t="str">
         <v>naver</v>
@@ -3898,7 +3898,7 @@
         <v>동부</v>
       </c>
       <c r="B135" t="str">
-        <v>9억 5,000</v>
+        <v>8억 4,000</v>
       </c>
       <c r="C135">
         <v>78</v>
@@ -3907,13 +3907,13 @@
         <v>106동</v>
       </c>
       <c r="E135" t="str">
-        <v>중/17</v>
+        <v>고/17</v>
       </c>
       <c r="F135" t="str">
         <v>남동향</v>
       </c>
       <c r="G135" t="str">
-        <v>조합승계 입주협의 방3 특올수리 초중고 메디컬센터 도서관 역세권등</v>
+        <v>동부</v>
       </c>
       <c r="H135" t="str">
         <v>naver</v>
@@ -3924,22 +3924,22 @@
         <v>동부</v>
       </c>
       <c r="B136" t="str">
-        <v>8억 2,000</v>
+        <v>8억 7,000</v>
       </c>
       <c r="C136">
         <v>78</v>
       </c>
       <c r="D136" t="str">
-        <v>103동</v>
+        <v>106동</v>
       </c>
       <c r="E136" t="str">
-        <v>1/17</v>
+        <v>고/17</v>
       </c>
       <c r="F136" t="str">
         <v>남동향</v>
       </c>
       <c r="G136" t="str">
-        <v>세안고,  샷시포함 올수리</v>
+        <v>동부</v>
       </c>
       <c r="H136" t="str">
         <v>naver</v>
@@ -3950,22 +3950,22 @@
         <v>동부</v>
       </c>
       <c r="B137" t="str">
-        <v>9억 5,000</v>
+        <v>9억</v>
       </c>
       <c r="C137">
         <v>78</v>
       </c>
       <c r="D137" t="str">
-        <v>106동</v>
+        <v>102동</v>
       </c>
       <c r="E137" t="str">
-        <v>9/17</v>
+        <v>고/17</v>
       </c>
       <c r="F137" t="str">
         <v>남동향</v>
       </c>
       <c r="G137" t="str">
-        <v>입주 협의 리모델링 추진단지 방3개 올수리 깨끗</v>
+        <v>방3 계단식, 주인거주,올수리,전철역세권</v>
       </c>
       <c r="H137" t="str">
         <v>naver</v>
@@ -3982,16 +3982,16 @@
         <v>78</v>
       </c>
       <c r="D138" t="str">
-        <v>106동</v>
+        <v>103동</v>
       </c>
       <c r="E138" t="str">
-        <v>고/17</v>
+        <v>중/17</v>
       </c>
       <c r="F138" t="str">
         <v>남동향</v>
       </c>
       <c r="G138" t="str">
-        <v xml:space="preserve">조합세대 세안고 급매매 로얄동 </v>
+        <v>입주 내부수리 신분당선도보 8분  쾌적한 단지 살기좋아요</v>
       </c>
       <c r="H138" t="str">
         <v>naver</v>
@@ -4002,59 +4002,60 @@
         <v>동부</v>
       </c>
       <c r="B139" t="str">
-        <v>9억</v>
+        <v>8억 5,000</v>
       </c>
       <c r="C139">
         <v>78</v>
       </c>
       <c r="D139" t="str">
-        <v>103동</v>
+        <v>105동</v>
       </c>
       <c r="E139" t="str">
-        <v>7/17</v>
+        <v>고/17</v>
       </c>
       <c r="F139" t="str">
-        <v>남동향</v>
+        <v/>
       </c>
       <c r="G139" t="str">
-        <v>방2, 수리깨끗, 정상입주가능, 수지구청역 역세권, 로얄층, 명문학군</v>
+        <v>조합세대 리모델링 사업진행 탑층 입주가능매매</v>
       </c>
       <c r="H139" t="str">
         <v>naver</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" xml:space="preserve">
       <c r="A140" t="str">
         <v>동부</v>
       </c>
       <c r="B140" t="str">
-        <v>8억 5,000</v>
+        <v>8억 7,000</v>
       </c>
       <c r="C140">
         <v>78</v>
       </c>
       <c r="D140" t="str">
-        <v>102동</v>
+        <v>104동</v>
       </c>
       <c r="E140" t="str">
-        <v>저/17</v>
+        <v>중/17</v>
       </c>
       <c r="F140" t="str">
-        <v>남동향</v>
-      </c>
-      <c r="G140" t="str">
-        <v>입주협의거실확장 샤시일부교체 리모추진중 역세권 초중고인접 도서관 메디컬외</v>
+        <v/>
+      </c>
+      <c r="G140" t="str" xml:space="preserve">
+        <v xml:space="preserve">주인 거주중이며 입주 가능하고 올수리 깔끔한 매매입니다_x000d_
+</v>
       </c>
       <c r="H140" t="str">
         <v>naver</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" xml:space="preserve">
       <c r="A141" t="str">
         <v>동부</v>
       </c>
       <c r="B141" t="str">
-        <v>9억 3,000</v>
+        <v>9억 5,000</v>
       </c>
       <c r="C141">
         <v>78</v>
@@ -4063,13 +4064,14 @@
         <v>105동</v>
       </c>
       <c r="E141" t="str">
-        <v>중/17</v>
+        <v>6/17</v>
       </c>
       <c r="F141" t="str">
         <v>남동향</v>
       </c>
-      <c r="G141" t="str">
-        <v>입주협의 방3  최근올수리 초중고인접 도서관 메디칼센터 역세권 공원인접</v>
+      <c r="G141" t="str" xml:space="preserve">
+        <v xml:space="preserve">샷시포함 특올수리이며 입주 가능한 매매입니다_x000d_
+</v>
       </c>
       <c r="H141" t="str">
         <v>naver</v>
@@ -4080,22 +4082,22 @@
         <v>동부</v>
       </c>
       <c r="B142" t="str">
-        <v>8억 5,000</v>
+        <v>8억 9,000</v>
       </c>
       <c r="C142">
         <v>78</v>
       </c>
       <c r="D142" t="str">
-        <v>101동</v>
+        <v>105동</v>
       </c>
       <c r="E142" t="str">
-        <v>고/17</v>
+        <v>9/17</v>
       </c>
       <c r="F142" t="str">
         <v>남동향</v>
       </c>
       <c r="G142" t="str">
-        <v>방3 계단식,올수리,전망, 전철역세권</v>
+        <v>올수리이며 입주 가능한 매매입니다</v>
       </c>
       <c r="H142" t="str">
         <v>naver</v>
@@ -4106,48 +4108,48 @@
         <v>동부</v>
       </c>
       <c r="B143" t="str">
-        <v>9억</v>
-      </c>
-      <c r="C143">
-        <v>78</v>
+        <v>8억 9,000</v>
+      </c>
+      <c r="C143" t="str">
+        <v>155</v>
       </c>
       <c r="D143" t="str">
-        <v>106동</v>
+        <v>101동</v>
       </c>
       <c r="E143" t="str">
-        <v>7/17</v>
+        <v>고층</v>
       </c>
       <c r="F143" t="str">
-        <v>남동향</v>
+        <v/>
       </c>
       <c r="G143" t="str">
-        <v>방3 계단식,주인거주,로얄층,수리,전철역세권</v>
+        <v>싱크대 수리되어 있으며 햇살 따뜻한 집이에요.</v>
       </c>
       <c r="H143" t="str">
-        <v>naver</v>
+        <v>asil</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>동부</v>
+        <v>동보</v>
       </c>
       <c r="B144" t="str">
-        <v>8억 2,000</v>
+        <v>12억</v>
       </c>
       <c r="C144">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="D144" t="str">
-        <v>103동</v>
+        <v>105동</v>
       </c>
       <c r="E144" t="str">
-        <v>17/17</v>
+        <v>8/17</v>
       </c>
       <c r="F144" t="str">
-        <v>남동향</v>
+        <v>남향</v>
       </c>
       <c r="G144" t="str">
-        <v>깨끗함, 주인거주</v>
+        <v>27.10입주세안고,전체나무마루포함내부올수리,수지구청6분,최강학군상권</v>
       </c>
       <c r="H144" t="str">
         <v>naver</v>
@@ -4155,25 +4157,25 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>동부</v>
+        <v>동보</v>
       </c>
       <c r="B145" t="str">
-        <v>8억 5,000</v>
+        <v>12억</v>
       </c>
       <c r="C145">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="D145" t="str">
-        <v>104동</v>
+        <v>105동</v>
       </c>
       <c r="E145" t="str">
-        <v>3/17</v>
+        <v>7/17</v>
       </c>
       <c r="F145" t="str">
-        <v>남동향</v>
+        <v>남향</v>
       </c>
       <c r="G145" t="str">
-        <v>깨끗함, 기본상태, 주인거주 정상입주</v>
+        <v>H .햇살좋은 남향 방4 깨끗관리 교육환경최상 수지구청역</v>
       </c>
       <c r="H145" t="str">
         <v>naver</v>
@@ -4181,25 +4183,25 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>동부</v>
+        <v>동보</v>
       </c>
       <c r="B146" t="str">
-        <v>9억</v>
+        <v>12억</v>
       </c>
       <c r="C146">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="D146" t="str">
-        <v>104동</v>
+        <v>102동</v>
       </c>
       <c r="E146" t="str">
-        <v>중/17</v>
+        <v>12/17</v>
       </c>
       <c r="F146" t="str">
-        <v>남동향</v>
+        <v>남향</v>
       </c>
       <c r="G146" t="str">
-        <v>방2 계단식,주인거주,올수리,로얄층,역세권</v>
+        <v>41. 7월만기 세안고 햇살가득한집 관리잘된집</v>
       </c>
       <c r="H146" t="str">
         <v>naver</v>
@@ -4207,25 +4209,25 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>동부</v>
+        <v>동보</v>
       </c>
       <c r="B147" t="str">
-        <v>9억 3,000</v>
+        <v>12억 4,000</v>
       </c>
       <c r="C147">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="D147" t="str">
-        <v>104동</v>
+        <v>102동</v>
       </c>
       <c r="E147" t="str">
-        <v>중/17</v>
+        <v>11/17</v>
       </c>
       <c r="F147" t="str">
-        <v>남동향</v>
+        <v>남향</v>
       </c>
       <c r="G147" t="str">
-        <v>입주협의, 방2개, 관리잘된집, 리모델링추진중, 수지구청역 도보10분</v>
+        <v>과거올수리,주인거주,최상뷰굿,수지구청역6분,재건축이슈,최강교통학군상권</v>
       </c>
       <c r="H147" t="str">
         <v>naver</v>
@@ -4233,25 +4235,25 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>동부</v>
+        <v>동보</v>
       </c>
       <c r="B148" t="str">
-        <v>8억 9,000</v>
+        <v>10억 8,000</v>
       </c>
       <c r="C148">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="D148" t="str">
-        <v>102동</v>
+        <v>101동</v>
       </c>
       <c r="E148" t="str">
-        <v>중/17</v>
+        <v>1/17</v>
       </c>
       <c r="F148" t="str">
-        <v>남동향</v>
+        <v>남향</v>
       </c>
       <c r="G148" t="str">
-        <v xml:space="preserve">세안고 로얄동로얄층 화이트올수리 리모델링추진단지 </v>
+        <v>초역세권 수지구청역도보 방4개 기본깨끗 입주일협의</v>
       </c>
       <c r="H148" t="str">
         <v>naver</v>
@@ -4259,25 +4261,25 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>동부</v>
+        <v>동보</v>
       </c>
       <c r="B149" t="str">
-        <v>9억 5,000</v>
+        <v>12억</v>
       </c>
       <c r="C149">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="D149" t="str">
-        <v>102동</v>
+        <v>101동</v>
       </c>
       <c r="E149" t="str">
-        <v>12/17</v>
+        <v>8/17</v>
       </c>
       <c r="F149" t="str">
-        <v>남동향</v>
+        <v>남향</v>
       </c>
       <c r="G149" t="str">
-        <v>기본상태, 주인거주</v>
+        <v>세안고매매,6년전샤시포함 잘 올수리된집,수지구청역6분,최강교통학군상권</v>
       </c>
       <c r="H149" t="str">
         <v>naver</v>
@@ -4285,25 +4287,25 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>동부</v>
+        <v>동보</v>
       </c>
       <c r="B150" t="str">
-        <v>8억 9,000</v>
+        <v>12억</v>
       </c>
       <c r="C150">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="D150" t="str">
-        <v>104동</v>
+        <v>103동</v>
       </c>
       <c r="E150" t="str">
-        <v>7/17</v>
+        <v>중/17</v>
       </c>
       <c r="F150" t="str">
-        <v>남동향</v>
+        <v>남향</v>
       </c>
       <c r="G150" t="str">
-        <v>내부수리 도배깨끗 즉시입주 입주일자유선택가능 앞뒤전망트임</v>
+        <v>기본,방4,정상입주,초역세권,학세권,해잘드는 정남향집</v>
       </c>
       <c r="H150" t="str">
         <v>naver</v>
@@ -4311,25 +4313,25 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>동부</v>
+        <v>동보</v>
       </c>
       <c r="B151" t="str">
-        <v>9억 2,000</v>
+        <v>12억</v>
       </c>
       <c r="C151">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="D151" t="str">
-        <v>101동</v>
+        <v>105동</v>
       </c>
       <c r="E151" t="str">
-        <v>고/17</v>
+        <v>2/17</v>
       </c>
       <c r="F151" t="str">
-        <v>남동향</v>
+        <v>남향</v>
       </c>
       <c r="G151" t="str">
-        <v>강추 로얄동로얄층  최근특급올수리 방3 화1 전망최고 채광 일조량최고</v>
+        <v>동보</v>
       </c>
       <c r="H151" t="str">
         <v>naver</v>
@@ -4337,25 +4339,25 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>동부</v>
+        <v>동보</v>
       </c>
       <c r="B152" t="str">
-        <v>8억 4,000</v>
+        <v>12억</v>
       </c>
       <c r="C152">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="D152" t="str">
-        <v>106동</v>
+        <v>101동</v>
       </c>
       <c r="E152" t="str">
-        <v>고/17</v>
+        <v>4/17</v>
       </c>
       <c r="F152" t="str">
-        <v>남동향</v>
+        <v>남향</v>
       </c>
       <c r="G152" t="str">
-        <v>동부</v>
+        <v>화장실2개 주방 수리,재건축이슈,정남,교통학군상권,수지구청역세권</v>
       </c>
       <c r="H152" t="str">
         <v>naver</v>
@@ -4363,25 +4365,25 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>동부</v>
+        <v>동보</v>
       </c>
       <c r="B153" t="str">
-        <v>8억 7,000</v>
+        <v>11억</v>
       </c>
       <c r="C153">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="D153" t="str">
-        <v>106동</v>
+        <v>105동</v>
       </c>
       <c r="E153" t="str">
-        <v>고/17</v>
+        <v>6/17</v>
       </c>
       <c r="F153" t="str">
-        <v>남동향</v>
+        <v>남향</v>
       </c>
       <c r="G153" t="str">
-        <v>동부</v>
+        <v>동보</v>
       </c>
       <c r="H153" t="str">
         <v>naver</v>
@@ -4389,25 +4391,25 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>동부</v>
+        <v>동보</v>
       </c>
       <c r="B154" t="str">
-        <v>9억</v>
+        <v>12억 5,000</v>
       </c>
       <c r="C154">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="D154" t="str">
         <v>102동</v>
       </c>
       <c r="E154" t="str">
-        <v>고/17</v>
+        <v>11/17</v>
       </c>
       <c r="F154" t="str">
-        <v>남동향</v>
+        <v>남향</v>
       </c>
       <c r="G154" t="str">
-        <v>방3 계단식, 주인거주,올수리,전철역세권</v>
+        <v>추천, 샷시포함 올수리, 방1확장, 주인거주, 깨끗관리, 풍부한일조량</v>
       </c>
       <c r="H154" t="str">
         <v>naver</v>
@@ -4415,25 +4417,25 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>동부</v>
+        <v>동보</v>
       </c>
       <c r="B155" t="str">
-        <v>8억 3,000</v>
+        <v>12억</v>
       </c>
       <c r="C155">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="D155" t="str">
-        <v>103동</v>
+        <v>105동</v>
       </c>
       <c r="E155" t="str">
-        <v>중/17</v>
+        <v>15/17</v>
       </c>
       <c r="F155" t="str">
-        <v>남동향</v>
+        <v>남향</v>
       </c>
       <c r="G155" t="str">
-        <v>입주 내부수리 신분당선도보 8분  쾌적한 단지 살기좋아요</v>
+        <v>뷰가 잘나오는 맨 앞동 로얄동 로얄층</v>
       </c>
       <c r="H155" t="str">
         <v>naver</v>
@@ -4441,79 +4443,77 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>동부</v>
+        <v>동천마을현대홈타운1차</v>
       </c>
       <c r="B156" t="str">
-        <v>8억 5,000</v>
+        <v>10억 9,000</v>
       </c>
       <c r="C156">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="D156" t="str">
-        <v>105동</v>
+        <v>104동</v>
       </c>
       <c r="E156" t="str">
-        <v>고/17</v>
+        <v>23/25</v>
       </c>
       <c r="F156" t="str">
-        <v/>
+        <v>남향</v>
       </c>
       <c r="G156" t="str">
-        <v>조합세대 리모델링 사업진행 탑층 입주가능매매</v>
+        <v>역세권 단지 탁트인 전망의 엘베 연결 로얄동 입주 정상 협의</v>
       </c>
       <c r="H156" t="str">
         <v>naver</v>
       </c>
     </row>
-    <row r="157" xml:space="preserve">
+    <row r="157">
       <c r="A157" t="str">
-        <v>동부</v>
+        <v>동천마을현대홈타운1차</v>
       </c>
       <c r="B157" t="str">
-        <v>8억 7,000</v>
+        <v>10억 9,000</v>
       </c>
       <c r="C157">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="D157" t="str">
-        <v>104동</v>
+        <v>103동</v>
       </c>
       <c r="E157" t="str">
-        <v>중/17</v>
+        <v>5/16</v>
       </c>
       <c r="F157" t="str">
-        <v/>
-      </c>
-      <c r="G157" t="str" xml:space="preserve">
-        <v xml:space="preserve">주인 거주중이며 입주 가능하고 올수리 깔끔한 매매입니다_x000d_
-</v>
+        <v>남향</v>
+      </c>
+      <c r="G157" t="str">
+        <v>종일 밝은 정남향 올확장 깨끗관리 컨디션최고 동천역5분</v>
       </c>
       <c r="H157" t="str">
         <v>naver</v>
       </c>
     </row>
-    <row r="158" xml:space="preserve">
+    <row r="158">
       <c r="A158" t="str">
-        <v>동부</v>
+        <v>동천마을현대홈타운1차</v>
       </c>
       <c r="B158" t="str">
-        <v>9억 5,000</v>
+        <v>10억 9,000</v>
       </c>
       <c r="C158">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="D158" t="str">
-        <v>105동</v>
+        <v>103동</v>
       </c>
       <c r="E158" t="str">
-        <v>6/17</v>
+        <v>중/16</v>
       </c>
       <c r="F158" t="str">
-        <v>남동향</v>
-      </c>
-      <c r="G158" t="str" xml:space="preserve">
-        <v xml:space="preserve">샷시포함 특올수리이며 입주 가능한 매매입니다_x000d_
-</v>
+        <v>남향</v>
+      </c>
+      <c r="G158" t="str">
+        <v>동천역5분, 남향, 거실확장, 입주협의가능, 부분수리되어 깨끗함</v>
       </c>
       <c r="H158" t="str">
         <v>naver</v>
@@ -4521,25 +4521,25 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>동부</v>
+        <v>동천마을현대홈타운1차</v>
       </c>
       <c r="B159" t="str">
-        <v>8억 9,000</v>
+        <v>10억 7,000</v>
       </c>
       <c r="C159">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="D159" t="str">
-        <v>105동</v>
+        <v>106동</v>
       </c>
       <c r="E159" t="str">
-        <v>9/17</v>
+        <v>저/16</v>
       </c>
       <c r="F159" t="str">
-        <v>남동향</v>
+        <v>남향</v>
       </c>
       <c r="G159" t="str">
-        <v>올수리이며 입주 가능한 매매입니다</v>
+        <v>동천역5분, 남향, 세안고매매, 올확장, 1층아님, 주차연결동</v>
       </c>
       <c r="H159" t="str">
         <v>naver</v>
@@ -4547,51 +4547,51 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>동부</v>
+        <v>동천마을현대홈타운1차</v>
       </c>
       <c r="B160" t="str">
-        <v>8억 9,000</v>
-      </c>
-      <c r="C160" t="str">
-        <v>155</v>
+        <v>12억</v>
+      </c>
+      <c r="C160">
+        <v>122</v>
       </c>
       <c r="D160" t="str">
         <v>101동</v>
       </c>
       <c r="E160" t="str">
-        <v>고층</v>
+        <v>8/25</v>
       </c>
       <c r="F160" t="str">
-        <v/>
+        <v>남향</v>
       </c>
       <c r="G160" t="str">
-        <v>싱크대 수리되어 있으며 햇살 따뜻한 집이에요.</v>
+        <v>37. 신분당선동천역 화이트톤올수리 확트인뷰 해 잘드는집 정남향 입주협</v>
       </c>
       <c r="H160" t="str">
-        <v>asil</v>
+        <v>naver</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>동보</v>
+        <v>동천마을현대홈타운1차</v>
       </c>
       <c r="B161" t="str">
-        <v>12억</v>
+        <v>11억</v>
       </c>
       <c r="C161">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D161" t="str">
-        <v>105동</v>
+        <v>104동</v>
       </c>
       <c r="E161" t="str">
-        <v>8/17</v>
+        <v>6/25</v>
       </c>
       <c r="F161" t="str">
         <v>남향</v>
       </c>
       <c r="G161" t="str">
-        <v>27.10입주세안고,전체나무마루포함내부올수리,수지구청6분,최강학군상권</v>
+        <v>동천역5분, 남향, 주방,욕실,도배,장판,탄성 등 수리됨, 가격조정가</v>
       </c>
       <c r="H161" t="str">
         <v>naver</v>
@@ -4599,25 +4599,25 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>동보</v>
+        <v>동천마을현대홈타운1차</v>
       </c>
       <c r="B162" t="str">
-        <v>12억</v>
+        <v>11억</v>
       </c>
       <c r="C162">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D162" t="str">
-        <v>105동</v>
+        <v>104동</v>
       </c>
       <c r="E162" t="str">
-        <v>7/17</v>
+        <v>고/25</v>
       </c>
       <c r="F162" t="str">
         <v>남향</v>
       </c>
       <c r="G162" t="str">
-        <v>H .햇살좋은 남향 방4 깨끗관리 교육환경최상 수지구청역</v>
+        <v>동천역5분, 남향, 화이트수리, 비확장, 입주협의가능</v>
       </c>
       <c r="H162" t="str">
         <v>naver</v>
@@ -4625,25 +4625,25 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>동보</v>
+        <v>동천마을현대홈타운1차</v>
       </c>
       <c r="B163" t="str">
-        <v>12억</v>
+        <v>11억</v>
       </c>
       <c r="C163">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="D163" t="str">
-        <v>102동</v>
+        <v>106동</v>
       </c>
       <c r="E163" t="str">
-        <v>12/17</v>
+        <v>고/16</v>
       </c>
       <c r="F163" t="str">
         <v>남향</v>
       </c>
       <c r="G163" t="str">
-        <v>41. 7월만기 세안고 햇살가득한집 관리잘된집</v>
+        <v>동천역5분, 남향, 로열동, 주차연결, 입주협의가능, 수리기간드림</v>
       </c>
       <c r="H163" t="str">
         <v>naver</v>
@@ -4651,25 +4651,25 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>동보</v>
+        <v>동천마을현대홈타운1차</v>
       </c>
       <c r="B164" t="str">
-        <v>12억 4,000</v>
+        <v>11억 9,000</v>
       </c>
       <c r="C164">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="D164" t="str">
-        <v>102동</v>
+        <v>101동</v>
       </c>
       <c r="E164" t="str">
-        <v>11/17</v>
+        <v>저/25</v>
       </c>
       <c r="F164" t="str">
         <v>남향</v>
       </c>
       <c r="G164" t="str">
-        <v>과거올수리,주인거주,최상뷰굿,수지구청역6분,재건축이슈,최강교통학군상권</v>
+        <v>H. 햇살가득 따뜻한 남향 올확장 화이트수리 관리최상 동천역</v>
       </c>
       <c r="H164" t="str">
         <v>naver</v>
@@ -4677,25 +4677,25 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>동보</v>
+        <v>동천마을현대홈타운1차</v>
       </c>
       <c r="B165" t="str">
-        <v>10억 8,000</v>
+        <v>11억 5,000</v>
       </c>
       <c r="C165">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="D165" t="str">
-        <v>101동</v>
+        <v>105동</v>
       </c>
       <c r="E165" t="str">
-        <v>1/17</v>
+        <v>중/16</v>
       </c>
       <c r="F165" t="str">
         <v>남향</v>
       </c>
       <c r="G165" t="str">
-        <v>초역세권 수지구청역도보 방4개 기본깨끗 입주일협의</v>
+        <v>동천역5분, 남향, 전망굿, 로열동, 7월이후입주 협의가능</v>
       </c>
       <c r="H165" t="str">
         <v>naver</v>
@@ -4703,25 +4703,25 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>동보</v>
+        <v>동천마을현대홈타운1차</v>
       </c>
       <c r="B166" t="str">
-        <v>12억</v>
+        <v>11억 7,000</v>
       </c>
       <c r="C166">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="D166" t="str">
-        <v>101동</v>
+        <v>107동</v>
       </c>
       <c r="E166" t="str">
-        <v>8/17</v>
+        <v>고/23</v>
       </c>
       <c r="F166" t="str">
         <v>남향</v>
       </c>
       <c r="G166" t="str">
-        <v>세안고매매,6년전샤시포함 잘 올수리된집,수지구청역6분,최강교통학군상권</v>
+        <v>올수리. 2027.8월 임대안고, 전망좋은집, 동천역 도보3분</v>
       </c>
       <c r="H166" t="str">
         <v>naver</v>
@@ -4729,25 +4729,25 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>동보</v>
+        <v>동천마을현대홈타운1차</v>
       </c>
       <c r="B167" t="str">
-        <v>12억</v>
+        <v>11억 7,000</v>
       </c>
       <c r="C167">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="D167" t="str">
-        <v>103동</v>
+        <v>107동</v>
       </c>
       <c r="E167" t="str">
-        <v>중/17</v>
+        <v>18/23</v>
       </c>
       <c r="F167" t="str">
         <v>남향</v>
       </c>
       <c r="G167" t="str">
-        <v>기본,방4,정상입주,초역세권,학세권,해잘드는 정남향집</v>
+        <v>2027년 8월 월세안고, 전망이 좋은집, 동천역 도보5분거리,수리된집</v>
       </c>
       <c r="H167" t="str">
         <v>naver</v>
@@ -4755,51 +4755,51 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>동보</v>
+        <v>동천마을현대홈타운1차</v>
       </c>
       <c r="B168" t="str">
-        <v>12억</v>
-      </c>
-      <c r="C168">
-        <v>125</v>
+        <v>10억 9,000</v>
+      </c>
+      <c r="C168" t="str">
+        <v>122</v>
       </c>
       <c r="D168" t="str">
-        <v>105동</v>
+        <v>104동</v>
       </c>
       <c r="E168" t="str">
-        <v>2/17</v>
+        <v>고층</v>
       </c>
       <c r="F168" t="str">
-        <v>남향</v>
+        <v/>
       </c>
       <c r="G168" t="str">
-        <v>동보</v>
+        <v>햇살가득남향 특전망 로얄동 올수리 컨디션최고 엘베연결</v>
       </c>
       <c r="H168" t="str">
-        <v>naver</v>
+        <v>asil</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>동보</v>
+        <v>동천마을현대홈타운2차</v>
       </c>
       <c r="B169" t="str">
-        <v>12억</v>
+        <v>11억</v>
       </c>
       <c r="C169">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="D169" t="str">
-        <v>101동</v>
+        <v>204동</v>
       </c>
       <c r="E169" t="str">
-        <v>4/17</v>
+        <v>20/25</v>
       </c>
       <c r="F169" t="str">
         <v>남향</v>
       </c>
       <c r="G169" t="str">
-        <v>화장실2개 주방 수리,재건축이슈,정남,교통학군상권,수지구청역세권</v>
+        <v>남향 조용한단지전망 햇볕짱 부분수리 싱크대,도기교체 세안고</v>
       </c>
       <c r="H169" t="str">
         <v>naver</v>
@@ -4807,25 +4807,25 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>동보</v>
+        <v>동천마을현대홈타운2차</v>
       </c>
       <c r="B170" t="str">
-        <v>11억</v>
+        <v>10억</v>
       </c>
       <c r="C170">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="D170" t="str">
-        <v>105동</v>
+        <v>201동</v>
       </c>
       <c r="E170" t="str">
-        <v>6/17</v>
+        <v>5/25</v>
       </c>
       <c r="F170" t="str">
-        <v>남향</v>
+        <v>동향</v>
       </c>
       <c r="G170" t="str">
-        <v>동보</v>
+        <v>o.최근화이트특올수리.샤시교체. 트인전망시원함. 조용한입구동,신혼추천</v>
       </c>
       <c r="H170" t="str">
         <v>naver</v>
@@ -4833,25 +4833,25 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>동보</v>
+        <v>동천마을현대홈타운2차</v>
       </c>
       <c r="B171" t="str">
-        <v>12억 5,000</v>
+        <v>10억 5,000</v>
       </c>
       <c r="C171">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="D171" t="str">
-        <v>102동</v>
+        <v>204동</v>
       </c>
       <c r="E171" t="str">
-        <v>11/17</v>
+        <v>6/25</v>
       </c>
       <c r="F171" t="str">
         <v>남향</v>
       </c>
       <c r="G171" t="str">
-        <v>추천, 샷시포함 올수리, 방1확장, 주인거주, 깨끗관리, 풍부한일조량</v>
+        <v>따스한남향 조용한단지전망 동천역인접동 동천역세권 세안고</v>
       </c>
       <c r="H171" t="str">
         <v>naver</v>
@@ -4859,25 +4859,25 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>동보</v>
+        <v>동천마을현대홈타운2차</v>
       </c>
       <c r="B172" t="str">
-        <v>12억</v>
+        <v>9억</v>
       </c>
       <c r="C172">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="D172" t="str">
-        <v>105동</v>
+        <v>201동</v>
       </c>
       <c r="E172" t="str">
-        <v>15/17</v>
+        <v>2/25</v>
       </c>
       <c r="F172" t="str">
-        <v>남향</v>
+        <v>동향</v>
       </c>
       <c r="G172" t="str">
-        <v>뷰가 잘나오는 맨 앞동 로얄동 로얄층</v>
+        <v>대단지아파트 동천역근접동  기본형 9월초이후 교통편리</v>
       </c>
       <c r="H172" t="str">
         <v>naver</v>
@@ -4885,25 +4885,25 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>동천마을현대홈타운1차</v>
+        <v>동천마을현대홈타운2차</v>
       </c>
       <c r="B173" t="str">
-        <v>10억 9,000</v>
+        <v>10억 3,000</v>
       </c>
       <c r="C173">
         <v>122</v>
       </c>
       <c r="D173" t="str">
-        <v>104동</v>
+        <v>204동</v>
       </c>
       <c r="E173" t="str">
-        <v>23/25</v>
+        <v>1/25</v>
       </c>
       <c r="F173" t="str">
         <v>남향</v>
       </c>
       <c r="G173" t="str">
-        <v>역세권 단지 탁트인 전망의 엘베 연결 로얄동 입주 정상 협의</v>
+        <v>남향, 확장, 부분수리, 깨끗, 동천역가까운동, 입지좋은대단지</v>
       </c>
       <c r="H173" t="str">
         <v>naver</v>
@@ -4911,25 +4911,25 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>동천마을현대홈타운1차</v>
+        <v>동천마을현대홈타운2차</v>
       </c>
       <c r="B174" t="str">
-        <v>10억 9,000</v>
+        <v>11억</v>
       </c>
       <c r="C174">
         <v>122</v>
       </c>
       <c r="D174" t="str">
-        <v>103동</v>
+        <v>206동</v>
       </c>
       <c r="E174" t="str">
-        <v>5/16</v>
+        <v>중/25</v>
       </c>
       <c r="F174" t="str">
-        <v>남향</v>
+        <v>동향</v>
       </c>
       <c r="G174" t="str">
-        <v>종일 밝은 정남향 올확장 깨끗관리 컨디션최고 동천역5분</v>
+        <v>탁트인전망 채광굿 잘관리된집 동천역세권 입주협의</v>
       </c>
       <c r="H174" t="str">
         <v>naver</v>
@@ -4937,25 +4937,25 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>동천마을현대홈타운1차</v>
+        <v>동천마을현대홈타운2차</v>
       </c>
       <c r="B175" t="str">
-        <v>10억 9,000</v>
+        <v>11억</v>
       </c>
       <c r="C175">
         <v>122</v>
       </c>
       <c r="D175" t="str">
-        <v>103동</v>
+        <v>208동</v>
       </c>
       <c r="E175" t="str">
-        <v>중/16</v>
+        <v>고/25</v>
       </c>
       <c r="F175" t="str">
         <v>남향</v>
       </c>
       <c r="G175" t="str">
-        <v>동천역5분, 남향, 거실확장, 입주협의가능, 부분수리되어 깨끗함</v>
+        <v>남향 정상입주 로얄동 환상전망 채광굿 기본형</v>
       </c>
       <c r="H175" t="str">
         <v>naver</v>
@@ -4963,25 +4963,25 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>동천마을현대홈타운1차</v>
+        <v>동천마을현대홈타운2차</v>
       </c>
       <c r="B176" t="str">
-        <v>10억 7,000</v>
+        <v>11억 1,000</v>
       </c>
       <c r="C176">
         <v>122</v>
       </c>
       <c r="D176" t="str">
-        <v>106동</v>
+        <v>209동</v>
       </c>
       <c r="E176" t="str">
-        <v>저/16</v>
+        <v>고/25</v>
       </c>
       <c r="F176" t="str">
         <v>남향</v>
       </c>
       <c r="G176" t="str">
-        <v>동천역5분, 남향, 세안고매매, 올확장, 1층아님, 주차연결동</v>
+        <v>따스한남향 로얄동 관리가잘된집 싱크대교체 채광굿 입주협의</v>
       </c>
       <c r="H176" t="str">
         <v>naver</v>
@@ -4989,25 +4989,25 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>동천마을현대홈타운1차</v>
+        <v>동천마을현대홈타운2차</v>
       </c>
       <c r="B177" t="str">
-        <v>12억</v>
+        <v>9억 9,000</v>
       </c>
       <c r="C177">
         <v>122</v>
       </c>
       <c r="D177" t="str">
-        <v>101동</v>
+        <v>202동</v>
       </c>
       <c r="E177" t="str">
-        <v>8/25</v>
+        <v>저/24</v>
       </c>
       <c r="F177" t="str">
         <v>남향</v>
       </c>
       <c r="G177" t="str">
-        <v>37. 신분당선동천역 화이트톤올수리 확트인뷰 해 잘드는집 정남향 입주협</v>
+        <v>H.햇살가득 따뜻한 남향 거실확장 부분수리 깔끔해요 동천역 세안고</v>
       </c>
       <c r="H177" t="str">
         <v>naver</v>
@@ -5015,25 +5015,25 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>동천마을현대홈타운1차</v>
+        <v>동천마을현대홈타운2차</v>
       </c>
       <c r="B178" t="str">
-        <v>11억</v>
+        <v>10억 8,000</v>
       </c>
       <c r="C178">
         <v>122</v>
       </c>
       <c r="D178" t="str">
-        <v>104동</v>
+        <v>202동</v>
       </c>
       <c r="E178" t="str">
-        <v>6/25</v>
+        <v>고/24</v>
       </c>
       <c r="F178" t="str">
         <v>남향</v>
       </c>
       <c r="G178" t="str">
-        <v>동천역5분, 남향, 주방,욕실,도배,장판,탄성 등 수리됨, 가격조정가</v>
+        <v>H. 좋은집 밝고환한남향 관리최상 채광굿 주차편리 학세권 동천역</v>
       </c>
       <c r="H178" t="str">
         <v>naver</v>
@@ -5041,25 +5041,25 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>동천마을현대홈타운1차</v>
+        <v>동천마을현대홈타운2차</v>
       </c>
       <c r="B179" t="str">
-        <v>11억</v>
+        <v>10억 6,000</v>
       </c>
       <c r="C179">
         <v>122</v>
       </c>
       <c r="D179" t="str">
-        <v>106동</v>
+        <v>206동</v>
       </c>
       <c r="E179" t="str">
-        <v>고/16</v>
+        <v>중/25</v>
       </c>
       <c r="F179" t="str">
-        <v>남향</v>
+        <v>동향</v>
       </c>
       <c r="G179" t="str">
-        <v>동천역5분, 남향, 로열동, 주차연결, 입주협의가능, 수리기간드림</v>
+        <v>올확장 시원한전망 관리가 잘된집  동천역세권 입주협의</v>
       </c>
       <c r="H179" t="str">
         <v>naver</v>
@@ -5067,25 +5067,25 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>동천마을현대홈타운1차</v>
+        <v>동천마을현대홈타운2차</v>
       </c>
       <c r="B180" t="str">
-        <v>11억</v>
+        <v>11억 5,000</v>
       </c>
       <c r="C180">
         <v>122</v>
       </c>
       <c r="D180" t="str">
-        <v>104동</v>
+        <v>207동</v>
       </c>
       <c r="E180" t="str">
-        <v>고/25</v>
+        <v>고/23</v>
       </c>
       <c r="F180" t="str">
         <v>남향</v>
       </c>
       <c r="G180" t="str">
-        <v>동천역5분, 남향, 화이트수리, 비확장, 입주협의가능</v>
+        <v>따스한남향 로얄동 관리가잘된집 화이트수리 채광굿 입주협의</v>
       </c>
       <c r="H180" t="str">
         <v>naver</v>
@@ -5093,25 +5093,25 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>동천마을현대홈타운1차</v>
+        <v>동천마을현대홈타운2차</v>
       </c>
       <c r="B181" t="str">
-        <v>11억 9,000</v>
+        <v>11억 3,000</v>
       </c>
       <c r="C181">
         <v>122</v>
       </c>
       <c r="D181" t="str">
-        <v>101동</v>
+        <v>207동</v>
       </c>
       <c r="E181" t="str">
-        <v>저/25</v>
+        <v>6/23</v>
       </c>
       <c r="F181" t="str">
         <v>남향</v>
       </c>
       <c r="G181" t="str">
-        <v>H. 햇살가득 따뜻한 남향 올확장 화이트수리 관리최상 동천역</v>
+        <v>로얄동 부분수리 채광굿 깔끔관리 정상입주</v>
       </c>
       <c r="H181" t="str">
         <v>naver</v>
@@ -5119,25 +5119,25 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>동천마을현대홈타운1차</v>
+        <v>동천마을현대홈타운2차</v>
       </c>
       <c r="B182" t="str">
-        <v>11억 5,000</v>
+        <v>10억 5,000</v>
       </c>
       <c r="C182">
         <v>122</v>
       </c>
       <c r="D182" t="str">
-        <v>105동</v>
+        <v>204동</v>
       </c>
       <c r="E182" t="str">
-        <v>중/16</v>
+        <v>2/25</v>
       </c>
       <c r="F182" t="str">
         <v>남향</v>
       </c>
       <c r="G182" t="str">
-        <v>동천역5분, 남향, 전망굿, 로열동, 7월이후입주 협의가능</v>
+        <v>남향 확장형 화이트올수리 싱크대욕실ok   세안고</v>
       </c>
       <c r="H182" t="str">
         <v>naver</v>
@@ -5145,25 +5145,25 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>동천마을현대홈타운1차</v>
+        <v>동천마을현대홈타운2차</v>
       </c>
       <c r="B183" t="str">
-        <v>11억 7,000</v>
+        <v>11억 5,000</v>
       </c>
       <c r="C183">
         <v>122</v>
       </c>
       <c r="D183" t="str">
-        <v>107동</v>
+        <v>208동</v>
       </c>
       <c r="E183" t="str">
-        <v>고/23</v>
+        <v>고/25</v>
       </c>
       <c r="F183" t="str">
         <v>남향</v>
       </c>
       <c r="G183" t="str">
-        <v>올수리. 2027.8월 임대안고, 전망좋은집, 동천역 도보3분</v>
+        <v>로얄동층 굿라인 화이트올수리 환상전망 샷시교체 입주협의</v>
       </c>
       <c r="H183" t="str">
         <v>naver</v>
@@ -5171,25 +5171,25 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>동천마을현대홈타운1차</v>
+        <v>동천디이스트</v>
       </c>
       <c r="B184" t="str">
-        <v>11억 7,000</v>
+        <v>11억 5,000</v>
       </c>
       <c r="C184">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D184" t="str">
-        <v>107동</v>
+        <v>511동</v>
       </c>
       <c r="E184" t="str">
-        <v>18/23</v>
+        <v>22/24</v>
       </c>
       <c r="F184" t="str">
-        <v>남향</v>
+        <v>남동향</v>
       </c>
       <c r="G184" t="str">
-        <v>2027년 8월 월세안고, 전망이 좋은집, 동천역 도보5분거리,수리된집</v>
+        <v>동천디이스트</v>
       </c>
       <c r="H184" t="str">
         <v>naver</v>
@@ -5197,103 +5197,103 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>동천마을현대홈타운1차</v>
+        <v>동천디이스트</v>
       </c>
       <c r="B185" t="str">
-        <v>10억 9,000</v>
-      </c>
-      <c r="C185" t="str">
-        <v>122</v>
+        <v>13억</v>
+      </c>
+      <c r="C185">
+        <v>108</v>
       </c>
       <c r="D185" t="str">
-        <v>104동</v>
+        <v>514동</v>
       </c>
       <c r="E185" t="str">
-        <v>고층</v>
+        <v>12/25</v>
       </c>
       <c r="F185" t="str">
-        <v/>
+        <v>남동향</v>
       </c>
       <c r="G185" t="str">
-        <v>햇살가득남향 특전망 로얄동 올수리 컨디션최고 엘베연결</v>
+        <v>로얄동,프리미엄확장,트인전망,깔끔</v>
       </c>
       <c r="H185" t="str">
-        <v>asil</v>
+        <v>naver</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>동천마을현대홈타운1차</v>
+        <v>동천디이스트</v>
       </c>
       <c r="B186" t="str">
-        <v>10억 7,000</v>
-      </c>
-      <c r="C186" t="str">
-        <v>122</v>
+        <v>12억 3,000</v>
+      </c>
+      <c r="C186">
+        <v>108</v>
       </c>
       <c r="D186" t="str">
-        <v>106동</v>
+        <v>509동</v>
       </c>
       <c r="E186" t="str">
-        <v>고층</v>
+        <v>20/25</v>
       </c>
       <c r="F186" t="str">
-        <v/>
+        <v>남서향</v>
       </c>
       <c r="G186" t="str">
-        <v>동천역5분, 남향, 로열동, 주차연결, 입주협의가능, 수리기간드림</v>
+        <v>입구동. 확장형.부분수리  컨디션 아주 좋음. 햇빛가득한 집.</v>
       </c>
       <c r="H186" t="str">
-        <v>asil</v>
+        <v>naver</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>동천마을현대홈타운1차</v>
+        <v>동천디이스트</v>
       </c>
       <c r="B187" t="str">
-        <v>11억</v>
-      </c>
-      <c r="C187" t="str">
-        <v>122</v>
+        <v>12억 5,000</v>
+      </c>
+      <c r="C187">
+        <v>108</v>
       </c>
       <c r="D187" t="str">
-        <v>104동</v>
+        <v>502동</v>
       </c>
       <c r="E187" t="str">
-        <v>23층</v>
+        <v>10/21</v>
       </c>
       <c r="F187" t="str">
-        <v/>
+        <v>남동향</v>
       </c>
       <c r="G187" t="str">
-        <v>동천역5분, 남향, 전망굿, 부분수리, 주차연결동, 입주협의가능</v>
+        <v>앞트인 시원뷰.프리미엄확장.상태최상.입구동산책로근접,동천역도보권.생활편리</v>
       </c>
       <c r="H187" t="str">
-        <v>asil</v>
+        <v>naver</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>동천마을현대홈타운2차</v>
+        <v>동천디이스트</v>
       </c>
       <c r="B188" t="str">
-        <v>11억</v>
+        <v>12억 2,000</v>
       </c>
       <c r="C188">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D188" t="str">
-        <v>204동</v>
+        <v>514동</v>
       </c>
       <c r="E188" t="str">
-        <v>20/25</v>
+        <v>고/25</v>
       </c>
       <c r="F188" t="str">
-        <v>남향</v>
+        <v>남동향</v>
       </c>
       <c r="G188" t="str">
-        <v>남향 조용한단지전망 햇볕짱 부분수리 싱크대,도기교체 세안고</v>
+        <v>트인뷰,프리미엄확장형, 선호동,선호층,채광,환기좋음. 세안고</v>
       </c>
       <c r="H188" t="str">
         <v>naver</v>
@@ -5301,25 +5301,25 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>동천마을현대홈타운2차</v>
+        <v>동천디이스트</v>
       </c>
       <c r="B189" t="str">
-        <v>10억</v>
+        <v>12억 5,000</v>
       </c>
       <c r="C189">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="D189" t="str">
-        <v>201동</v>
+        <v>509동</v>
       </c>
       <c r="E189" t="str">
-        <v>5/25</v>
+        <v>22/25</v>
       </c>
       <c r="F189" t="str">
-        <v>동향</v>
+        <v>남서향</v>
       </c>
       <c r="G189" t="str">
-        <v>o.최근화이트특올수리.샤시교체. 트인전망시원함. 조용한입구동,신혼추천</v>
+        <v>강추 눈부시게예쁜집 3년전특올수리올확장 시스템에어컨4대 동간거리넓은광장뷰</v>
       </c>
       <c r="H189" t="str">
         <v>naver</v>
@@ -5327,25 +5327,25 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>동천마을현대홈타운2차</v>
+        <v>동천디이스트</v>
       </c>
       <c r="B190" t="str">
-        <v>10억 5,000</v>
+        <v>12억</v>
       </c>
       <c r="C190">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D190" t="str">
-        <v>204동</v>
+        <v>514동</v>
       </c>
       <c r="E190" t="str">
         <v>6/25</v>
       </c>
       <c r="F190" t="str">
-        <v>남향</v>
+        <v>남동향</v>
       </c>
       <c r="G190" t="str">
-        <v>따스한남향 조용한단지전망 동천역인접동 동천역세권 세안고</v>
+        <v>0318966776 수리됨입주협의전망짱</v>
       </c>
       <c r="H190" t="str">
         <v>naver</v>
@@ -5353,25 +5353,25 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>동천마을현대홈타운2차</v>
+        <v>동천디이스트</v>
       </c>
       <c r="B191" t="str">
-        <v>10억 3,000</v>
+        <v>13억</v>
       </c>
       <c r="C191">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D191" t="str">
-        <v>204동</v>
+        <v>512동</v>
       </c>
       <c r="E191" t="str">
-        <v>1/25</v>
+        <v>중/23</v>
       </c>
       <c r="F191" t="str">
-        <v>남향</v>
+        <v>남동향</v>
       </c>
       <c r="G191" t="str">
-        <v>남향, 확장, 부분수리, 깨끗, 동천역가까운동, 입지좋은대단지</v>
+        <v>o.최근특올수리,올확장,화이트톤,탁트인전망,최로얄동층,상태최상,정상입주</v>
       </c>
       <c r="H191" t="str">
         <v>naver</v>
@@ -5379,25 +5379,25 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>동천마을현대홈타운2차</v>
+        <v>동천디이스트</v>
       </c>
       <c r="B192" t="str">
-        <v>9억</v>
+        <v>12억 4,000</v>
       </c>
       <c r="C192">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="D192" t="str">
-        <v>201동</v>
+        <v>506동</v>
       </c>
       <c r="E192" t="str">
-        <v>2/25</v>
+        <v>22/25</v>
       </c>
       <c r="F192" t="str">
-        <v>동향</v>
+        <v>남동향</v>
       </c>
       <c r="G192" t="str">
-        <v>대단지아파트 동천역근접동  기본형 9월초이후 교통편리</v>
+        <v>프리미엄확장형, 빠른입주가능, 동천역세권</v>
       </c>
       <c r="H192" t="str">
         <v>naver</v>
@@ -5405,25 +5405,25 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>동천마을현대홈타운2차</v>
+        <v>동천디이스트</v>
       </c>
       <c r="B193" t="str">
-        <v>11억</v>
+        <v>13억</v>
       </c>
       <c r="C193">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D193" t="str">
-        <v>206동</v>
+        <v>514동</v>
       </c>
       <c r="E193" t="str">
-        <v>중/25</v>
+        <v>10/25</v>
       </c>
       <c r="F193" t="str">
-        <v>동향</v>
+        <v>남동향</v>
       </c>
       <c r="G193" t="str">
-        <v>탁트인전망 채광굿 잘관리된집 동천역세권 입주협의</v>
+        <v>0318966776 최근확장올수리됨입주협의가능.</v>
       </c>
       <c r="H193" t="str">
         <v>naver</v>
@@ -5431,25 +5431,25 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>동천마을현대홈타운2차</v>
+        <v>동천디이스트</v>
       </c>
       <c r="B194" t="str">
-        <v>11억</v>
+        <v>13억</v>
       </c>
       <c r="C194">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D194" t="str">
-        <v>208동</v>
+        <v>512동</v>
       </c>
       <c r="E194" t="str">
-        <v>고/25</v>
+        <v>저/23</v>
       </c>
       <c r="F194" t="str">
-        <v>남향</v>
+        <v>남서향</v>
       </c>
       <c r="G194" t="str">
-        <v>남향 정상입주 로얄동 환상전망 채광굿 기본형</v>
+        <v>로얄동,로얄층,특올수리,특전망</v>
       </c>
       <c r="H194" t="str">
         <v>naver</v>
@@ -5457,25 +5457,25 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>동천마을현대홈타운2차</v>
+        <v>동천디이스트</v>
       </c>
       <c r="B195" t="str">
-        <v>10억 6,000</v>
+        <v>12억 2,000</v>
       </c>
       <c r="C195">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D195" t="str">
-        <v>206동</v>
+        <v>512동</v>
       </c>
       <c r="E195" t="str">
-        <v>중/25</v>
+        <v>중/23</v>
       </c>
       <c r="F195" t="str">
-        <v>동향</v>
+        <v>남서향</v>
       </c>
       <c r="G195" t="str">
-        <v>올확장 시원한전망 관리가 잘된집  동천역세권 입주협의</v>
+        <v>로얄동 확장 깨끗  세안고</v>
       </c>
       <c r="H195" t="str">
         <v>naver</v>
@@ -5483,25 +5483,25 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>동천마을현대홈타운2차</v>
+        <v>동천디이스트</v>
       </c>
       <c r="B196" t="str">
-        <v>11억 1,000</v>
+        <v>11억 7,000</v>
       </c>
       <c r="C196">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D196" t="str">
-        <v>209동</v>
+        <v>510동</v>
       </c>
       <c r="E196" t="str">
-        <v>고/25</v>
+        <v>저/24</v>
       </c>
       <c r="F196" t="str">
-        <v>남향</v>
+        <v>남동향</v>
       </c>
       <c r="G196" t="str">
-        <v>따스한남향 로얄동 관리가잘된집 싱크대교체 채광굿 입주협의</v>
+        <v>프리미엄확장.정상입주.동천역 도보 9분. 전자계약 가능</v>
       </c>
       <c r="H196" t="str">
         <v>naver</v>
@@ -5509,25 +5509,25 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>동천마을현대홈타운2차</v>
+        <v>동천디이스트</v>
       </c>
       <c r="B197" t="str">
-        <v>9억 9,000</v>
+        <v>12억 3,000</v>
       </c>
       <c r="C197">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D197" t="str">
-        <v>202동</v>
+        <v>515동</v>
       </c>
       <c r="E197" t="str">
-        <v>저/24</v>
+        <v>저/23</v>
       </c>
       <c r="F197" t="str">
-        <v>남향</v>
+        <v>북서향</v>
       </c>
       <c r="G197" t="str">
-        <v>H.햇살가득 따뜻한 남향 거실확장 부분수리 깔끔해요 동천역 세안고</v>
+        <v>전체 확장 화이트올수리 입주가 탁트인정원전망 라인굿</v>
       </c>
       <c r="H197" t="str">
         <v>naver</v>
@@ -5535,25 +5535,25 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>동천마을현대홈타운2차</v>
+        <v>동천디이스트</v>
       </c>
       <c r="B198" t="str">
-        <v>10억 8,000</v>
+        <v>12억 7,000</v>
       </c>
       <c r="C198">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D198" t="str">
-        <v>202동</v>
+        <v>503동</v>
       </c>
       <c r="E198" t="str">
-        <v>고/24</v>
+        <v>25/25</v>
       </c>
       <c r="F198" t="str">
-        <v>남향</v>
+        <v>남동향</v>
       </c>
       <c r="G198" t="str">
-        <v>H. 좋은집 밝고환한남향 관리최상 채광굿 주차편리 학세권 동천역</v>
+        <v>o성실o프리미엄확장.전망굿탑층.실입주.로얄동.주인관리깨끗.동천역도보</v>
       </c>
       <c r="H198" t="str">
         <v>naver</v>
@@ -5561,25 +5561,25 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>동천마을현대홈타운2차</v>
+        <v>동천디이스트</v>
       </c>
       <c r="B199" t="str">
-        <v>11억 5,000</v>
+        <v>12억</v>
       </c>
       <c r="C199">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D199" t="str">
-        <v>207동</v>
+        <v>504동</v>
       </c>
       <c r="E199" t="str">
-        <v>고/23</v>
+        <v>2/25</v>
       </c>
       <c r="F199" t="str">
-        <v>남향</v>
+        <v>남서향</v>
       </c>
       <c r="G199" t="str">
-        <v>따스한남향 로얄동 관리가잘된집 화이트수리 채광굿 입주협의</v>
+        <v>0318966776 전망아주좋음확장수리잘됨</v>
       </c>
       <c r="H199" t="str">
         <v>naver</v>
@@ -5587,25 +5587,25 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>동천마을현대홈타운2차</v>
+        <v>동천디이스트</v>
       </c>
       <c r="B200" t="str">
-        <v>11억 3,000</v>
+        <v>11억 1,000</v>
       </c>
       <c r="C200">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D200" t="str">
-        <v>207동</v>
+        <v>501동</v>
       </c>
       <c r="E200" t="str">
-        <v>6/23</v>
+        <v>저/25</v>
       </c>
       <c r="F200" t="str">
-        <v>남향</v>
+        <v>남동향</v>
       </c>
       <c r="G200" t="str">
-        <v>로얄동 부분수리 채광굿 깔끔관리 정상입주</v>
+        <v>로얄동 출입동 입주협의가 깨끗 생활편리 동천역도보편리</v>
       </c>
       <c r="H200" t="str">
         <v>naver</v>
@@ -5613,25 +5613,25 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>동천마을현대홈타운2차</v>
+        <v>동천디이스트</v>
       </c>
       <c r="B201" t="str">
-        <v>10억 5,000</v>
+        <v>12억 9,000</v>
       </c>
       <c r="C201">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D201" t="str">
-        <v>204동</v>
+        <v>509동</v>
       </c>
       <c r="E201" t="str">
-        <v>2/25</v>
+        <v>고/25</v>
       </c>
       <c r="F201" t="str">
-        <v>남향</v>
+        <v>남서향</v>
       </c>
       <c r="G201" t="str">
-        <v>남향 확장형 화이트올수리 싱크대욕실ok   세안고</v>
+        <v>특올수리 채광좋은고층 생활편리 로얄동 입주협의 소유주직접의뢰</v>
       </c>
       <c r="H201" t="str">
         <v>naver</v>
@@ -5639,25 +5639,25 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>동천마을현대홈타운2차</v>
+        <v>동천디이스트</v>
       </c>
       <c r="B202" t="str">
-        <v>11억 5,000</v>
+        <v>12억 3,000</v>
       </c>
       <c r="C202">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D202" t="str">
-        <v>208동</v>
+        <v>505동</v>
       </c>
       <c r="E202" t="str">
         <v>고/25</v>
       </c>
       <c r="F202" t="str">
-        <v>남향</v>
+        <v>남동향</v>
       </c>
       <c r="G202" t="str">
-        <v>로얄동층 굿라인 화이트올수리 환상전망 샷시교체 입주협의</v>
+        <v>확장형 채광좋은 관리잘된집 조율가 동천역도보10분</v>
       </c>
       <c r="H202" t="str">
         <v>naver</v>
@@ -5668,22 +5668,22 @@
         <v>동천디이스트</v>
       </c>
       <c r="B203" t="str">
-        <v>11억 5,000</v>
+        <v>12억</v>
       </c>
       <c r="C203">
         <v>108</v>
       </c>
       <c r="D203" t="str">
-        <v>511동</v>
+        <v>504동</v>
       </c>
       <c r="E203" t="str">
-        <v>22/24</v>
+        <v>중/25</v>
       </c>
       <c r="F203" t="str">
-        <v>남동향</v>
+        <v>남서향</v>
       </c>
       <c r="G203" t="str">
-        <v>동천디이스트</v>
+        <v>전망 좋은 로얄동,올확장,입주일 협의 가</v>
       </c>
       <c r="H203" t="str">
         <v>naver</v>
@@ -5694,22 +5694,22 @@
         <v>동천디이스트</v>
       </c>
       <c r="B204" t="str">
-        <v>13억</v>
+        <v>12억 2,000</v>
       </c>
       <c r="C204">
         <v>108</v>
       </c>
       <c r="D204" t="str">
-        <v>514동</v>
+        <v>502동</v>
       </c>
       <c r="E204" t="str">
-        <v>12/25</v>
+        <v>중/21</v>
       </c>
       <c r="F204" t="str">
         <v>남동향</v>
       </c>
       <c r="G204" t="str">
-        <v>로얄동,프리미엄확장,트인전망,깔끔</v>
+        <v>올수리 프리미엄확장 로얄동층 트인불곡산전망 출입동생활편리</v>
       </c>
       <c r="H204" t="str">
         <v>naver</v>
@@ -5720,7 +5720,7 @@
         <v>동천디이스트</v>
       </c>
       <c r="B205" t="str">
-        <v>12억 3,000</v>
+        <v>12억</v>
       </c>
       <c r="C205">
         <v>108</v>
@@ -5729,13 +5729,13 @@
         <v>509동</v>
       </c>
       <c r="E205" t="str">
-        <v>20/25</v>
+        <v>7/25</v>
       </c>
       <c r="F205" t="str">
         <v>남서향</v>
       </c>
       <c r="G205" t="str">
-        <v>입구동. 확장형.부분수리  컨디션 아주 좋음. 햇빛가득한 집.</v>
+        <v>세안고, 파크뷰, 동천초, 산책로굿, 조용</v>
       </c>
       <c r="H205" t="str">
         <v>naver</v>
@@ -5752,16 +5752,16 @@
         <v>108</v>
       </c>
       <c r="D206" t="str">
-        <v>502동</v>
+        <v>503동</v>
       </c>
       <c r="E206" t="str">
-        <v>10/21</v>
+        <v>중/25</v>
       </c>
       <c r="F206" t="str">
         <v>남동향</v>
       </c>
       <c r="G206" t="str">
-        <v>앞트인 시원뷰.프리미엄확장.상태최상.입구동산책로근접,동천역도보권.생활편리</v>
+        <v>로얄동층 트인불곡산전망 확장 화이트수리 관리최상 동천역도보편리</v>
       </c>
       <c r="H206" t="str">
         <v>naver</v>
@@ -5772,22 +5772,22 @@
         <v>동천디이스트</v>
       </c>
       <c r="B207" t="str">
-        <v>12억 2,000</v>
+        <v>12억 3,000</v>
       </c>
       <c r="C207">
         <v>108</v>
       </c>
       <c r="D207" t="str">
-        <v>514동</v>
+        <v>515동</v>
       </c>
       <c r="E207" t="str">
-        <v>고/25</v>
+        <v>중/23</v>
       </c>
       <c r="F207" t="str">
-        <v>남동향</v>
+        <v>남서향</v>
       </c>
       <c r="G207" t="str">
-        <v>트인뷰,프리미엄확장형, 선호동,선호층,채광,환기좋음. 세안고</v>
+        <v>올확장  입주가능 탁트인뷰 채광굿</v>
       </c>
       <c r="H207" t="str">
         <v>naver</v>
@@ -5798,22 +5798,22 @@
         <v>동천디이스트</v>
       </c>
       <c r="B208" t="str">
-        <v>12억 5,000</v>
+        <v>12억</v>
       </c>
       <c r="C208">
         <v>108</v>
       </c>
       <c r="D208" t="str">
-        <v>509동</v>
+        <v>505동</v>
       </c>
       <c r="E208" t="str">
-        <v>22/25</v>
+        <v>고/25</v>
       </c>
       <c r="F208" t="str">
-        <v>남서향</v>
+        <v>남동향</v>
       </c>
       <c r="G208" t="str">
-        <v>강추 눈부시게예쁜집 3년전특올수리올확장 시스템에어컨4대 동간거리넓은광장뷰</v>
+        <v>프리미엄확장,밝고 깔끔,학교까까운 동</v>
       </c>
       <c r="H208" t="str">
         <v>naver</v>
@@ -5824,7 +5824,7 @@
         <v>동천디이스트</v>
       </c>
       <c r="B209" t="str">
-        <v>12억</v>
+        <v>13억</v>
       </c>
       <c r="C209">
         <v>108</v>
@@ -5833,13 +5833,13 @@
         <v>514동</v>
       </c>
       <c r="E209" t="str">
-        <v>6/25</v>
+        <v>중/25</v>
       </c>
       <c r="F209" t="str">
-        <v>남동향</v>
+        <v/>
       </c>
       <c r="G209" t="str">
-        <v>0318966776 수리됨입주협의전망짱</v>
+        <v>로얄동,트인뷰,프리미엄확장,깔끔관리</v>
       </c>
       <c r="H209" t="str">
         <v>naver</v>
@@ -5850,25 +5850,25 @@
         <v>동천디이스트</v>
       </c>
       <c r="B210" t="str">
-        <v>13억</v>
-      </c>
-      <c r="C210">
+        <v>12억 4,000</v>
+      </c>
+      <c r="C210" t="str">
         <v>108</v>
       </c>
       <c r="D210" t="str">
-        <v>512동</v>
+        <v>506동</v>
       </c>
       <c r="E210" t="str">
-        <v>중/23</v>
+        <v>고층</v>
       </c>
       <c r="F210" t="str">
-        <v>남동향</v>
+        <v/>
       </c>
       <c r="G210" t="str">
-        <v>o.최근특올수리,올확장,화이트톤,탁트인전망,최로얄동층,상태최상,정상입주</v>
+        <v>o성실o전체확장형.해잘들어밝아요.LED교체.깨끗해요.빠른입주가능</v>
       </c>
       <c r="H210" t="str">
-        <v>naver</v>
+        <v>asil</v>
       </c>
     </row>
     <row r="211">
@@ -5876,25 +5876,25 @@
         <v>동천디이스트</v>
       </c>
       <c r="B211" t="str">
-        <v>12억 4,000</v>
-      </c>
-      <c r="C211">
+        <v>11억 2,000</v>
+      </c>
+      <c r="C211" t="str">
         <v>108</v>
       </c>
       <c r="D211" t="str">
         <v>506동</v>
       </c>
       <c r="E211" t="str">
-        <v>22/25</v>
+        <v>7층</v>
       </c>
       <c r="F211" t="str">
-        <v>남동향</v>
+        <v/>
       </c>
       <c r="G211" t="str">
-        <v>프리미엄확장형, 빠른입주가능, 동천역세권</v>
+        <v>급매, 확장형, 공원전망 , 입주일자 협의가능</v>
       </c>
       <c r="H211" t="str">
-        <v>naver</v>
+        <v>asil</v>
       </c>
     </row>
     <row r="212">
@@ -5902,25 +5902,25 @@
         <v>동천디이스트</v>
       </c>
       <c r="B212" t="str">
-        <v>13억</v>
-      </c>
-      <c r="C212">
+        <v>11억 5,000</v>
+      </c>
+      <c r="C212" t="str">
         <v>108</v>
       </c>
       <c r="D212" t="str">
-        <v>514동</v>
+        <v>511동</v>
       </c>
       <c r="E212" t="str">
-        <v>10/25</v>
+        <v>고층</v>
       </c>
       <c r="F212" t="str">
-        <v>남동향</v>
+        <v/>
       </c>
       <c r="G212" t="str">
-        <v>0318966776 최근확장올수리됨입주협의가능.</v>
+        <v>o.세안고27.3.27입주,탁트인전망,올확장,최근올수리,관리최상</v>
       </c>
       <c r="H212" t="str">
-        <v>naver</v>
+        <v>asil</v>
       </c>
     </row>
     <row r="213">
@@ -5928,25 +5928,25 @@
         <v>동천디이스트</v>
       </c>
       <c r="B213" t="str">
-        <v>13억</v>
-      </c>
-      <c r="C213">
+        <v>12억 5,000</v>
+      </c>
+      <c r="C213" t="str">
         <v>108</v>
       </c>
       <c r="D213" t="str">
-        <v>512동</v>
+        <v>503동</v>
       </c>
       <c r="E213" t="str">
-        <v>저/23</v>
+        <v>25층</v>
       </c>
       <c r="F213" t="str">
-        <v>남서향</v>
+        <v/>
       </c>
       <c r="G213" t="str">
-        <v>로얄동,로얄층,특올수리,특전망</v>
+        <v>탁트인로얄동 환상전망 프리미엄확장 상권교통편리한입구동 대단지</v>
       </c>
       <c r="H213" t="str">
-        <v>naver</v>
+        <v>asil</v>
       </c>
     </row>
     <row r="214">
@@ -5954,48 +5954,48 @@
         <v>동천디이스트</v>
       </c>
       <c r="B214" t="str">
-        <v>12억 2,000</v>
-      </c>
-      <c r="C214">
+        <v>12억 5,000</v>
+      </c>
+      <c r="C214" t="str">
         <v>108</v>
       </c>
       <c r="D214" t="str">
-        <v>512동</v>
+        <v>502동</v>
       </c>
       <c r="E214" t="str">
-        <v>중/23</v>
+        <v>중층</v>
       </c>
       <c r="F214" t="str">
-        <v>남서향</v>
+        <v/>
       </c>
       <c r="G214" t="str">
-        <v>로얄동 확장 깨끗  세안고</v>
+        <v>로얄동층 완전트인뷰 프리미엄확장 입주협의가 출입동 동천역도보편리</v>
       </c>
       <c r="H214" t="str">
-        <v>naver</v>
+        <v>asil</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>동천디이스트</v>
+        <v>써니벨리</v>
       </c>
       <c r="B215" t="str">
-        <v>11억 7,000</v>
+        <v>11억 2,000</v>
       </c>
       <c r="C215">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D215" t="str">
-        <v>510동</v>
+        <v>107동</v>
       </c>
       <c r="E215" t="str">
-        <v>저/24</v>
+        <v>7/18</v>
       </c>
       <c r="F215" t="str">
-        <v>남동향</v>
+        <v>남향</v>
       </c>
       <c r="G215" t="str">
-        <v>프리미엄확장.정상입주.동천역 도보 9분. 전자계약 가능</v>
+        <v>추천매물 로얄동 앞트인전망 결로 곰팡이없이 관리최상</v>
       </c>
       <c r="H215" t="str">
         <v>naver</v>
@@ -6003,25 +6003,25 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>동천디이스트</v>
+        <v>써니벨리</v>
       </c>
       <c r="B216" t="str">
-        <v>12억 3,000</v>
+        <v>9억 3,000</v>
       </c>
       <c r="C216">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="D216" t="str">
-        <v>515동</v>
+        <v>106동</v>
       </c>
       <c r="E216" t="str">
-        <v>저/23</v>
+        <v>1/19</v>
       </c>
       <c r="F216" t="str">
-        <v>북서향</v>
+        <v>남향</v>
       </c>
       <c r="G216" t="str">
-        <v>전체 확장 화이트올수리 입주가 탁트인정원전망 라인굿</v>
+        <v>정상,깨끗하고 일부수리에 전망굿 단지내초등학교 신분당선 동천역10분</v>
       </c>
       <c r="H216" t="str">
         <v>naver</v>
@@ -6029,25 +6029,25 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>동천디이스트</v>
+        <v>써니벨리</v>
       </c>
       <c r="B217" t="str">
-        <v>12억 7,000</v>
+        <v>10억</v>
       </c>
       <c r="C217">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="D217" t="str">
-        <v>503동</v>
+        <v>101동</v>
       </c>
       <c r="E217" t="str">
-        <v>25/25</v>
+        <v>13/15</v>
       </c>
       <c r="F217" t="str">
-        <v>남동향</v>
+        <v>남향</v>
       </c>
       <c r="G217" t="str">
-        <v>o성실o프리미엄확장.전망굿탑층.실입주.로얄동.주인관리깨끗.동천역도보</v>
+        <v>28. 동천역 손곡초중 남향 방3화2 현재 세입자거주중 월세안고매매</v>
       </c>
       <c r="H217" t="str">
         <v>naver</v>
@@ -6055,25 +6055,25 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>동천디이스트</v>
+        <v>써니벨리</v>
       </c>
       <c r="B218" t="str">
-        <v>12억</v>
+        <v>10억 3,000</v>
       </c>
       <c r="C218">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D218" t="str">
-        <v>504동</v>
+        <v>103동</v>
       </c>
       <c r="E218" t="str">
-        <v>2/25</v>
+        <v>1/19</v>
       </c>
       <c r="F218" t="str">
-        <v>남서향</v>
+        <v>남향</v>
       </c>
       <c r="G218" t="str">
-        <v>0318966776 전망아주좋음확장수리잘됨</v>
+        <v>초품아,방2확장 화이트수리,주인거주,강남판교 출퇴근 용이</v>
       </c>
       <c r="H218" t="str">
         <v>naver</v>
@@ -6081,25 +6081,25 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>동천디이스트</v>
+        <v>써니벨리</v>
       </c>
       <c r="B219" t="str">
-        <v>12억 2,000</v>
+        <v>11억</v>
       </c>
       <c r="C219">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D219" t="str">
-        <v>515동</v>
+        <v>104동</v>
       </c>
       <c r="E219" t="str">
-        <v>중/23</v>
+        <v>7/19</v>
       </c>
       <c r="F219" t="str">
-        <v>남서향</v>
+        <v>남향</v>
       </c>
       <c r="G219" t="str">
-        <v>로얄동층 트인전망예뻐요 확장형 동천역과상가인접이라서 편해요</v>
+        <v>로얄동 급매 짧은세안고</v>
       </c>
       <c r="H219" t="str">
         <v>naver</v>
@@ -6107,25 +6107,25 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>동천디이스트</v>
+        <v>써니벨리</v>
       </c>
       <c r="B220" t="str">
-        <v>11억 1,000</v>
+        <v>10억</v>
       </c>
       <c r="C220">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="D220" t="str">
-        <v>501동</v>
+        <v>106동</v>
       </c>
       <c r="E220" t="str">
-        <v>저/25</v>
+        <v>18/19</v>
       </c>
       <c r="F220" t="str">
-        <v>남동향</v>
+        <v>남향</v>
       </c>
       <c r="G220" t="str">
-        <v>로얄동 출입동 입주협의가 깨끗 생활편리 동천역도보편리</v>
+        <v>귀한매물 올확장 수리 전망트임</v>
       </c>
       <c r="H220" t="str">
         <v>naver</v>
@@ -6133,25 +6133,25 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>동천디이스트</v>
+        <v>써니벨리</v>
       </c>
       <c r="B221" t="str">
-        <v>12억 9,000</v>
+        <v>10억 3,000</v>
       </c>
       <c r="C221">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D221" t="str">
-        <v>509동</v>
+        <v>105동</v>
       </c>
       <c r="E221" t="str">
-        <v>고/25</v>
+        <v>2/19</v>
       </c>
       <c r="F221" t="str">
-        <v>남서향</v>
+        <v>남향</v>
       </c>
       <c r="G221" t="str">
-        <v>특올수리 채광좋은고층 생활편리 로얄동 입주협의 소유주직접의뢰</v>
+        <v>로얄동 5.1억 전세안고 매매 초품아 잔금일협의</v>
       </c>
       <c r="H221" t="str">
         <v>naver</v>
@@ -6159,25 +6159,25 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>동천디이스트</v>
+        <v>써니벨리</v>
       </c>
       <c r="B222" t="str">
-        <v>12억 3,000</v>
+        <v>10억</v>
       </c>
       <c r="C222">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="D222" t="str">
-        <v>505동</v>
+        <v>106동</v>
       </c>
       <c r="E222" t="str">
-        <v>고/25</v>
+        <v>고/19</v>
       </c>
       <c r="F222" t="str">
-        <v>남동향</v>
+        <v>남향</v>
       </c>
       <c r="G222" t="str">
-        <v>확장형 채광좋은 관리잘된집 조율가 동천역도보10분</v>
+        <v>정상,깨끗하고 전망굿 단지내초등학교 신분당선 동천역10분</v>
       </c>
       <c r="H222" t="str">
         <v>naver</v>
@@ -6185,25 +6185,25 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>동천디이스트</v>
+        <v>써니벨리</v>
       </c>
       <c r="B223" t="str">
-        <v>12억</v>
+        <v>11억 5,000</v>
       </c>
       <c r="C223">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D223" t="str">
-        <v>504동</v>
+        <v>107동</v>
       </c>
       <c r="E223" t="str">
-        <v>중/25</v>
+        <v>17/18</v>
       </c>
       <c r="F223" t="str">
-        <v>남서향</v>
+        <v>남향</v>
       </c>
       <c r="G223" t="str">
-        <v>전망 좋은 로얄동,올확장,입주일 협의 가</v>
+        <v>로얄동 전망최고 수리됨</v>
       </c>
       <c r="H223" t="str">
         <v>naver</v>
@@ -6211,25 +6211,25 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>동천디이스트</v>
+        <v>써니벨리</v>
       </c>
       <c r="B224" t="str">
-        <v>12억 2,000</v>
+        <v>10억</v>
       </c>
       <c r="C224">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D224" t="str">
-        <v>502동</v>
+        <v>105동</v>
       </c>
       <c r="E224" t="str">
-        <v>중/21</v>
+        <v>1/19</v>
       </c>
       <c r="F224" t="str">
-        <v>남동향</v>
+        <v>남향</v>
       </c>
       <c r="G224" t="str">
-        <v>올수리 프리미엄확장 로얄동층 트인불곡산전망 출입동생활편리</v>
+        <v>따스한남향 방확장 주인거주 채광굿 깔끔관리</v>
       </c>
       <c r="H224" t="str">
         <v>naver</v>
@@ -6237,25 +6237,25 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>동천디이스트</v>
+        <v>써니벨리</v>
       </c>
       <c r="B225" t="str">
-        <v>12억</v>
+        <v>10억 2,000</v>
       </c>
       <c r="C225">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D225" t="str">
-        <v>509동</v>
+        <v>102동</v>
       </c>
       <c r="E225" t="str">
-        <v>7/25</v>
+        <v>3/14</v>
       </c>
       <c r="F225" t="str">
-        <v>남서향</v>
+        <v>남향</v>
       </c>
       <c r="G225" t="str">
-        <v>세안고, 파크뷰, 동천초, 산책로굿, 조용</v>
+        <v>남향 확장 세안고</v>
       </c>
       <c r="H225" t="str">
         <v>naver</v>
@@ -6263,25 +6263,25 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>동천디이스트</v>
+        <v>성동마을강남</v>
       </c>
       <c r="B226" t="str">
-        <v>12억 5,000</v>
+        <v>13억</v>
       </c>
       <c r="C226">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="D226" t="str">
-        <v>503동</v>
+        <v>107동</v>
       </c>
       <c r="E226" t="str">
-        <v>중/25</v>
+        <v>15/18</v>
       </c>
       <c r="F226" t="str">
-        <v>남동향</v>
+        <v>남향</v>
       </c>
       <c r="G226" t="str">
-        <v>로얄동층 트인불곡산전망 확장 화이트수리 관리최상 동천역도보편리</v>
+        <v>강추,49형,로얄동,화이트올수리,깨끗한집.초역세권,세안고다주택자</v>
       </c>
       <c r="H226" t="str">
         <v>naver</v>
@@ -6289,25 +6289,25 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>동천디이스트</v>
+        <v>성동마을강남</v>
       </c>
       <c r="B227" t="str">
-        <v>12억 3,000</v>
+        <v>14억 5,000</v>
       </c>
       <c r="C227">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="D227" t="str">
-        <v>515동</v>
+        <v>107동</v>
       </c>
       <c r="E227" t="str">
-        <v>중/23</v>
+        <v>6/18</v>
       </c>
       <c r="F227" t="str">
-        <v>남서향</v>
+        <v>남향</v>
       </c>
       <c r="G227" t="str">
-        <v>올확장  입주가능 탁트인뷰 채광굿</v>
+        <v>로얄동 트인전망  초역세권 생활권좋음 세안고</v>
       </c>
       <c r="H227" t="str">
         <v>naver</v>
@@ -6315,25 +6315,25 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>동천디이스트</v>
+        <v>성동마을강남</v>
       </c>
       <c r="B228" t="str">
-        <v>12억</v>
+        <v>14억 3,000</v>
       </c>
       <c r="C228">
-        <v>108</v>
+        <v>195</v>
       </c>
       <c r="D228" t="str">
-        <v>505동</v>
+        <v>101동</v>
       </c>
       <c r="E228" t="str">
-        <v>고/25</v>
+        <v>18/18</v>
       </c>
       <c r="F228" t="str">
-        <v>남동향</v>
+        <v>남서향</v>
       </c>
       <c r="G228" t="str">
-        <v>프리미엄확장,밝고 깔끔,학교까까운 동</v>
+        <v>입구동 전망굿 초역세권 화장실2수리</v>
       </c>
       <c r="H228" t="str">
         <v>naver</v>
@@ -6341,25 +6341,25 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>동천디이스트</v>
+        <v>성동마을강남</v>
       </c>
       <c r="B229" t="str">
-        <v>13억</v>
+        <v>14억 5,000</v>
       </c>
       <c r="C229">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="D229" t="str">
-        <v>514동</v>
+        <v>105동</v>
       </c>
       <c r="E229" t="str">
-        <v>중/25</v>
+        <v>중/18</v>
       </c>
       <c r="F229" t="str">
-        <v/>
+        <v>남향</v>
       </c>
       <c r="G229" t="str">
-        <v>로얄동,트인뷰,프리미엄확장,깔끔관리</v>
+        <v>샷시포함특올수리 성복역세권 생활편리 학군최고</v>
       </c>
       <c r="H229" t="str">
         <v>naver</v>
@@ -6367,155 +6367,155 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>동천디이스트</v>
+        <v>성동마을강남</v>
       </c>
       <c r="B230" t="str">
-        <v>12억 4,000</v>
-      </c>
-      <c r="C230" t="str">
-        <v>108</v>
+        <v>12억</v>
+      </c>
+      <c r="C230">
+        <v>109</v>
       </c>
       <c r="D230" t="str">
-        <v>506동</v>
+        <v>103동</v>
       </c>
       <c r="E230" t="str">
-        <v>고층</v>
+        <v>중/18</v>
       </c>
       <c r="F230" t="str">
-        <v/>
+        <v>남동향</v>
       </c>
       <c r="G230" t="str">
-        <v>o성실o전체확장형.해잘들어밝아요.LED교체.깨끗해요.빠른입주가능</v>
+        <v>정상입주,방확장,주방씽크대외수리함.성복역초역세권</v>
       </c>
       <c r="H230" t="str">
-        <v>asil</v>
+        <v>naver</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>동천디이스트</v>
+        <v>성동마을강남</v>
       </c>
       <c r="B231" t="str">
-        <v>11억 2,000</v>
-      </c>
-      <c r="C231" t="str">
-        <v>108</v>
+        <v>11억 5,000</v>
+      </c>
+      <c r="C231">
+        <v>109</v>
       </c>
       <c r="D231" t="str">
-        <v>506동</v>
+        <v>103동</v>
       </c>
       <c r="E231" t="str">
-        <v>7층</v>
+        <v>11/18</v>
       </c>
       <c r="F231" t="str">
-        <v/>
+        <v>남동향</v>
       </c>
       <c r="G231" t="str">
-        <v>급매, 확장형, 공원전망 , 입주일자 협의가능</v>
+        <v>올수리 폴딩도어 정상입주 성복역 도보2분 생활권좋음</v>
       </c>
       <c r="H231" t="str">
-        <v>asil</v>
+        <v>naver</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>동천디이스트</v>
+        <v>성동마을강남</v>
       </c>
       <c r="B232" t="str">
-        <v>11억 5,000</v>
-      </c>
-      <c r="C232" t="str">
-        <v>108</v>
+        <v>13억 5,000</v>
+      </c>
+      <c r="C232">
+        <v>163</v>
       </c>
       <c r="D232" t="str">
-        <v>511동</v>
+        <v>105동</v>
       </c>
       <c r="E232" t="str">
-        <v>고층</v>
+        <v>7/18</v>
       </c>
       <c r="F232" t="str">
-        <v/>
+        <v>남향</v>
       </c>
       <c r="G232" t="str">
-        <v>o.세안고27.3.27입주,탁트인전망,올확장,최근올수리,관리최상</v>
+        <v>세안고 남향 성복역 도보2분 상권인접 기본</v>
       </c>
       <c r="H232" t="str">
-        <v>asil</v>
+        <v>naver</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>동천디이스트</v>
+        <v>성동마을강남</v>
       </c>
       <c r="B233" t="str">
-        <v>12억 5,000</v>
-      </c>
-      <c r="C233" t="str">
-        <v>108</v>
+        <v>13억 5,000</v>
+      </c>
+      <c r="C233">
+        <v>163</v>
       </c>
       <c r="D233" t="str">
-        <v>503동</v>
+        <v>106동</v>
       </c>
       <c r="E233" t="str">
-        <v>25층</v>
+        <v>12/18</v>
       </c>
       <c r="F233" t="str">
-        <v/>
+        <v>남동향</v>
       </c>
       <c r="G233" t="str">
-        <v>탁트인로얄동 환상전망 프리미엄확장 상권교통편리한입구동 대단지</v>
+        <v>채광굿 초역세권 도보2분 생활권 좋음  기본</v>
       </c>
       <c r="H233" t="str">
-        <v>asil</v>
+        <v>naver</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>동천디이스트</v>
+        <v>성동마을강남</v>
       </c>
       <c r="B234" t="str">
-        <v>12억 5,000</v>
-      </c>
-      <c r="C234" t="str">
-        <v>108</v>
+        <v>11억 2,000</v>
+      </c>
+      <c r="C234">
+        <v>109</v>
       </c>
       <c r="D234" t="str">
-        <v>502동</v>
+        <v>104동</v>
       </c>
       <c r="E234" t="str">
-        <v>중층</v>
+        <v>10/18</v>
       </c>
       <c r="F234" t="str">
-        <v/>
+        <v>남동향</v>
       </c>
       <c r="G234" t="str">
-        <v>로얄동층 완전트인뷰 프리미엄확장 입주협의가 출입동 동천역도보편리</v>
+        <v>거실확장 방1확장 올수리 초역세권 도보3분 상권인접</v>
       </c>
       <c r="H234" t="str">
-        <v>asil</v>
+        <v>naver</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>써니벨리</v>
+        <v>성동마을강남</v>
       </c>
       <c r="B235" t="str">
-        <v>9억 3,000</v>
+        <v>15억</v>
       </c>
       <c r="C235">
-        <v>92</v>
+        <v>195</v>
       </c>
       <c r="D235" t="str">
-        <v>106동</v>
+        <v>101동</v>
       </c>
       <c r="E235" t="str">
-        <v>1/19</v>
+        <v>고/18</v>
       </c>
       <c r="F235" t="str">
-        <v>남향</v>
+        <v>남서향</v>
       </c>
       <c r="G235" t="str">
-        <v>정상,깨끗하고 일부수리에 전망굿 단지내초등학교 신분당선 동천역10분</v>
+        <v>깨끗하고 해잘드는 이쁜집</v>
       </c>
       <c r="H235" t="str">
         <v>naver</v>
@@ -6523,553 +6523,33 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>써니벨리</v>
+        <v>성동마을강남</v>
       </c>
       <c r="B236" t="str">
-        <v>11억 2,000</v>
-      </c>
-      <c r="C236">
-        <v>109</v>
+        <v>12억 9,000</v>
+      </c>
+      <c r="C236" t="str">
+        <v>163</v>
       </c>
       <c r="D236" t="str">
         <v>107동</v>
       </c>
       <c r="E236" t="str">
-        <v>7/18</v>
+        <v>15층</v>
       </c>
       <c r="F236" t="str">
-        <v>남향</v>
+        <v/>
       </c>
       <c r="G236" t="str">
-        <v>추천매물 로얄동 앞트인전망 결로 곰팡이없이 관리최상</v>
+        <v>무주택자, 세안고, 남향, 화이트 올수리, 트인 조망, 성복역 도보5분</v>
       </c>
       <c r="H236" t="str">
-        <v>naver</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="str">
-        <v>써니벨리</v>
-      </c>
-      <c r="B237" t="str">
-        <v>10억</v>
-      </c>
-      <c r="C237">
-        <v>92</v>
-      </c>
-      <c r="D237" t="str">
-        <v>101동</v>
-      </c>
-      <c r="E237" t="str">
-        <v>13/15</v>
-      </c>
-      <c r="F237" t="str">
-        <v>남향</v>
-      </c>
-      <c r="G237" t="str">
-        <v>28. 동천역 손곡초중 남향 방3화2 현재 세입자거주중 월세안고매매</v>
-      </c>
-      <c r="H237" t="str">
-        <v>naver</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="str">
-        <v>써니벨리</v>
-      </c>
-      <c r="B238" t="str">
-        <v>10억 3,000</v>
-      </c>
-      <c r="C238">
-        <v>109</v>
-      </c>
-      <c r="D238" t="str">
-        <v>103동</v>
-      </c>
-      <c r="E238" t="str">
-        <v>1/19</v>
-      </c>
-      <c r="F238" t="str">
-        <v>남향</v>
-      </c>
-      <c r="G238" t="str">
-        <v>초품아,방2확장 화이트수리,주인거주,강남판교 출퇴근 용이</v>
-      </c>
-      <c r="H238" t="str">
-        <v>naver</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="str">
-        <v>써니벨리</v>
-      </c>
-      <c r="B239" t="str">
-        <v>11억</v>
-      </c>
-      <c r="C239">
-        <v>109</v>
-      </c>
-      <c r="D239" t="str">
-        <v>104동</v>
-      </c>
-      <c r="E239" t="str">
-        <v>7/19</v>
-      </c>
-      <c r="F239" t="str">
-        <v>남향</v>
-      </c>
-      <c r="G239" t="str">
-        <v>로얄동 급매 짧은세안고</v>
-      </c>
-      <c r="H239" t="str">
-        <v>naver</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="str">
-        <v>써니벨리</v>
-      </c>
-      <c r="B240" t="str">
-        <v>10억</v>
-      </c>
-      <c r="C240">
-        <v>92</v>
-      </c>
-      <c r="D240" t="str">
-        <v>106동</v>
-      </c>
-      <c r="E240" t="str">
-        <v>18/19</v>
-      </c>
-      <c r="F240" t="str">
-        <v>남향</v>
-      </c>
-      <c r="G240" t="str">
-        <v>귀한매물 올확장 수리 전망트임</v>
-      </c>
-      <c r="H240" t="str">
-        <v>naver</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="str">
-        <v>써니벨리</v>
-      </c>
-      <c r="B241" t="str">
-        <v>10억 3,000</v>
-      </c>
-      <c r="C241">
-        <v>109</v>
-      </c>
-      <c r="D241" t="str">
-        <v>105동</v>
-      </c>
-      <c r="E241" t="str">
-        <v>2/19</v>
-      </c>
-      <c r="F241" t="str">
-        <v>남향</v>
-      </c>
-      <c r="G241" t="str">
-        <v>로얄동 5.1억 전세안고 매매 초품아 잔금일협의</v>
-      </c>
-      <c r="H241" t="str">
-        <v>naver</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="str">
-        <v>써니벨리</v>
-      </c>
-      <c r="B242" t="str">
-        <v>10억</v>
-      </c>
-      <c r="C242">
-        <v>92</v>
-      </c>
-      <c r="D242" t="str">
-        <v>106동</v>
-      </c>
-      <c r="E242" t="str">
-        <v>고/19</v>
-      </c>
-      <c r="F242" t="str">
-        <v>남향</v>
-      </c>
-      <c r="G242" t="str">
-        <v>정상,깨끗하고 전망굿 단지내초등학교 신분당선 동천역10분</v>
-      </c>
-      <c r="H242" t="str">
-        <v>naver</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="str">
-        <v>써니벨리</v>
-      </c>
-      <c r="B243" t="str">
-        <v>11억 5,000</v>
-      </c>
-      <c r="C243">
-        <v>109</v>
-      </c>
-      <c r="D243" t="str">
-        <v>107동</v>
-      </c>
-      <c r="E243" t="str">
-        <v>17/18</v>
-      </c>
-      <c r="F243" t="str">
-        <v>남향</v>
-      </c>
-      <c r="G243" t="str">
-        <v>로얄동 전망최고 수리됨</v>
-      </c>
-      <c r="H243" t="str">
-        <v>naver</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="str">
-        <v>써니벨리</v>
-      </c>
-      <c r="B244" t="str">
-        <v>10억</v>
-      </c>
-      <c r="C244">
-        <v>109</v>
-      </c>
-      <c r="D244" t="str">
-        <v>105동</v>
-      </c>
-      <c r="E244" t="str">
-        <v>1/19</v>
-      </c>
-      <c r="F244" t="str">
-        <v>남향</v>
-      </c>
-      <c r="G244" t="str">
-        <v>따스한남향 방확장 주인거주 채광굿 깔끔관리</v>
-      </c>
-      <c r="H244" t="str">
-        <v>naver</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="str">
-        <v>써니벨리</v>
-      </c>
-      <c r="B245" t="str">
-        <v>10억 2,000</v>
-      </c>
-      <c r="C245">
-        <v>109</v>
-      </c>
-      <c r="D245" t="str">
-        <v>102동</v>
-      </c>
-      <c r="E245" t="str">
-        <v>3/14</v>
-      </c>
-      <c r="F245" t="str">
-        <v>남향</v>
-      </c>
-      <c r="G245" t="str">
-        <v>남향 확장 세안고</v>
-      </c>
-      <c r="H245" t="str">
-        <v>naver</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="str">
-        <v>성동마을강남</v>
-      </c>
-      <c r="B246" t="str">
-        <v>13억</v>
-      </c>
-      <c r="C246">
-        <v>163</v>
-      </c>
-      <c r="D246" t="str">
-        <v>107동</v>
-      </c>
-      <c r="E246" t="str">
-        <v>15/18</v>
-      </c>
-      <c r="F246" t="str">
-        <v>남향</v>
-      </c>
-      <c r="G246" t="str">
-        <v>강추,49형,로얄동,화이트올수리,깨끗한집.초역세권,세안고다주택자</v>
-      </c>
-      <c r="H246" t="str">
-        <v>naver</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="str">
-        <v>성동마을강남</v>
-      </c>
-      <c r="B247" t="str">
-        <v>14억 5,000</v>
-      </c>
-      <c r="C247">
-        <v>163</v>
-      </c>
-      <c r="D247" t="str">
-        <v>107동</v>
-      </c>
-      <c r="E247" t="str">
-        <v>6/18</v>
-      </c>
-      <c r="F247" t="str">
-        <v>남향</v>
-      </c>
-      <c r="G247" t="str">
-        <v>로얄동 트인전망  초역세권 생활권좋음 세안고</v>
-      </c>
-      <c r="H247" t="str">
-        <v>naver</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="str">
-        <v>성동마을강남</v>
-      </c>
-      <c r="B248" t="str">
-        <v>14억 3,000</v>
-      </c>
-      <c r="C248">
-        <v>195</v>
-      </c>
-      <c r="D248" t="str">
-        <v>101동</v>
-      </c>
-      <c r="E248" t="str">
-        <v>18/18</v>
-      </c>
-      <c r="F248" t="str">
-        <v>남서향</v>
-      </c>
-      <c r="G248" t="str">
-        <v>입구동 전망굿 초역세권 화장실2수리</v>
-      </c>
-      <c r="H248" t="str">
-        <v>naver</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="str">
-        <v>성동마을강남</v>
-      </c>
-      <c r="B249" t="str">
-        <v>14억 5,000</v>
-      </c>
-      <c r="C249">
-        <v>163</v>
-      </c>
-      <c r="D249" t="str">
-        <v>105동</v>
-      </c>
-      <c r="E249" t="str">
-        <v>중/18</v>
-      </c>
-      <c r="F249" t="str">
-        <v>남향</v>
-      </c>
-      <c r="G249" t="str">
-        <v>샷시포함특올수리 성복역세권 생활편리 학군최고</v>
-      </c>
-      <c r="H249" t="str">
-        <v>naver</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="str">
-        <v>성동마을강남</v>
-      </c>
-      <c r="B250" t="str">
-        <v>12억</v>
-      </c>
-      <c r="C250">
-        <v>109</v>
-      </c>
-      <c r="D250" t="str">
-        <v>103동</v>
-      </c>
-      <c r="E250" t="str">
-        <v>중/18</v>
-      </c>
-      <c r="F250" t="str">
-        <v>남동향</v>
-      </c>
-      <c r="G250" t="str">
-        <v>정상입주,방확장,주방씽크대외수리함.성복역초역세권</v>
-      </c>
-      <c r="H250" t="str">
-        <v>naver</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="str">
-        <v>성동마을강남</v>
-      </c>
-      <c r="B251" t="str">
-        <v>11억 5,000</v>
-      </c>
-      <c r="C251">
-        <v>109</v>
-      </c>
-      <c r="D251" t="str">
-        <v>103동</v>
-      </c>
-      <c r="E251" t="str">
-        <v>11/18</v>
-      </c>
-      <c r="F251" t="str">
-        <v>남동향</v>
-      </c>
-      <c r="G251" t="str">
-        <v>올수리 폴딩도어 정상입주 성복역 도보2분 생활권좋음</v>
-      </c>
-      <c r="H251" t="str">
-        <v>naver</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="str">
-        <v>성동마을강남</v>
-      </c>
-      <c r="B252" t="str">
-        <v>13억 5,000</v>
-      </c>
-      <c r="C252">
-        <v>163</v>
-      </c>
-      <c r="D252" t="str">
-        <v>105동</v>
-      </c>
-      <c r="E252" t="str">
-        <v>7/18</v>
-      </c>
-      <c r="F252" t="str">
-        <v>남향</v>
-      </c>
-      <c r="G252" t="str">
-        <v>세안고 남향 성복역 도보2분 상권인접 기본</v>
-      </c>
-      <c r="H252" t="str">
-        <v>naver</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="str">
-        <v>성동마을강남</v>
-      </c>
-      <c r="B253" t="str">
-        <v>13억 5,000</v>
-      </c>
-      <c r="C253">
-        <v>163</v>
-      </c>
-      <c r="D253" t="str">
-        <v>106동</v>
-      </c>
-      <c r="E253" t="str">
-        <v>12/18</v>
-      </c>
-      <c r="F253" t="str">
-        <v>남동향</v>
-      </c>
-      <c r="G253" t="str">
-        <v>채광굿 초역세권 도보2분 생활권 좋음  기본</v>
-      </c>
-      <c r="H253" t="str">
-        <v>naver</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="str">
-        <v>성동마을강남</v>
-      </c>
-      <c r="B254" t="str">
-        <v>11억 2,000</v>
-      </c>
-      <c r="C254">
-        <v>109</v>
-      </c>
-      <c r="D254" t="str">
-        <v>104동</v>
-      </c>
-      <c r="E254" t="str">
-        <v>10/18</v>
-      </c>
-      <c r="F254" t="str">
-        <v>남동향</v>
-      </c>
-      <c r="G254" t="str">
-        <v>거실확장 방1확장 올수리 초역세권 도보3분 상권인접</v>
-      </c>
-      <c r="H254" t="str">
-        <v>naver</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="str">
-        <v>성동마을강남</v>
-      </c>
-      <c r="B255" t="str">
-        <v>15억</v>
-      </c>
-      <c r="C255">
-        <v>195</v>
-      </c>
-      <c r="D255" t="str">
-        <v>101동</v>
-      </c>
-      <c r="E255" t="str">
-        <v>고/18</v>
-      </c>
-      <c r="F255" t="str">
-        <v>남서향</v>
-      </c>
-      <c r="G255" t="str">
-        <v>깨끗하고 해잘드는 이쁜집</v>
-      </c>
-      <c r="H255" t="str">
-        <v>naver</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="str">
-        <v>성동마을강남</v>
-      </c>
-      <c r="B256" t="str">
-        <v>12억 9,000</v>
-      </c>
-      <c r="C256" t="str">
-        <v>163</v>
-      </c>
-      <c r="D256" t="str">
-        <v>107동</v>
-      </c>
-      <c r="E256" t="str">
-        <v>15층</v>
-      </c>
-      <c r="F256" t="str">
-        <v/>
-      </c>
-      <c r="G256" t="str">
-        <v>무주택자, 세안고, 남향, 화이트 올수리, 트인 조망, 성복역 도보5분</v>
-      </c>
-      <c r="H256" t="str">
         <v>asil</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H256"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H236"/>
   </ignoredErrors>
 </worksheet>
 </file>